--- a/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
+++ b/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>200302</t>
+          <t>220890</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ساره هانى منصور سيد رزق</t>
+          <t>يوسف حسين ناجي الصرايره</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -521,12 +521,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>200502</t>
+          <t>220896</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>مازن ايمن محمود عبدربه</t>
+          <t>احمد السر ميرغني عمر</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -548,12 +548,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>200891</t>
+          <t>220900</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>احمد جمال القبانى</t>
+          <t>ديما حسن نصر الله الزاملي</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -575,12 +575,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>211139</t>
+          <t>220902</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>احمد يعقوب عمر طرايره</t>
+          <t>كاتيا منيمنة</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -602,12 +602,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>211513</t>
+          <t>220908</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ايه محمد سعد الدين العدوى</t>
+          <t>عمرو زين العابدين طلعت عابدين</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>220321</t>
+          <t>220909</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>احمد عبد الرحمن جابر سالمان</t>
+          <t>احمد جمال محمد عليمى محمد</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -656,12 +656,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>220392</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>انس محمد محمد صوابى هيكل</t>
+          <t>شيماء بدر زبير علي</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -683,12 +683,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>220449</t>
+          <t>220914</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>حبيبة الله وائل البرماوى</t>
+          <t>محمد بن ضيف الله بن رزق الصبحى</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -710,12 +710,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>220452</t>
+          <t>220919</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>حبيبه شريف احمد عبدالعليم عبدالحميد</t>
+          <t>احمد سليم عيسى ابو لاوى</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>220494</t>
+          <t>220920</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>رودينا تامر محمد الدهان</t>
+          <t>دارين محمد طاهر</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -764,12 +764,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>220501</t>
+          <t>220925</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ريماس سامر العطائي</t>
+          <t>دينا زياد ابراهيم زقماط</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -791,12 +791,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>220516</t>
+          <t>220927</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>سلمى حسين عبد المنعم عبد الحميد محمد</t>
+          <t>سعيد احمد سعيد محمد عبدالسيد</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -818,12 +818,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>220537</t>
+          <t>220928</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>شروق هانى مبروك على السيد النجار</t>
+          <t>ابراهيم عبدالفتاح ابراهيم السروري</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -845,12 +845,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>220550</t>
+          <t>220929</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>شيماء شريف محمد عبد الرحمن احمد</t>
+          <t>الوليد بن عبدالله بن محمد عامر</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -872,12 +872,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>220577</t>
+          <t>220930</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد عبداللطيف شهاب</t>
+          <t>يوسف نبيل فريد شاهين</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>220937</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
+          <t>اسيل يحيى محمد المزايده</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -926,12 +926,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>220616</t>
+          <t>220940</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>غاده احمد احمد احمد الشريف</t>
+          <t>عبدالرحمن محمد محسن الزقري</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -953,12 +953,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>220623</t>
+          <t>220942</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>فاطمه احمد محمد محمود كرم</t>
+          <t>عدي علي فلاح الحديد</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -980,12 +980,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>220624</t>
+          <t>220947</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>فاطمه السيد محمد فتحى عطيه الله</t>
+          <t>مهند عبد الفتاح سلام مقبل</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>220625</t>
+          <t>220950</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>فاطمه حموده على عبد الحميد حموده</t>
+          <t>يوسف اسماعيل ابراهيم احمد</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1034,12 +1034,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>220627</t>
+          <t>220951</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
+          <t>محمد تيسير محمد ياسين</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1061,12 +1061,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>220628</t>
+          <t>220954</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>فاطمه محمود محمد امام</t>
+          <t>طيف فرج علي العماري</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>220629</t>
+          <t>220955</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>فتحى محمد فتحى السيد عبد الله</t>
+          <t>غاده عبدالاله عبدالكريم عبدالله</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>220630</t>
+          <t>220956</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>فريده محمود فؤاد محمود</t>
+          <t>نور الحسين أسعد جاسم العكيلي</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1142,12 +1142,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>220635</t>
+          <t>220958</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>كريم ايمن محمد مصطفى ابراهيم</t>
+          <t>محمد حميد حمود علي الديلي</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1169,12 +1169,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>220636</t>
+          <t>220959</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>كريم سعيد احمد ابراهيم الحريزى</t>
+          <t>ايليا سالم يعقوب المدانات</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1196,12 +1196,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>220639</t>
+          <t>220961</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>كريم مصطفى عبد الرحمن على سعد</t>
+          <t>رهف نزار احمد الامام</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1223,12 +1223,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>220645</t>
+          <t>220963</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>لجين احمد عبد الله البسطويسى</t>
+          <t>شهد بنت عبدالله بن حسين ال الصومعي</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1250,12 +1250,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>220646</t>
+          <t>220964</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>لجين اشرف جلال عبد الرحمن السمرى</t>
+          <t>ميس غسان مرشد مفارجة</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1277,12 +1277,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>220966</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
+          <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1-D1</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1304,12 +1304,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>220649</t>
+          <t>180289</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>لؤى على حسين حسن ابو صفيه</t>
+          <t>عبد الرحمن سلامة حنفى</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1331,12 +1331,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>220651</t>
+          <t>200302</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ليلى اشرف وصفى</t>
+          <t>ساره هانى منصور سيد رزق</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1358,12 +1358,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>220653</t>
+          <t>200502</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ماجد حسنى السيد التلاوى</t>
+          <t>مازن ايمن محمود عبدربه</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1385,12 +1385,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>220655</t>
+          <t>200891</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>مارى مجدى منير عبده</t>
+          <t>احمد جمال القبانى</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1412,12 +1412,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>220659</t>
+          <t>211139</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>مالك محمود على محمود زين الدين</t>
+          <t>احمد يعقوب عمر طرايره</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>211513</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
+          <t>ايه محمد سعد الدين العدوى</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>220662</t>
+          <t>211701</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
+          <t>فادى عبدالله جميل شورى</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1493,12 +1493,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>220666</t>
+          <t>220321</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>محمد احمد فتحى احمد احمد</t>
+          <t>احمد عبد الرحمن جابر سالمان</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1520,12 +1520,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>220667</t>
+          <t>220392</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>محمد اسامه علاء الدين اللو</t>
+          <t>انس محمد محمد صوابى هيكل</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>220669</t>
+          <t>220449</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>محمد السعيد السعيد محمد شعبان</t>
+          <t>حبيبة الله وائل البرماوى</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1574,12 +1574,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>220670</t>
+          <t>220452</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>محمد السعيد مسعد مصطفى حراز</t>
+          <t>حبيبه شريف احمد عبدالعليم عبدالحميد</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>220672</t>
+          <t>220494</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>محمد الشحات على احمد سرور</t>
+          <t>رودينا تامر محمد الدهان</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1628,12 +1628,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>220673</t>
+          <t>220501</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>محمد أيمن محمد أحمد ناصف</t>
+          <t>ريماس سامر العطائي</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>220674</t>
+          <t>220516</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>محمد باسم عبد الكريم محمود</t>
+          <t>سلمى حسين عبد المنعم عبد الحميد محمد</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>220678</t>
+          <t>220537</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>محمد بهاء عبد الحميد عبد الغفار</t>
+          <t>شروق هانى مبروك على السيد النجار</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -1709,12 +1709,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>220679</t>
+          <t>220550</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>محمد جابر توفيق الشافعى</t>
+          <t>شيماء شريف محمد عبد الرحمن احمد</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1736,12 +1736,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>220680</t>
+          <t>220577</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>محمد حسن جلال عبد المجيد وهدان</t>
+          <t>عبدالرحمن محمد عبداللطيف شهاب</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>220683</t>
+          <t>220615</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>محمد سعيد محمود عبد المنعم محمود</t>
+          <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -1790,12 +1790,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>220684</t>
+          <t>220616</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>محمد صبرى جوده عبد الله خضر</t>
+          <t>غاده احمد احمد احمد الشريف</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -1817,12 +1817,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>220685</t>
+          <t>220623</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>محمد صلاح حسن عبد الله حسن</t>
+          <t>فاطمه احمد محمد محمود كرم</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -1844,12 +1844,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>220686</t>
+          <t>220624</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
+          <t>فاطمه السيد محمد فتحى عطيه الله</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>220687</t>
+          <t>220625</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>محمد طارق محمد عبد الرحمن العرينى</t>
+          <t>فاطمه حموده على عبد الحميد حموده</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>220688</t>
+          <t>220627</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>محمد عبد الحفيظ عبد الله محمد على</t>
+          <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>220689</t>
+          <t>220628</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
+          <t>فاطمه محمود محمد امام</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -1952,12 +1952,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>220690</t>
+          <t>220629</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>محمد عبد النبى عطيه ابو شعيشع</t>
+          <t>فتحى محمد فتحى السيد عبد الله</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -1979,12 +1979,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>220691</t>
+          <t>220630</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>محمد عبدالهادى عبدالمنعم عمر</t>
+          <t>فريده محمود فؤاد محمود</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -2006,12 +2006,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>220693</t>
+          <t>220635</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>محمد علاء محمد عبد العزيز عبد الله</t>
+          <t>كريم ايمن محمد مصطفى ابراهيم</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2033,12 +2033,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>220694</t>
+          <t>220636</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>محمد على محمد احمد محمد</t>
+          <t>كريم سعيد احمد ابراهيم الحريزى</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2060,12 +2060,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>220639</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>محمد محمد عبد الله التهامي</t>
+          <t>كريم مصطفى عبد الرحمن على سعد</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>220701</t>
+          <t>220645</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
+          <t>لجين احمد عبد الله البسطويسى</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2114,12 +2114,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>220702</t>
+          <t>220646</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>محمد محيى الدين محمد سيد مكاوى</t>
+          <t>لجين اشرف جلال عبد الرحمن السمرى</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2141,12 +2141,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>220703</t>
+          <t>220647</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>محمد مختار شعبان هلالى سليمان</t>
+          <t>لوجين السيد محروس اسماعيل</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2168,12 +2168,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>220705</t>
+          <t>220648</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>محمد مفرح عبد الباسط عبد الحليم</t>
+          <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -2195,12 +2195,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>220706</t>
+          <t>220649</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>محمد وائل محمد العيسوى</t>
+          <t>لؤى على حسين حسن ابو صفيه</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -2222,12 +2222,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>220707</t>
+          <t>220651</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>محمد وحيد محمد رزق</t>
+          <t>ليلى اشرف وصفى</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>220708</t>
+          <t>220653</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>محمد ياسر الشافعى محمد على</t>
+          <t>ماجد حسنى السيد التلاوى</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -2276,12 +2276,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>220709</t>
+          <t>220655</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>محمد ياسر حامد دياب حمد</t>
+          <t>مارى مجدى منير عبده</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2303,12 +2303,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>220710</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>محمود جمال حسين محمد رسلان</t>
+          <t>مالك محمود على محمود زين الدين</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>220711</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
+          <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>220712</t>
+          <t>220662</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>محمود حسن عبد النبى حسين</t>
+          <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>220714</t>
+          <t>220666</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>محمود كريم شحاته حسن كرد</t>
+          <t>محمد احمد فتحى احمد احمد</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>220717</t>
+          <t>220667</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>محمود منصور محمود محمد السيد يعقوب</t>
+          <t>محمد اسامه علاء الدين اللو</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -2438,12 +2438,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>220720</t>
+          <t>220669</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>مروان صبحى ابو الحسن محمد على</t>
+          <t>محمد السعيد السعيد محمد شعبان</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>220670</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
+          <t>محمد السعيد مسعد مصطفى حراز</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -2492,12 +2492,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>220722</t>
+          <t>220672</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>مروه عبد الحميد على حسن ايوب</t>
+          <t>محمد الشحات على احمد سرور</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -2519,12 +2519,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>220723</t>
+          <t>220673</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>مريم ابراهيم احمد ابراهيم مبارك</t>
+          <t>محمد أيمن محمد أحمد ناصف</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>220724</t>
+          <t>220674</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>مريم الحسن احمد ابراهيم بيومى</t>
+          <t>محمد باسم عبد الكريم محمود</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2573,12 +2573,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>220725</t>
+          <t>220678</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>مريم ايمن عبد الله محمود فخرى</t>
+          <t>محمد بهاء عبد الحميد عبد الغفار</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -2600,12 +2600,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>220726</t>
+          <t>220679</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>مريم ايمن فؤاد عبدالستار</t>
+          <t>محمد جابر توفيق الشافعى</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>220727</t>
+          <t>220680</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>مريم ايهاب ملاك ثابت</t>
+          <t>محمد حسن جلال عبد المجيد وهدان</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -2654,12 +2654,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>220729</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>مريم رضا محمد ابراهيم صبره</t>
+          <t>محمد سعيد محمود عبد المنعم محمود</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2681,12 +2681,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>220730</t>
+          <t>220684</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>مريم شعبان مصباح خليفه</t>
+          <t>محمد صبرى جوده عبد الله خضر</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>220731</t>
+          <t>220685</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>مريم شفيق صبحى شفيق حنا</t>
+          <t>محمد صلاح حسن عبد الله حسن</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -2735,12 +2735,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>220732</t>
+          <t>220686</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>مريم عمرو يحيى عبده مدنى</t>
+          <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -2762,12 +2762,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>220733</t>
+          <t>220687</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد احمد فاروق الديب الشريف</t>
+          <t>محمد طارق محمد عبد الرحمن العرينى</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2789,12 +2789,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>220734</t>
+          <t>220688</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد احمد محمد عبد المنعم</t>
+          <t>محمد عبد الحفيظ عبد الله محمد على</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>220735</t>
+          <t>220689</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد ثروت صايم مصطفى</t>
+          <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>220737</t>
+          <t>220690</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
+          <t>محمد عبد النبى عطيه ابو شعيشع</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>220740</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
+          <t>محمد عبدالهادى عبدالمنعم عمر</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -2897,12 +2897,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>220742</t>
+          <t>220693</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
+          <t>محمد علاء محمد عبد العزيز عبد الله</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -2924,12 +2924,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>220744</t>
+          <t>220694</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
+          <t>محمد على محمد احمد محمد</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -2951,12 +2951,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>220745</t>
+          <t>220698</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>مصطفى محمود مصطفى محمود</t>
+          <t>محمد محمد احمد الفتيانى</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -2978,12 +2978,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>220746</t>
+          <t>220700</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>معاذ طاهر محمد شبانه على</t>
+          <t>محمد محمد عبد الله التهامي</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3005,12 +3005,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>220747</t>
+          <t>220701</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>ملك عبدالغنى احمد حسن</t>
+          <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>220748</t>
+          <t>220702</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>ملك عمرو على حسن</t>
+          <t>محمد محيى الدين محمد سيد مكاوى</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>220749</t>
+          <t>220703</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>ملك ياسر عبد الوهاب محمد الغندور</t>
+          <t>محمد مختار شعبان هلالى سليمان</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -3086,12 +3086,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>220751</t>
+          <t>220705</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>منة الله هانى عبد السميع شكرى</t>
+          <t>محمد مفرح عبد الباسط عبد الحليم</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3113,12 +3113,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>220752</t>
+          <t>220706</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>منصور هانى منصور عبدالله</t>
+          <t>محمد وائل محمد العيسوى</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -3140,12 +3140,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>220753</t>
+          <t>220707</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>منه الله احمد محمد جمعه عثمان</t>
+          <t>محمد وحيد محمد رزق</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -3167,12 +3167,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>220754</t>
+          <t>220708</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>منه الله محمد صالح محمد النور</t>
+          <t>محمد ياسر الشافعى محمد على</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -3194,12 +3194,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>220755</t>
+          <t>220709</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>منه الله محمد عبد الرازق سالم غاليه</t>
+          <t>محمد ياسر حامد دياب حمد</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>220756</t>
+          <t>220710</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>منه عبد الوهاب عبدالله مصطفى</t>
+          <t>محمود جمال حسين محمد رسلان</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -3248,12 +3248,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>220758</t>
+          <t>220711</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>منه محمود محمد احمد</t>
+          <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>220759</t>
+          <t>220712</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>منى عبد الحميد ناصف سيف</t>
+          <t>محمود حسن عبد النبى حسين</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>220760</t>
+          <t>220714</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
+          <t>محمود كريم شحاته حسن كرد</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -3329,12 +3329,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>220762</t>
+          <t>220717</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>مؤيد وليد علي كرجه</t>
+          <t>محمود منصور محمود محمد السيد يعقوب</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -3356,12 +3356,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>220764</t>
+          <t>220720</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>مياده سلامه قاسم محمد السيد</t>
+          <t>مروان صبحى ابو الحسن محمد على</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3383,12 +3383,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>220765</t>
+          <t>220721</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>ميار احمد صبحى السيد السيد</t>
+          <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>220767</t>
+          <t>220722</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>ميار صلاح محمد سليمان سليمان</t>
+          <t>مروه عبد الحميد على حسن ايوب</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>220772</t>
+          <t>220723</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
+          <t>مريم ابراهيم احمد ابراهيم مبارك</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -3464,12 +3464,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>220773</t>
+          <t>220724</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ندى اشرف عبد الله ابراهيم</t>
+          <t>مريم الحسن احمد ابراهيم بيومى</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -3491,12 +3491,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>220774</t>
+          <t>220725</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>ندى اشرف محمد محمد</t>
+          <t>مريم ايمن عبد الله محمود فخرى</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>220726</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ندى حسن السيد احمد عطا الله</t>
+          <t>مريم ايمن فؤاد عبدالستار</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -3545,12 +3545,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>220776</t>
+          <t>220727</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>ندى عاطف محمد محمد عبده الشيمى</t>
+          <t>مريم ايهاب ملاك ثابت</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>220777</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ندى على زيد عبد الرحمن</t>
+          <t>مريم رضا محمد ابراهيم صبره</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>220778</t>
+          <t>220730</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>ندى محمد احمد حامد عامر</t>
+          <t>مريم شعبان مصباح خليفه</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -3626,12 +3626,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>220780</t>
+          <t>220731</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>نصر الدين الابراهيم</t>
+          <t>مريم شفيق صبحى شفيق حنا</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -3653,12 +3653,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>220781</t>
+          <t>220732</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>نظمى مصطفى نظمى على عبد النبى</t>
+          <t>مريم عمرو يحيى عبده مدنى</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -3680,12 +3680,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>220782</t>
+          <t>220733</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
+          <t>مريم محمد احمد فاروق الديب الشريف</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -3707,12 +3707,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>220783</t>
+          <t>220734</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>نهى احمد ابراهيم محمد عيطه</t>
+          <t>مريم محمد احمد محمد عبد المنعم</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>220735</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>نهى على عبد الرحمن على</t>
+          <t>مريم محمد ثروت صايم مصطفى</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -3761,12 +3761,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>220787</t>
+          <t>220736</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>نور محمد عبد الجليل محمد</t>
+          <t>مريم محمد عطيه عبد السلام</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -3788,12 +3788,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>220788</t>
+          <t>220737</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>نوران اسامه محمد محمود</t>
+          <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -3815,12 +3815,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>220789</t>
+          <t>220740</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>نوران فوزى شعبان فوزى علام</t>
+          <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -3842,12 +3842,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>220790</t>
+          <t>220742</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>نورهان حسن عبد الرحمن حسن محمد</t>
+          <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -3869,12 +3869,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>220791</t>
+          <t>220744</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>نورهان محمد عبد العزيز حسن</t>
+          <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -3896,12 +3896,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>220792</t>
+          <t>220745</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>نورهان محمود السيد محمود اللقانى</t>
+          <t>مصطفى محمود مصطفى محمود</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -3923,12 +3923,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>220793</t>
+          <t>220746</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>نورين احمد عبد الحكيم رضوان</t>
+          <t>معاذ طاهر محمد شبانه على</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -3950,12 +3950,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>220794</t>
+          <t>220747</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
+          <t>ملك عبدالغنى احمد حسن</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>220795</t>
+          <t>220748</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
+          <t>ملك عمرو على حسن</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -4004,12 +4004,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>220796</t>
+          <t>220749</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
+          <t>ملك ياسر عبد الوهاب محمد الغندور</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -4031,12 +4031,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>220797</t>
+          <t>220751</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
+          <t>منة الله هانى عبد السميع شكرى</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>220799</t>
+          <t>220752</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>هاجر احمد رمضان سعد الفرحاتى</t>
+          <t>منصور هانى منصور عبدالله</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -4085,12 +4085,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>220800</t>
+          <t>220753</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>هاجر عاطف سيد عبد الجيد احمد</t>
+          <t>منه الله احمد محمد جمعه عثمان</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -4112,12 +4112,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>220801</t>
+          <t>220754</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>هايدى محمد حسين رفاعى فراج</t>
+          <t>منه الله محمد صالح محمد النور</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>220802</t>
+          <t>220755</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>هدى مدحت خيرى احمد فرج</t>
+          <t>منه الله محمد عبد الرازق سالم غاليه</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>220803</t>
+          <t>220756</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>هرمينا عبد الله جاد جرجس</t>
+          <t>منه عبد الوهاب عبدالله مصطفى</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -4193,12 +4193,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>220804</t>
+          <t>220758</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>هنا خليل عبد الرؤف محمد سعيد</t>
+          <t>منه محمود محمد احمد</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>220805</t>
+          <t>220759</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>وسام ايمن على الشريف</t>
+          <t>منى عبد الحميد ناصف سيف</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>220807</t>
+          <t>220760</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>وليد ياسر عبد الشافى محمود</t>
+          <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -4274,12 +4274,12 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>220808</t>
+          <t>220762</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ياسمين عادل السيد الفرغلى حسن</t>
+          <t>مؤيد وليد علي كرجه</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -4301,12 +4301,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>220809</t>
+          <t>220764</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>يحيى احمد محمد عبد الفتاح الزيات</t>
+          <t>مياده سلامه قاسم محمد السيد</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -4328,12 +4328,12 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>220810</t>
+          <t>220765</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>يحيى محمد يحى على</t>
+          <t>ميار احمد صبحى السيد السيد</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>220813</t>
+          <t>220767</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
+          <t>ميار صلاح محمد سليمان سليمان</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>220814</t>
+          <t>220772</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>يوسف جلال محمد عبد الفتاح صالح</t>
+          <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -4409,12 +4409,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>220816</t>
+          <t>220773</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>يوسف عمرو على حفنى ابراهيم</t>
+          <t>ندى اشرف عبد الله ابراهيم</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -4436,12 +4436,12 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>220817</t>
+          <t>220774</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>يوسف فهيم عبد الحميد ابو عزيز</t>
+          <t>ندى اشرف محمد محمد</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>220818</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>يوسف محمد رضا جلال احمد سيد احمد</t>
+          <t>ندى حسن السيد احمد عطا الله</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -4490,12 +4490,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220776</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>يوسف محمد محمد السيد البطه</t>
+          <t>ندى عاطف محمد محمد عبده الشيمى</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>220820</t>
+          <t>220777</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>يوسف محمود محمد ابراهيم</t>
+          <t>ندى على زيد عبد الرحمن</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -4544,12 +4544,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>220821</t>
+          <t>220778</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>يوسف مصطفى محمد رسلان</t>
+          <t>ندى محمد احمد حامد عامر</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -4571,12 +4571,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>220822</t>
+          <t>220779</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>يوسف مصطفى مصطفى محمد</t>
+          <t>نزار عمرو حسن عبد الغنى</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -4598,12 +4598,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>220824</t>
+          <t>220780</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>يوسف وائل حامد ابراهيم العالم</t>
+          <t>نصر الدين الابراهيم</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>220825</t>
+          <t>220781</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>يوسف سيد محمد يوسف</t>
+          <t>نظمى مصطفى نظمى على عبد النبى</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>220826</t>
+          <t>220782</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>عبد الله خالد احمد باحاذق</t>
+          <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -4679,12 +4679,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>220827</t>
+          <t>220783</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>أبوبكر طارق أبوبكر رمضان</t>
+          <t>نهى احمد ابراهيم محمد عيطه</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -4706,12 +4706,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>220828</t>
+          <t>220784</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>سلمى مصطفى عبد العاطى حسن ناصف</t>
+          <t>نهى على عبد الرحمن على</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -4733,12 +4733,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>220829</t>
+          <t>220787</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>تبارك رائد حسن كميل</t>
+          <t>نور محمد عبد الجليل محمد</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -4760,12 +4760,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>220830</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>مصطفى محمد على</t>
+          <t>نوران اسامه محمد محمود</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -4787,12 +4787,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>220832</t>
+          <t>220789</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>احمد عبد الله نعمان محمد</t>
+          <t>نوران فوزى شعبان فوزى علام</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -4814,12 +4814,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>220833</t>
+          <t>220790</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>رغد فيصل عقيل العمايري</t>
+          <t>نورهان حسن عبد الرحمن حسن محمد</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -4841,12 +4841,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>220834</t>
+          <t>220791</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>احمد سليمان محمد</t>
+          <t>نورهان محمد عبد العزيز حسن</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -4868,12 +4868,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>220838</t>
+          <t>220792</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>حمزه طارق الطراد</t>
+          <t>نورهان محمود السيد محمود اللقانى</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -4895,12 +4895,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>220839</t>
+          <t>220793</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>عزام نبيل يحي العمير</t>
+          <t>نورين احمد عبد الحكيم رضوان</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -4922,12 +4922,12 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>220845</t>
+          <t>220794</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ريان تاج الدين عبد الله أحمد</t>
+          <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -4949,12 +4949,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>220848</t>
+          <t>220795</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>عبد الله مسعود مصطفى</t>
+          <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -4976,12 +4976,12 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>220853</t>
+          <t>220796</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>قند عدي بدران</t>
+          <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>220856</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>ماسه بلال الدهبي</t>
+          <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -5030,12 +5030,12 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>220857</t>
+          <t>220799</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>محمد عبده علوي محمد</t>
+          <t>هاجر احمد رمضان سعد الفرحاتى</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -5057,12 +5057,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>220867</t>
+          <t>220800</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>شهد جمعه على عبد الفتاح</t>
+          <t>هاجر عاطف سيد عبد الجيد احمد</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -5084,12 +5084,12 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>220876</t>
+          <t>220801</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>عبد المهيمن مهند سلمان</t>
+          <t>هايدى محمد حسين رفاعى فراج</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -5111,12 +5111,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>220878</t>
+          <t>220802</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
+          <t>هدى مدحت خيرى احمد فرج</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -5138,12 +5138,12 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>220879</t>
+          <t>220803</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>علي بن محمد بن على المحمد صالح</t>
+          <t>هرمينا عبد الله جاد جرجس</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -5165,12 +5165,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>220889</t>
+          <t>220804</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>سجى السر ميرغني عمر</t>
+          <t>هنا خليل عبد الرؤف محمد سعيد</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -5192,12 +5192,12 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>220896</t>
+          <t>220805</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>احمد السر ميرغني عمر</t>
+          <t>وسام ايمن على الشريف</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -5219,12 +5219,12 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>220900</t>
+          <t>220807</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>ديما حسن نصر الله الزاملي</t>
+          <t>وليد ياسر عبد الشافى محمود</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -5246,12 +5246,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>220902</t>
+          <t>220808</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>كاتيا منيمنة</t>
+          <t>ياسمين عادل السيد الفرغلى حسن</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -5273,12 +5273,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>220908</t>
+          <t>220809</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>عمرو زين العابدين طلعت عابدين</t>
+          <t>يحيى احمد محمد عبد الفتاح الزيات</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -5300,12 +5300,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>220909</t>
+          <t>220810</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>احمد جمال محمد عليمى محمد</t>
+          <t>يحيى محمد يحى على</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -5327,12 +5327,12 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>220912</t>
+          <t>220813</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>شيماء بدر زبير علي</t>
+          <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>220914</t>
+          <t>220814</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>محمد بن ضيف الله بن رزق الصبحى</t>
+          <t>يوسف جلال محمد عبد الفتاح صالح</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>220919</t>
+          <t>220815</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>احمد سليم عيسى ابو لاوى</t>
+          <t>يوسف حمدى احمد طاجن</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>220816</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>دارين محمد طاهر</t>
+          <t>يوسف عمرو على حفنى ابراهيم</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -5435,12 +5435,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>220925</t>
+          <t>220817</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>دينا زياد ابراهيم زقماط</t>
+          <t>يوسف فهيم عبد الحميد ابو عزيز</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -5462,12 +5462,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>220927</t>
+          <t>220818</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>سعيد احمد سعيد محمد عبدالسيد</t>
+          <t>يوسف محمد رضا جلال احمد سيد احمد</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>220928</t>
+          <t>220819</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>ابراهيم عبدالفتاح ابراهيم السروري</t>
+          <t>يوسف محمد محمد السيد البطه</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -5516,12 +5516,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>220929</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>الوليد بن عبدالله بن محمد عامر</t>
+          <t>يوسف محمود محمد ابراهيم</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>220930</t>
+          <t>220821</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>يوسف نبيل فريد شاهين</t>
+          <t>يوسف مصطفى محمد رسلان</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -5570,12 +5570,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>220937</t>
+          <t>220822</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>اسيل يحيى محمد المزايده</t>
+          <t>يوسف مصطفى مصطفى محمد</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -5597,12 +5597,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>220940</t>
+          <t>220824</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد محسن الزقري</t>
+          <t>يوسف وائل حامد ابراهيم العالم</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>220942</t>
+          <t>220825</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>عدي علي فلاح الحديد</t>
+          <t>يوسف سيد محمد يوسف</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -5651,12 +5651,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>220947</t>
+          <t>220826</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>مهند عبد الفتاح سلام مقبل</t>
+          <t>عبد الله خالد احمد باحاذق</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -5678,12 +5678,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>220950</t>
+          <t>220827</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>يوسف اسماعيل ابراهيم احمد</t>
+          <t>أبوبكر طارق أبوبكر رمضان</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -5705,12 +5705,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>220951</t>
+          <t>220828</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>محمد تيسير محمد ياسين</t>
+          <t>سلمى مصطفى عبد العاطى حسن ناصف</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>220954</t>
+          <t>220829</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>طيف فرج علي العماري</t>
+          <t>تبارك رائد حسن كميل</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -5759,12 +5759,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>220955</t>
+          <t>220830</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>غاده عبدالاله عبدالكريم عبدالله</t>
+          <t>مصطفى محمد على</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -5786,12 +5786,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>220956</t>
+          <t>220832</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>نور الحسين أسعد جاسم العكيلي</t>
+          <t>احمد عبد الله نعمان محمد</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -5813,12 +5813,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>220958</t>
+          <t>220833</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>محمد حميد حمود علي الديلي</t>
+          <t>رغد فيصل عقيل العمايري</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -5840,12 +5840,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>220834</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>ايليا سالم يعقوب المدانات</t>
+          <t>احمد سليمان محمد</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
@@ -5867,12 +5867,12 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>220961</t>
+          <t>220838</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>رهف نزار احمد الامام</t>
+          <t>حمزه طارق الطراد</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -5894,12 +5894,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>220963</t>
+          <t>220839</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>شهد بنت عبدالله بن حسين ال الصومعي</t>
+          <t>عزام نبيل يحي العمير</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -5921,12 +5921,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>220964</t>
+          <t>220845</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>ميس غسان مرشد مفارجة</t>
+          <t>ريان تاج الدين عبد الله أحمد</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -5948,12 +5948,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>220966</t>
+          <t>220848</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
+          <t>عبد الله مسعود مصطفى</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
@@ -5975,12 +5975,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>220970</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>مبارك حسن ابراهيم</t>
+          <t>قند عدي بدران</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -6002,12 +6002,12 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>220971</t>
+          <t>220856</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>فراس حسين نعيم الكوز</t>
+          <t>ماسه بلال الدهبي</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>220972</t>
+          <t>220857</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>عاصم عبدالحكيم محمد سعيد ناصر</t>
+          <t>محمد عبده علوي محمد</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -6056,12 +6056,12 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>220974</t>
+          <t>220867</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>مايا رضوان احمد سالم</t>
+          <t>شهد جمعه على عبد الفتاح</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -6083,12 +6083,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>220979</t>
+          <t>220876</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>محمد حسين محمد الحامد</t>
+          <t>عبد المهيمن مهند سلمان</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -6110,12 +6110,12 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>220983</t>
+          <t>220878</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>حسام محمد احمد الكوز</t>
+          <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
@@ -6137,12 +6137,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>220986</t>
+          <t>220879</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>هاشم احمد صالح الشرجي</t>
+          <t>علي بن محمد بن على المحمد صالح</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
@@ -6164,12 +6164,12 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>220989</t>
+          <t>220889</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>مشاري محمد يحيي الكحلاني</t>
+          <t>سجى السر ميرغني عمر</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
@@ -6191,12 +6191,12 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>220991</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>عمر حسام الدين الزيبق</t>
+          <t>نهال حسام زهره</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
@@ -6218,12 +6218,12 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>220992</t>
+          <t>220970</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>يحيى عبدالغني بني</t>
+          <t>مبارك حسن ابراهيم</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -6245,12 +6245,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>220996</t>
+          <t>220971</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>صفية وفائي</t>
+          <t>فراس حسين نعيم الكوز</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -6272,12 +6272,12 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>220997</t>
+          <t>220972</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>احمد عماد الدين محمد عبد الرحمن</t>
+          <t>عاصم عبدالحكيم محمد سعيد ناصر</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -6299,12 +6299,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>221002</t>
+          <t>220974</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>هاجر مؤيد السلوم</t>
+          <t>مايا رضوان احمد سالم</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>221006</t>
+          <t>220979</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>فهد هارون ادم محمد</t>
+          <t>محمد حسين محمد الحامد</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>221008</t>
+          <t>220983</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>وفاق عبدالوهاب محمد ابراهيم</t>
+          <t>حسام محمد احمد الكوز</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -6380,12 +6380,12 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>221012</t>
+          <t>220986</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>اسامه الشيخ احمد الامام</t>
+          <t>هاشم احمد صالح الشرجي</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>221015</t>
+          <t>220989</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>وفاء حسين ميرغنى محمود</t>
+          <t>مشاري محمد يحيي الكحلاني</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -6434,12 +6434,12 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>221016</t>
+          <t>220991</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>ايمن ناصر محمد ابو ديه</t>
+          <t>عمر حسام الدين الزيبق</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -6461,12 +6461,12 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>221018</t>
+          <t>220992</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>رامي احمد الخطيب</t>
+          <t>يحيى عبدالغني بني</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>221020</t>
+          <t>220996</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>مي سلوم سالم لم يصعد</t>
+          <t>صفية وفائي</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
@@ -6515,12 +6515,12 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>221021</t>
+          <t>220997</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>عثمان ابوالقاسم احمد حسن</t>
+          <t>احمد عماد الدين محمد عبد الرحمن</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -6542,12 +6542,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>221023</t>
+          <t>221002</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>مرام عبدالله محمد حامد</t>
+          <t>هاجر مؤيد السلوم</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
@@ -6569,12 +6569,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>221006</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>بتول محمد يوسف</t>
+          <t>فهد هارون ادم محمد</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -6596,12 +6596,12 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>221029</t>
+          <t>221008</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>معتصم توفيق محمد بكرون</t>
+          <t>وفاق عبدالوهاب محمد ابراهيم</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -6623,12 +6623,12 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>221035</t>
+          <t>221012</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>محمد بدر احمد علي مول الدويله</t>
+          <t>اسامه الشيخ احمد الامام</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>221036</t>
+          <t>221015</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>عبد السلام وليد عبد السلام ابو حلوان</t>
+          <t>وفاء حسين ميرغنى محمود</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
@@ -6677,12 +6677,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>221037</t>
+          <t>221016</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>رنا بنت عبد الغني بن بكر برناوي</t>
+          <t>ايمن ناصر محمد ابو ديه</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -6704,12 +6704,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>221040</t>
+          <t>221018</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>محمد الطاهر محمد الطاهر</t>
+          <t>رامي احمد الخطيب</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>221046</t>
+          <t>221020</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>احمد مجدي امين محمد</t>
+          <t>مي سلوم سالم لم يصعد</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -6758,12 +6758,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>221048</t>
+          <t>221021</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
+          <t>عثمان ابوالقاسم احمد حسن</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -6785,12 +6785,12 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>221049</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>ادهم عامر عبدالحافظ احمد محمد</t>
+          <t>مرام عبدالله محمد حامد</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -6812,12 +6812,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>221050</t>
+          <t>221025</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>اسراء احمد محمد عبد الصادق نور</t>
+          <t>بتول محمد يوسف</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
@@ -6839,12 +6839,12 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>221051</t>
+          <t>221029</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>اسراء هشام محمد عبد المنعم</t>
+          <t>معتصم توفيق محمد بكرون</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -6866,12 +6866,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>221052</t>
+          <t>221035</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>امنيه سلامه عبده محمد</t>
+          <t>محمد بدر احمد علي مول الدويله</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>221053</t>
+          <t>221036</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>امينه خالد عوض عفيفى تاج الدين</t>
+          <t>عبد السلام وليد عبد السلام ابو حلوان</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -6920,12 +6920,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>221054</t>
+          <t>221037</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>انجي علاء سعد الدين الشحات السيد</t>
+          <t>رنا بنت عبد الغني بن بكر برناوي</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
@@ -6947,12 +6947,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>221055</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>ايلاري هاني سند ماضي</t>
+          <t>محمد الطاهر محمد الطاهر</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -6974,12 +6974,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>221056</t>
+          <t>221046</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>إيريني وجدي عزمي عبدالمسيح</t>
+          <t>احمد مجدي امين محمد</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
@@ -7001,12 +7001,12 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>221059</t>
+          <t>221047</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>أحمد عزت مختار عزت</t>
+          <t>احمد محسن محمد ماهر ابو هاشم</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -7028,12 +7028,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>221060</t>
+          <t>221048</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
+          <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
@@ -7055,12 +7055,12 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>221062</t>
+          <t>221049</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
+          <t>ادهم عامر عبدالحافظ احمد محمد</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -7082,12 +7082,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>221063</t>
+          <t>221050</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
+          <t>اسراء احمد محمد عبد الصادق نور</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
@@ -7109,12 +7109,12 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>221064</t>
+          <t>221051</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>أكرم مصطفي فتحي محمد</t>
+          <t>اسراء هشام محمد عبد المنعم</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -7136,12 +7136,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>221066</t>
+          <t>221052</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>أية عبدالسميع محمد سليمان</t>
+          <t>امنيه سلامه عبده محمد</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
@@ -7163,12 +7163,12 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>221067</t>
+          <t>221053</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>آيتن أحمد مصطفى محمد مصطفى</t>
+          <t>امينه خالد عوض عفيفى تاج الدين</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -7190,12 +7190,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>221068</t>
+          <t>221054</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>آيه حسن محمد مأمون</t>
+          <t>انجي علاء سعد الدين الشحات السيد</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
@@ -7217,12 +7217,12 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>221069</t>
+          <t>221055</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>بثينه خالد ابراهيم محمد موسى</t>
+          <t>ايلاري هاني سند ماضي</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -7244,12 +7244,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>221070</t>
+          <t>221056</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>بسمة علاء حسني زهران</t>
+          <t>إيريني وجدي عزمي عبدالمسيح</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -7271,12 +7271,12 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>221059</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>بسملة وسام صلاح أحمد</t>
+          <t>أحمد عزت مختار عزت</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -7298,12 +7298,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>221072</t>
+          <t>221060</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>بسنت احمد شكرالله عبدالباسط</t>
+          <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
@@ -7325,12 +7325,12 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>221073</t>
+          <t>221062</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
+          <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -7352,12 +7352,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>221075</t>
+          <t>221063</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>تسنيم اسامة يوسف نعيم</t>
+          <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
@@ -7379,12 +7379,12 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>221076</t>
+          <t>221064</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>تسنيم علاء ناجي عبدالراضي</t>
+          <t>أكرم مصطفي فتحي محمد</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -7406,12 +7406,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>221077</t>
+          <t>221066</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>تقي محمود احمد السمكري</t>
+          <t>أية عبدالسميع محمد سليمان</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
@@ -7433,12 +7433,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>221078</t>
+          <t>221067</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>توماس نبيل سامي غطاس</t>
+          <t>آيتن أحمد مصطفى محمد مصطفى</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>221079</t>
+          <t>221068</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>جنا هاني احمد عبد القادر</t>
+          <t>آيه حسن محمد مأمون</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>221080</t>
+          <t>221069</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>جنة الله علاء الدين أحمد عيد</t>
+          <t>بثينه خالد ابراهيم محمد موسى</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -7514,12 +7514,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>221084</t>
+          <t>221070</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>جودي احمد السيد سليمان</t>
+          <t>بسمة علاء حسني زهران</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -7541,12 +7541,12 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>221086</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>جونسي صلاح اسماعيل حجازي</t>
+          <t>بسملة وسام صلاح أحمد</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -7568,12 +7568,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>221087</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>جونى سامر صفوت فهمى ميخائيل</t>
+          <t>بسنت احمد شكرالله عبدالباسط</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
@@ -7595,12 +7595,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>221088</t>
+          <t>221073</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
+          <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -7622,12 +7622,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>221089</t>
+          <t>221075</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>حبيبة زكي محمد زكي</t>
+          <t>تسنيم اسامة يوسف نعيم</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
@@ -7649,12 +7649,12 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>221090</t>
+          <t>221076</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>حبيبه محمد صابر عبدالعال</t>
+          <t>تسنيم علاء ناجي عبدالراضي</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -7676,12 +7676,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>221091</t>
+          <t>221077</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>حسن احمد حسن الصفتي</t>
+          <t>تقي محمود احمد السمكري</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -7703,12 +7703,12 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>221092</t>
+          <t>221078</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>حسن محمد حسن شمس الدين</t>
+          <t>توماس نبيل سامي غطاس</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -7730,12 +7730,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>221093</t>
+          <t>221079</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>حلا احمد محمد محمد فضل الله</t>
+          <t>جنا هاني احمد عبد القادر</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
@@ -7757,12 +7757,12 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>221095</t>
+          <t>221080</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>حمزه هشام بكر ابو القميز</t>
+          <t>جنة الله علاء الدين أحمد عيد</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -7784,12 +7784,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>221096</t>
+          <t>221084</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>حنين طارق محرم شلبي</t>
+          <t>جودي احمد السيد سليمان</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -7811,12 +7811,12 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>221097</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>خالد علاء عبد السميع عبدالله الديب</t>
+          <t>جوفانا روماني راشد شنوده</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -7838,12 +7838,12 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>221099</t>
+          <t>221086</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>دارين أحمد فرج القاصد</t>
+          <t>جونسي صلاح اسماعيل حجازي</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -7865,12 +7865,12 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>221100</t>
+          <t>221087</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>دارين السيد مصيلحي مصيلحي</t>
+          <t>جونى سامر صفوت فهمى ميخائيل</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -7892,12 +7892,12 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>221101</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>دارين محمد ابراهيم ماضى</t>
+          <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -7919,12 +7919,12 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>221102</t>
+          <t>221089</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>دانا أسامة عبدالغني محمد</t>
+          <t>حبيبة زكي محمد زكي</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -7946,12 +7946,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>221103</t>
+          <t>221090</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>دانه عبداللطيف فؤاد زيان</t>
+          <t>حبيبه محمد صابر عبدالعال</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -7973,12 +7973,12 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>221104</t>
+          <t>221091</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>دعاء أشرف أحمد عبد الله</t>
+          <t>حسن احمد حسن الصفتي</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>221106</t>
+          <t>221092</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>دينا ناجي عبد المنعم الشيخ</t>
+          <t>حسن محمد حسن شمس الدين</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
@@ -8027,12 +8027,12 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>221108</t>
+          <t>221093</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>رانيا عادل طلخان رزق</t>
+          <t>حلا احمد محمد محمد فضل الله</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -8054,12 +8054,12 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>221110</t>
+          <t>221095</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>رفيده أيمن مصطفى النحاس شحاته</t>
+          <t>حمزه هشام بكر ابو القميز</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
@@ -8081,12 +8081,12 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>221111</t>
+          <t>221096</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>رنا عمرو محمد شرايحي</t>
+          <t>حنين طارق محرم شلبي</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>221112</t>
+          <t>221097</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>رنيم ايمن علي علام</t>
+          <t>خالد علاء عبد السميع عبدالله الديب</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
@@ -8135,12 +8135,12 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>221114</t>
+          <t>221099</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>روان محمد ياسر عبد العال ابو الوفا</t>
+          <t>دارين أحمد فرج القاصد</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -8162,12 +8162,12 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>221100</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>روينا محمد عبدالحكيم الاشموني</t>
+          <t>دارين السيد مصيلحي مصيلحي</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
@@ -8189,12 +8189,12 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>221117</t>
+          <t>221101</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>رؤى طارق مرسى محمود</t>
+          <t>دارين محمد ابراهيم ماضى</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -8216,12 +8216,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>221118</t>
+          <t>221102</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>ريم السيد صالح خليل</t>
+          <t>دانا أسامة عبدالغني محمد</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
@@ -8243,12 +8243,12 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>221119</t>
+          <t>221103</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>زياد شريف حلمي الألفي</t>
+          <t>دانه عبداللطيف فؤاد زيان</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -8270,12 +8270,12 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>221120</t>
+          <t>221104</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>سارة علاءالدين احمد محمد</t>
+          <t>دعاء أشرف أحمد عبد الله</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
@@ -8297,12 +8297,12 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>221121</t>
+          <t>221106</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>سارة احمد محمد على خليل</t>
+          <t>دينا ناجي عبد المنعم الشيخ</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -8324,12 +8324,12 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>221123</t>
+          <t>221108</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>ساره عاطف محمد الصادق</t>
+          <t>رانيا عادل طلخان رزق</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
@@ -8351,12 +8351,12 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>221124</t>
+          <t>221110</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>ساره نسيم فرج بكر</t>
+          <t>رفيده أيمن مصطفى النحاس شحاته</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
@@ -8378,12 +8378,12 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>221125</t>
+          <t>221111</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>ساره طارق زكريا حامد</t>
+          <t>رنا عمرو محمد شرايحي</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -8405,12 +8405,12 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>221126</t>
+          <t>221112</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>سامى السيد لبيب قاسم</t>
+          <t>رنيم ايمن علي علام</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -8432,12 +8432,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>221127</t>
+          <t>221114</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>ساندرا سامي عبدالملاك ملوكه</t>
+          <t>روان محمد ياسر عبد العال ابو الوفا</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
@@ -8459,12 +8459,12 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>221128</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>سلمى السيد أحمد فتيح</t>
+          <t>روينا محمد عبدالحكيم الاشموني</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
@@ -8486,12 +8486,12 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>221129</t>
+          <t>221117</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>سلمى ايمن سعيد محمد</t>
+          <t>رؤى طارق مرسى محمود</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -8513,12 +8513,12 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>221130</t>
+          <t>221118</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>سلمي احمد رمضان مخيمر</t>
+          <t>ريم السيد صالح خليل</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
@@ -8540,12 +8540,12 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>221131</t>
+          <t>221119</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>سلمي احمد موسي احمد الصحصاح</t>
+          <t>زياد شريف حلمي الألفي</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
@@ -8567,12 +8567,12 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>221132</t>
+          <t>221120</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>سلمي محمد السيد حسين</t>
+          <t>سارة علاءالدين احمد محمد</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -8594,12 +8594,12 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>221133</t>
+          <t>221121</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>سما حسام الدين عبدالفتاح محمود ناصف</t>
+          <t>سارة احمد محمد على خليل</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
@@ -8621,12 +8621,12 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>221134</t>
+          <t>221122</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>سما سامح سعد الشريفي</t>
+          <t>سارة أشرف السيد عباسي</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -8648,12 +8648,12 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>221136</t>
+          <t>221123</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>سما محمد عبد السلام الرافعي</t>
+          <t>ساره عاطف محمد الصادق</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
@@ -8675,12 +8675,12 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>221137</t>
+          <t>221124</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>سما ممدوح حسن عطيه ممدوح حسن عطيه حسن عطيه القاضي عطيه القاضي</t>
+          <t>ساره نسيم فرج بكر</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
@@ -8702,12 +8702,12 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>221138</t>
+          <t>221125</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>سماء اكرامي محمود عبد السميع</t>
+          <t>ساره طارق زكريا حامد</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
@@ -8729,12 +8729,12 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>221139</t>
+          <t>221126</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>سماح محمد ابراهيم يوسف</t>
+          <t>سامى السيد لبيب قاسم</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr">
@@ -8756,12 +8756,12 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>221140</t>
+          <t>221127</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>سندس رفعت السيد بسيوني علي</t>
+          <t>ساندرا سامي عبدالملاك ملوكه</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
@@ -8783,12 +8783,12 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>221141</t>
+          <t>221128</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>سيف الدين اشرف صالح سليمان</t>
+          <t>سلمى السيد أحمد فتيح</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -8810,12 +8810,12 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>221144</t>
+          <t>221129</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>شاهي أحمد محمد عز الدين ابراهيم مهران</t>
+          <t>سلمى ايمن سعيد محمد</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
@@ -8837,12 +8837,12 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>221145</t>
+          <t>221130</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>شروق أحمد عبد الرؤف عبد العال</t>
+          <t>سلمي احمد رمضان مخيمر</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
@@ -8864,12 +8864,12 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>221146</t>
+          <t>221131</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>شريف أحمد محمد صديق الخولي</t>
+          <t>سلمي احمد موسي احمد الصحصاح</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
@@ -8891,12 +8891,12 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>221147</t>
+          <t>221132</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>شهد انصاري عبدالرؤوف الانصاري</t>
+          <t>سلمي محمد السيد حسين</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -8918,12 +8918,12 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>221148</t>
+          <t>221133</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>شهد محمد عطيه الشبراوى</t>
+          <t>سما حسام الدين عبدالفتاح محمود ناصف</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
@@ -8945,12 +8945,12 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>221149</t>
+          <t>221134</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>شيري أشرف نصيف ميخائيل</t>
+          <t>سما سامح سعد الشريفي</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -8972,12 +8972,12 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>221150</t>
+          <t>221136</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>شيماء يسري سعد بدري</t>
+          <t>سما محمد عبد السلام الرافعي</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
@@ -8999,12 +8999,12 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>221151</t>
+          <t>221137</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>عبد الرحمن علاء فهمى سرج</t>
+          <t>سما ممدوح حسن عطيه ممدوح حسن عطيه حسن عطيه القاضي عطيه القاضي</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -9026,12 +9026,12 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>221152</t>
+          <t>221138</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>عبد الرحمن ايمن حسنى محمد عبد الرحمن</t>
+          <t>سماء اكرامي محمود عبد السميع</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
@@ -9053,12 +9053,12 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>221153</t>
+          <t>221139</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>عبد العزيز عصام عبد التواب فرج</t>
+          <t>سماح محمد ابراهيم يوسف</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -9080,12 +9080,12 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>221154</t>
+          <t>221140</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>عبدالرحمن احمد سعد محمد عبدالخالق</t>
+          <t>سندس رفعت السيد بسيوني علي</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -9107,12 +9107,12 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>221158</t>
+          <t>221141</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>عبدالله حسن محمد السعيد عزازي</t>
+          <t>سيف الدين اشرف صالح سليمان</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -9134,12 +9134,12 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>221159</t>
+          <t>221144</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>عبدالله محمد مصطفى علي</t>
+          <t>شاهي أحمد محمد عز الدين ابراهيم مهران</t>
         </is>
       </c>
       <c r="C322" s="3" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
@@ -9161,12 +9161,12 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>221160</t>
+          <t>221145</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>عزت حسام عبدالله عبدالعزيز</t>
+          <t>شروق أحمد عبد الرؤف عبد العال</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -9188,12 +9188,12 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>221161</t>
+          <t>221146</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>علاء هشام حسين ابوعلوان</t>
+          <t>شريف أحمد محمد صديق الخولي</t>
         </is>
       </c>
       <c r="C324" s="3" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -9215,12 +9215,12 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>221162</t>
+          <t>221147</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>علي أحمد حامد أمين</t>
+          <t>شهد انصاري عبدالرؤوف الانصاري</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -9242,12 +9242,12 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>221163</t>
+          <t>221148</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>عمار ياسر رشدي رجب</t>
+          <t>شهد محمد عطيه الشبراوى</t>
         </is>
       </c>
       <c r="C326" s="3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -9269,12 +9269,12 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>221164</t>
+          <t>221149</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>عمر جمعة عبدالكريم محمد</t>
+          <t>شيري أشرف نصيف ميخائيل</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -9296,12 +9296,12 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>221165</t>
+          <t>221150</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>عمر حمدي محمد طه</t>
+          <t>شيماء يسري سعد بدري</t>
         </is>
       </c>
       <c r="C328" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
@@ -9323,12 +9323,12 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>221166</t>
+          <t>221151</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>عمر عبد العزيز ابراهيم امين ابراهيم</t>
+          <t>عبد الرحمن علاء فهمى سرج</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -9350,12 +9350,12 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>221167</t>
+          <t>221152</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>عمر عبدالعال غريب عبدالعال</t>
+          <t>عبد الرحمن ايمن حسنى محمد عبد الرحمن</t>
         </is>
       </c>
       <c r="C330" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
@@ -9377,12 +9377,12 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>221168</t>
+          <t>221153</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>عمر محمد احمد احمد السيد فايد</t>
+          <t>عبد العزيز عصام عبد التواب فرج</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -9404,12 +9404,12 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>221169</t>
+          <t>221154</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>اروى ابراهيم احمد تهامى</t>
+          <t>عبدالرحمن احمد سعد محمد عبدالخالق</t>
         </is>
       </c>
       <c r="C332" s="3" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
@@ -9431,12 +9431,12 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>221170</t>
+          <t>221157</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>فادى عمرو فاروق العراقى</t>
+          <t>عبدالرحمن محمد عمر عيد</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>221174</t>
+          <t>221158</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>فريدة خالد ابوالفتوح احمد</t>
+          <t>عبدالله حسن محمد السعيد عزازي</t>
         </is>
       </c>
       <c r="C334" s="3" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
@@ -9485,12 +9485,12 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>221179</t>
+          <t>221159</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>لجين عمرو عبدالرازق محمد الطاهر</t>
+          <t>عبدالله محمد مصطفى علي</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -9512,12 +9512,12 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>221181</t>
+          <t>221160</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>لوجين محمد صبري محمد سعد القاضي</t>
+          <t>عزت حسام عبدالله عبدالعزيز</t>
         </is>
       </c>
       <c r="C336" s="3" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
@@ -9539,12 +9539,12 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>221202</t>
+          <t>221161</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>مرهان محمد عوض الديب</t>
+          <t>علاء هشام حسين ابوعلوان</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -9566,12 +9566,12 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>221206</t>
+          <t>221162</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>مريم هشام طلعت حسين</t>
+          <t>علي أحمد حامد أمين</t>
         </is>
       </c>
       <c r="C338" s="3" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
@@ -9593,12 +9593,12 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>221211</t>
+          <t>221163</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>ملك مصطفي ابراهيم ابراهيم</t>
+          <t>عمار ياسر رشدي رجب</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr">
@@ -9620,12 +9620,12 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>221214</t>
+          <t>221164</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>مها محمد سلامة عامر</t>
+          <t>عمر جمعة عبدالكريم محمد</t>
         </is>
       </c>
       <c r="C340" s="3" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
@@ -9647,12 +9647,12 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>221217</t>
+          <t>221165</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>ميرا اشرف بساده سعيد</t>
+          <t>عمر حمدي محمد طه</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
@@ -9674,12 +9674,12 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>221224</t>
+          <t>221166</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>نور عمرو محمد احمد حسن</t>
+          <t>عمر عبد العزيز ابراهيم امين ابراهيم</t>
         </is>
       </c>
       <c r="C342" s="3" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
@@ -9701,12 +9701,12 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>221228</t>
+          <t>221167</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>نوران ممدوح سيد بهجت</t>
+          <t>عمر عبدالعال غريب عبدالعال</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr">
@@ -9728,12 +9728,12 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>221234</t>
+          <t>221168</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>يارا هانى عبد الرحمن علام</t>
+          <t>عمر محمد احمد احمد السيد فايد</t>
         </is>
       </c>
       <c r="C344" s="3" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
@@ -9755,12 +9755,12 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>221237</t>
+          <t>221169</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>يمني تحسين عبدالمحيد سيداحمد</t>
+          <t>اروى ابراهيم احمد تهامى</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr">
@@ -9782,12 +9782,12 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>221335</t>
+          <t>221170</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>حذيفه طريف القطرنجى</t>
+          <t>فادى عمرو فاروق العراقى</t>
         </is>
       </c>
       <c r="C346" s="3" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
@@ -9809,12 +9809,12 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>221541</t>
+          <t>221174</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>ساره محمد محمود مالك</t>
+          <t>فريدة خالد ابوالفتوح احمد</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr">
@@ -9836,12 +9836,12 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>221625</t>
+          <t>221179</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>حلا طارق حسين احمد</t>
+          <t>لجين عمرو عبدالرازق محمد الطاهر</t>
         </is>
       </c>
       <c r="C348" s="3" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
@@ -9863,12 +9863,12 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>220890</t>
+          <t>221181</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>يوسف حسين ناجي الصرايره</t>
+          <t>لوجين محمد صبري محمد سعد القاضي</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr">
@@ -9890,12 +9890,12 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>180289</t>
+          <t>221202</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>عبد الرحمن سلامة حنفى</t>
+          <t>مرهان محمد عوض الديب</t>
         </is>
       </c>
       <c r="C350" s="3" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
@@ -9917,12 +9917,12 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>220647</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>لوجين السيد محروس اسماعيل</t>
+          <t>مريم هشام طلعت حسين</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr">
@@ -9944,12 +9944,12 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>220698</t>
+          <t>221211</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>محمد محمد احمد الفتيانى</t>
+          <t>ملك مصطفي ابراهيم ابراهيم</t>
         </is>
       </c>
       <c r="C352" s="3" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
@@ -9971,12 +9971,12 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>220736</t>
+          <t>221214</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد عطيه عبد السلام</t>
+          <t>مها محمد سلامة عامر</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr">
@@ -9998,12 +9998,12 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>220779</t>
+          <t>221217</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>نزار عمرو حسن عبد الغنى</t>
+          <t>ميرا اشرف بساده سعيد</t>
         </is>
       </c>
       <c r="C354" s="3" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
@@ -10025,12 +10025,12 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>220815</t>
+          <t>221224</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>يوسف حمدى احمد طاجن</t>
+          <t>نور عمرو محمد احمد حسن</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -10052,12 +10052,12 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>221228</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>نهال حسام زهره</t>
+          <t>نوران ممدوح سيد بهجت</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>A2-D2</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
@@ -10079,12 +10079,12 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>221047</t>
+          <t>221234</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>احمد محسن محمد ماهر ابو هاشم</t>
+          <t>يارا هانى عبد الرحمن علام</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>A2-E1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -10106,12 +10106,12 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>221237</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>جوفانا روماني راشد شنوده</t>
+          <t>يمني تحسين عبدالمحيد سيداحمد</t>
         </is>
       </c>
       <c r="C358" s="3" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>A2-E2</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
@@ -10133,12 +10133,12 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>221122</t>
+          <t>221335</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>سارة أشرف السيد عباسي</t>
+          <t>حذيفه طريف القطرنجى</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>A2-F1</t>
+          <t>A2-F2</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -10160,12 +10160,12 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>221157</t>
+          <t>221541</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد عمر عيد</t>
+          <t>ساره محمد محمود مالك</t>
         </is>
       </c>
       <c r="C360" s="3" t="inlineStr">
@@ -10179,6 +10179,33 @@
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
+        <is>
+          <t>A2.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="inlineStr">
+        <is>
+          <t>221625</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>حلا طارق حسين احمد</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>A2-F2</t>
+        </is>
+      </c>
+      <c r="E361" s="4" t="inlineStr">
         <is>
           <t>A2.xlsx</t>
         </is>

--- a/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
+++ b/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
@@ -461,7 +461,7 @@
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,12 +494,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>220890</t>
+          <t>180289</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>يوسف حسين ناجي الصرايره</t>
+          <t>عبد الرحمن سلامة حنفى</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>220896</t>
+          <t>200302</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>احمد السر ميرغني عمر</t>
+          <t>ساره هانى منصور سيد رزق</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -536,24 +536,24 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>220900</t>
+          <t>200502</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ديما حسن نصر الله الزاملي</t>
+          <t>مازن ايمن محمود عبدربه</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -563,24 +563,24 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>220902</t>
+          <t>200891</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>كاتيا منيمنة</t>
+          <t>احمد جمال القبانى</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -590,24 +590,24 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>220908</t>
+          <t>211139</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>عمرو زين العابدين طلعت عابدين</t>
+          <t>احمد يعقوب عمر طرايره</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>220909</t>
+          <t>211513</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>احمد جمال محمد عليمى محمد</t>
+          <t>ايه محمد سعد الدين العدوى</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -644,24 +644,24 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>220912</t>
+          <t>211701</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>شيماء بدر زبير علي</t>
+          <t>فادى عبدالله جميل شورى</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>220914</t>
+          <t>220321</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>محمد بن ضيف الله بن رزق الصبحى</t>
+          <t>احمد عبد الرحمن جابر سالمان</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>220919</t>
+          <t>220392</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>احمد سليم عيسى ابو لاوى</t>
+          <t>انس محمد محمد صوابى هيكل</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -725,24 +725,24 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>220452</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>دارين محمد طاهر</t>
+          <t>حبيبه شريف احمد عبدالعليم عبدالحميد</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>220925</t>
+          <t>220494</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>دينا زياد ابراهيم زقماط</t>
+          <t>رودينا تامر محمد الدهان</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>220927</t>
+          <t>220501</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>سعيد احمد سعيد محمد عبدالسيد</t>
+          <t>ريماس سامر العطائي</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>220928</t>
+          <t>220516</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ابراهيم عبدالفتاح ابراهيم السروري</t>
+          <t>سلمى حسين عبد المنعم عبد الحميد محمد</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>220929</t>
+          <t>220537</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>الوليد بن عبدالله بن محمد عامر</t>
+          <t>شروق هانى مبروك على السيد النجار</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>220930</t>
+          <t>220550</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>يوسف نبيل فريد شاهين</t>
+          <t>شيماء شريف محمد عبد الرحمن احمد</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>220937</t>
+          <t>220577</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>اسيل يحيى محمد المزايده</t>
+          <t>عبدالرحمن محمد عبداللطيف شهاب</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>220940</t>
+          <t>220615</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد محسن الزقري</t>
+          <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>220942</t>
+          <t>220616</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>عدي علي فلاح الحديد</t>
+          <t>غاده احمد احمد احمد الشريف</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>220947</t>
+          <t>220623</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>مهند عبد الفتاح سلام مقبل</t>
+          <t>فاطمه احمد محمد محمود كرم</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>220950</t>
+          <t>220624</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>يوسف اسماعيل ابراهيم احمد</t>
+          <t>فاطمه السيد محمد فتحى عطيه الله</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>220951</t>
+          <t>220625</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>محمد تيسير محمد ياسين</t>
+          <t>فاطمه حموده على عبد الحميد حموده</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>220954</t>
+          <t>220627</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>طيف فرج علي العماري</t>
+          <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>220955</t>
+          <t>220628</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>غاده عبدالاله عبدالكريم عبدالله</t>
+          <t>فاطمه محمود محمد امام</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>220956</t>
+          <t>220629</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>نور الحسين أسعد جاسم العكيلي</t>
+          <t>فتحى محمد فتحى السيد عبد الله</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>220958</t>
+          <t>220630</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>محمد حميد حمود علي الديلي</t>
+          <t>فريده محمود فؤاد محمود</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>220635</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ايليا سالم يعقوب المدانات</t>
+          <t>كريم ايمن محمد مصطفى ابراهيم</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>220961</t>
+          <t>220636</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>رهف نزار احمد الامام</t>
+          <t>كريم سعيد احمد ابراهيم الحريزى</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>220963</t>
+          <t>220639</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>شهد بنت عبدالله بن حسين ال الصومعي</t>
+          <t>كريم مصطفى عبد الرحمن على سعد</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>220964</t>
+          <t>220645</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ميس غسان مرشد مفارجة</t>
+          <t>لجين احمد عبد الله البسطويسى</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>220966</t>
+          <t>220646</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
+          <t>لجين اشرف جلال عبد الرحمن السمرى</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A1-D1</t>
+          <t>A2-A1</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>180289</t>
+          <t>220647</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>عبد الرحمن سلامة حنفى</t>
+          <t>لوجين السيد محروس اسماعيل</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>200302</t>
+          <t>220648</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ساره هانى منصور سيد رزق</t>
+          <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>200502</t>
+          <t>220649</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>مازن ايمن محمود عبدربه</t>
+          <t>لؤى على حسين حسن ابو صفيه</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>200891</t>
+          <t>220651</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>احمد جمال القبانى</t>
+          <t>ليلى اشرف وصفى</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>211139</t>
+          <t>220653</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>احمد يعقوب عمر طرايره</t>
+          <t>ماجد حسنى السيد التلاوى</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>211513</t>
+          <t>220655</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ايه محمد سعد الدين العدوى</t>
+          <t>مارى مجدى منير عبده</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>211701</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>فادى عبدالله جميل شورى</t>
+          <t>مالك محمود على محمود زين الدين</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>220321</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>احمد عبد الرحمن جابر سالمان</t>
+          <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>220392</t>
+          <t>220662</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>انس محمد محمد صوابى هيكل</t>
+          <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>220449</t>
+          <t>220666</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>حبيبة الله وائل البرماوى</t>
+          <t>محمد احمد فتحى احمد احمد</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>220452</t>
+          <t>220667</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>حبيبه شريف احمد عبدالعليم عبدالحميد</t>
+          <t>محمد اسامه علاء الدين اللو</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>220494</t>
+          <t>220669</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>رودينا تامر محمد الدهان</t>
+          <t>محمد السعيد السعيد محمد شعبان</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>220501</t>
+          <t>220670</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ريماس سامر العطائي</t>
+          <t>محمد السعيد مسعد مصطفى حراز</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>220516</t>
+          <t>220672</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>سلمى حسين عبد المنعم عبد الحميد محمد</t>
+          <t>محمد الشحات على احمد سرور</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>220537</t>
+          <t>220673</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>شروق هانى مبروك على السيد النجار</t>
+          <t>محمد أيمن محمد أحمد ناصف</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>220550</t>
+          <t>220674</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>شيماء شريف محمد عبد الرحمن احمد</t>
+          <t>محمد باسم عبد الكريم محمود</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>220577</t>
+          <t>220678</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد عبداللطيف شهاب</t>
+          <t>محمد بهاء عبد الحميد عبد الغفار</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1751,24 +1751,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>220679</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
+          <t>محمد جابر توفيق الشافعى</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>220616</t>
+          <t>220680</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>غاده احمد احمد احمد الشريف</t>
+          <t>محمد حسن جلال عبد المجيد وهدان</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>220623</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>فاطمه احمد محمد محمود كرم</t>
+          <t>محمد سعيد محمود عبد المنعم محمود</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>220624</t>
+          <t>220684</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>فاطمه السيد محمد فتحى عطيه الله</t>
+          <t>محمد صبرى جوده عبد الله خضر</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>220625</t>
+          <t>220685</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>فاطمه حموده على عبد الحميد حموده</t>
+          <t>محمد صلاح حسن عبد الله حسن</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>220627</t>
+          <t>220686</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
+          <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>220628</t>
+          <t>220687</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>فاطمه محمود محمد امام</t>
+          <t>محمد طارق محمد عبد الرحمن العرينى</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>220629</t>
+          <t>220688</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>فتحى محمد فتحى السيد عبد الله</t>
+          <t>محمد عبد الحفيظ عبد الله محمد على</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>220630</t>
+          <t>220689</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>فريده محمود فؤاد محمود</t>
+          <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>220635</t>
+          <t>220690</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>كريم ايمن محمد مصطفى ابراهيم</t>
+          <t>محمد عبد النبى عطيه ابو شعيشع</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>220636</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>كريم سعيد احمد ابراهيم الحريزى</t>
+          <t>محمد عبدالهادى عبدالمنعم عمر</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>220639</t>
+          <t>220693</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>كريم مصطفى عبد الرحمن على سعد</t>
+          <t>محمد علاء محمد عبد العزيز عبد الله</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>220645</t>
+          <t>220694</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>لجين احمد عبد الله البسطويسى</t>
+          <t>محمد على محمد احمد محمد</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>220646</t>
+          <t>220698</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>لجين اشرف جلال عبد الرحمن السمرى</t>
+          <t>محمد محمد احمد الفتيانى</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>220647</t>
+          <t>220700</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>لوجين السيد محروس اسماعيل</t>
+          <t>محمد محمد عبد الله التهامي</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>220701</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
+          <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>220649</t>
+          <t>220702</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>لؤى على حسين حسن ابو صفيه</t>
+          <t>محمد محيى الدين محمد سيد مكاوى</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>220651</t>
+          <t>220703</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ليلى اشرف وصفى</t>
+          <t>محمد مختار شعبان هلالى سليمان</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>220653</t>
+          <t>220705</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ماجد حسنى السيد التلاوى</t>
+          <t>محمد مفرح عبد الباسط عبد الحليم</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>220655</t>
+          <t>220706</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>مارى مجدى منير عبده</t>
+          <t>محمد وائل محمد العيسوى</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>220659</t>
+          <t>220707</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>مالك محمود على محمود زين الدين</t>
+          <t>محمد وحيد محمد رزق</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>220708</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
+          <t>محمد ياسر الشافعى محمد على</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>220662</t>
+          <t>220709</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
+          <t>محمد ياسر حامد دياب حمد</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>220666</t>
+          <t>220710</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>محمد احمد فتحى احمد احمد</t>
+          <t>محمود جمال حسين محمد رسلان</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>220667</t>
+          <t>220711</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>محمد اسامه علاء الدين اللو</t>
+          <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>220669</t>
+          <t>220712</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>محمد السعيد السعيد محمد شعبان</t>
+          <t>محمود حسن عبد النبى حسين</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>220670</t>
+          <t>220714</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>محمد السعيد مسعد مصطفى حراز</t>
+          <t>محمود كريم شحاته حسن كرد</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>220672</t>
+          <t>220717</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>محمد الشحات على احمد سرور</t>
+          <t>محمود منصور محمود محمد السيد يعقوب</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>220673</t>
+          <t>220720</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>محمد أيمن محمد أحمد ناصف</t>
+          <t>مروان صبحى ابو الحسن محمد على</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2534,24 +2534,24 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>220674</t>
+          <t>220721</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>محمد باسم عبد الكريم محمود</t>
+          <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>220678</t>
+          <t>220722</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>محمد بهاء عبد الحميد عبد الغفار</t>
+          <t>مروه عبد الحميد على حسن ايوب</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>220679</t>
+          <t>220723</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>محمد جابر توفيق الشافعى</t>
+          <t>مريم ابراهيم احمد ابراهيم مبارك</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>220680</t>
+          <t>220724</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>محمد حسن جلال عبد المجيد وهدان</t>
+          <t>مريم الحسن احمد ابراهيم بيومى</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>220683</t>
+          <t>220725</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>محمد سعيد محمود عبد المنعم محمود</t>
+          <t>مريم ايمن عبد الله محمود فخرى</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>220684</t>
+          <t>220726</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>محمد صبرى جوده عبد الله خضر</t>
+          <t>مريم ايمن فؤاد عبدالستار</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>220685</t>
+          <t>220727</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>محمد صلاح حسن عبد الله حسن</t>
+          <t>مريم ايهاب ملاك ثابت</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>220686</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
+          <t>مريم رضا محمد ابراهيم صبره</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>220687</t>
+          <t>220730</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>محمد طارق محمد عبد الرحمن العرينى</t>
+          <t>مريم شعبان مصباح خليفه</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>220688</t>
+          <t>220731</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>محمد عبد الحفيظ عبد الله محمد على</t>
+          <t>مريم شفيق صبحى شفيق حنا</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>220689</t>
+          <t>220732</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
+          <t>مريم عمرو يحيى عبده مدنى</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>220690</t>
+          <t>220733</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>محمد عبد النبى عطيه ابو شعيشع</t>
+          <t>مريم محمد احمد فاروق الديب الشريف</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>220691</t>
+          <t>220734</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>محمد عبدالهادى عبدالمنعم عمر</t>
+          <t>مريم محمد احمد محمد عبد المنعم</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>220693</t>
+          <t>220735</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>محمد علاء محمد عبد العزيز عبد الله</t>
+          <t>مريم محمد ثروت صايم مصطفى</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>220694</t>
+          <t>221051</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>محمد على محمد احمد محمد</t>
+          <t>اسراء هشام محمد عبد المنعم</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>220698</t>
+          <t>220736</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>محمد محمد احمد الفتيانى</t>
+          <t>مريم محمد عطيه عبد السلام</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>220737</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>محمد محمد عبد الله التهامي</t>
+          <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>220701</t>
+          <t>220740</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
+          <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>220702</t>
+          <t>220742</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>محمد محيى الدين محمد سيد مكاوى</t>
+          <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>220703</t>
+          <t>220744</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>محمد مختار شعبان هلالى سليمان</t>
+          <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>220705</t>
+          <t>220745</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>محمد مفرح عبد الباسط عبد الحليم</t>
+          <t>مصطفى محمود مصطفى محمود</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3101,24 +3101,24 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>220706</t>
+          <t>220746</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>محمد وائل محمد العيسوى</t>
+          <t>معاذ طاهر محمد شبانه على</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3128,24 +3128,24 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>220707</t>
+          <t>220747</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>محمد وحيد محمد رزق</t>
+          <t>ملك عبدالغنى احمد حسن</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>220708</t>
+          <t>220749</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>محمد ياسر الشافعى محمد على</t>
+          <t>ملك ياسر عبد الوهاب محمد الغندور</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3182,24 +3182,24 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>220709</t>
+          <t>220751</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>محمد ياسر حامد دياب حمد</t>
+          <t>منة الله هانى عبد السميع شكرى</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>220710</t>
+          <t>220752</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>محمود جمال حسين محمد رسلان</t>
+          <t>منصور هانى منصور عبدالله</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>220711</t>
+          <t>220753</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
+          <t>منه الله احمد محمد جمعه عثمان</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>220712</t>
+          <t>220754</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>محمود حسن عبد النبى حسين</t>
+          <t>منه الله محمد صالح محمد النور</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -3290,24 +3290,24 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>220714</t>
+          <t>220755</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>محمود كريم شحاته حسن كرد</t>
+          <t>منه الله محمد عبد الرازق سالم غاليه</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -3317,24 +3317,24 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>220717</t>
+          <t>220756</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>محمود منصور محمود محمد السيد يعقوب</t>
+          <t>منه عبد الوهاب عبدالله مصطفى</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -3344,24 +3344,24 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>220720</t>
+          <t>220758</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>مروان صبحى ابو الحسن محمد على</t>
+          <t>منه محمود محمد احمد</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3371,24 +3371,24 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>220759</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
+          <t>منى عبد الحميد ناصف سيف</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>220722</t>
+          <t>220760</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>مروه عبد الحميد على حسن ايوب</t>
+          <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3425,24 +3425,24 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>220723</t>
+          <t>220764</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>مريم ابراهيم احمد ابراهيم مبارك</t>
+          <t>مياده سلامه قاسم محمد السيد</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -3452,24 +3452,24 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>220724</t>
+          <t>220765</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>مريم الحسن احمد ابراهيم بيومى</t>
+          <t>ميار احمد صبحى السيد السيد</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -3479,24 +3479,24 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>220725</t>
+          <t>220767</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>مريم ايمن عبد الله محمود فخرى</t>
+          <t>ميار صلاح محمد سليمان سليمان</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>220726</t>
+          <t>220772</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>مريم ايمن فؤاد عبدالستار</t>
+          <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>220727</t>
+          <t>220773</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>مريم ايهاب ملاك ثابت</t>
+          <t>ندى اشرف عبد الله ابراهيم</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -3560,24 +3560,24 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>220729</t>
+          <t>220774</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>مريم رضا محمد ابراهيم صبره</t>
+          <t>ندى اشرف محمد محمد</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -3587,24 +3587,24 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>220730</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>مريم شعبان مصباح خليفه</t>
+          <t>ندى حسن السيد احمد عطا الله</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>220731</t>
+          <t>220776</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>مريم شفيق صبحى شفيق حنا</t>
+          <t>ندى عاطف محمد محمد عبده الشيمى</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3641,24 +3641,24 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>220732</t>
+          <t>220777</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>مريم عمرو يحيى عبده مدنى</t>
+          <t>ندى على زيد عبد الرحمن</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>220733</t>
+          <t>220778</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد احمد فاروق الديب الشريف</t>
+          <t>ندى محمد احمد حامد عامر</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -3695,24 +3695,24 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>220734</t>
+          <t>220779</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد احمد محمد عبد المنعم</t>
+          <t>نزار عمرو حسن عبد الغنى</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>220735</t>
+          <t>220780</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد ثروت صايم مصطفى</t>
+          <t>نصر الدين الابراهيم</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -3749,24 +3749,24 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>220736</t>
+          <t>220781</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد عطيه عبد السلام</t>
+          <t>نظمى مصطفى نظمى على عبد النبى</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3776,24 +3776,24 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>220737</t>
+          <t>220782</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
+          <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -3803,24 +3803,24 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>220740</t>
+          <t>220783</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
+          <t>نهى احمد ابراهيم محمد عيطه</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3830,24 +3830,24 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>220742</t>
+          <t>220784</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
+          <t>نهى على عبد الرحمن على</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -3857,24 +3857,24 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>220744</t>
+          <t>220787</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
+          <t>نور محمد عبد الجليل محمد</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3884,24 +3884,24 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>220745</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>مصطفى محمود مصطفى محمود</t>
+          <t>نوران اسامه محمد محمود</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -3911,24 +3911,24 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>220746</t>
+          <t>220789</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>معاذ طاهر محمد شبانه على</t>
+          <t>نوران فوزى شعبان فوزى علام</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3938,24 +3938,24 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>220747</t>
+          <t>220790</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ملك عبدالغنى احمد حسن</t>
+          <t>نورهان حسن عبد الرحمن حسن محمد</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>220748</t>
+          <t>220791</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>ملك عمرو على حسن</t>
+          <t>نورهان محمد عبد العزيز حسن</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3992,24 +3992,24 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>220749</t>
+          <t>220792</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ملك ياسر عبد الوهاب محمد الغندور</t>
+          <t>نورهان محمود السيد محمود اللقانى</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>220751</t>
+          <t>220793</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>منة الله هانى عبد السميع شكرى</t>
+          <t>نورين احمد عبد الحكيم رضوان</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>220752</t>
+          <t>220794</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>منصور هانى منصور عبدالله</t>
+          <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>220753</t>
+          <t>220795</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>منه الله احمد محمد جمعه عثمان</t>
+          <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -4100,24 +4100,24 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>220754</t>
+          <t>220796</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>منه الله محمد صالح محمد النور</t>
+          <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -4127,24 +4127,24 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>220755</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>منه الله محمد عبد الرازق سالم غاليه</t>
+          <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -4154,24 +4154,24 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>220756</t>
+          <t>220799</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>منه عبد الوهاب عبدالله مصطفى</t>
+          <t>هاجر احمد رمضان سعد الفرحاتى</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4181,24 +4181,24 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>220758</t>
+          <t>220800</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>منه محمود محمد احمد</t>
+          <t>هاجر عاطف سيد عبد الجيد احمد</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -4208,24 +4208,24 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>220759</t>
+          <t>220801</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>منى عبد الحميد ناصف سيف</t>
+          <t>هايدى محمد حسين رفاعى فراج</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>220760</t>
+          <t>220802</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
+          <t>هدى مدحت خيرى احمد فرج</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>220762</t>
+          <t>220803</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>مؤيد وليد علي كرجه</t>
+          <t>هرمينا عبد الله جاد جرجس</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -4289,24 +4289,24 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>220764</t>
+          <t>220804</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>مياده سلامه قاسم محمد السيد</t>
+          <t>هنا خليل عبد الرؤف محمد سعيد</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>220765</t>
+          <t>220805</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ميار احمد صبحى السيد السيد</t>
+          <t>وسام ايمن على الشريف</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -4343,24 +4343,24 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>220767</t>
+          <t>220807</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>ميار صلاح محمد سليمان سليمان</t>
+          <t>وليد ياسر عبد الشافى محمود</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -4370,24 +4370,24 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>220772</t>
+          <t>220808</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
+          <t>ياسمين عادل السيد الفرغلى حسن</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -4397,24 +4397,24 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>220773</t>
+          <t>220809</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>ندى اشرف عبد الله ابراهيم</t>
+          <t>يحيى احمد محمد عبد الفتاح الزيات</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -4424,24 +4424,24 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>220774</t>
+          <t>220810</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ندى اشرف محمد محمد</t>
+          <t>يحيى محمد يحى على</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>220813</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>ندى حسن السيد احمد عطا الله</t>
+          <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>220776</t>
+          <t>220814</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ندى عاطف محمد محمد عبده الشيمى</t>
+          <t>يوسف جلال محمد عبد الفتاح صالح</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -4505,24 +4505,24 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>220777</t>
+          <t>220890</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>ندى على زيد عبد الرحمن</t>
+          <t>يوسف حسين ناجي الصرايره</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -4532,24 +4532,24 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>220778</t>
+          <t>220815</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ندى محمد احمد حامد عامر</t>
+          <t>يوسف حمدى احمد طاجن</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -4559,24 +4559,24 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>220779</t>
+          <t>220816</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>نزار عمرو حسن عبد الغنى</t>
+          <t>يوسف عمرو على حفنى ابراهيم</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -4586,24 +4586,24 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>220780</t>
+          <t>220817</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>نصر الدين الابراهيم</t>
+          <t>يوسف فهيم عبد الحميد ابو عزيز</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -4613,24 +4613,24 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>220781</t>
+          <t>220818</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>نظمى مصطفى نظمى على عبد النبى</t>
+          <t>يوسف محمد رضا جلال احمد سيد احمد</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -4640,24 +4640,24 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>220782</t>
+          <t>220819</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
+          <t>يوسف محمد محمد السيد البطه</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -4667,24 +4667,24 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>220783</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>نهى احمد ابراهيم محمد عيطه</t>
+          <t>يوسف محمود محمد ابراهيم</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>220821</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>نهى على عبد الرحمن على</t>
+          <t>يوسف مصطفى محمد رسلان</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>220787</t>
+          <t>220822</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>نور محمد عبد الجليل محمد</t>
+          <t>يوسف مصطفى مصطفى محمد</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4748,24 +4748,24 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>220788</t>
+          <t>220824</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>نوران اسامه محمد محمود</t>
+          <t>يوسف وائل حامد ابراهيم العالم</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>220789</t>
+          <t>220825</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>نوران فوزى شعبان فوزى علام</t>
+          <t>يوسف سيد محمد يوسف</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -4802,24 +4802,24 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>220790</t>
+          <t>220826</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>نورهان حسن عبد الرحمن حسن محمد</t>
+          <t>عبد الله خالد احمد باحاذق</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -4829,24 +4829,24 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>220791</t>
+          <t>220827</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>نورهان محمد عبد العزيز حسن</t>
+          <t>أبوبكر طارق أبوبكر رمضان</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>220792</t>
+          <t>220829</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>نورهان محمود السيد محمود اللقانى</t>
+          <t>تبارك رائد حسن كميل</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>220793</t>
+          <t>220830</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>نورين احمد عبد الحكيم رضوان</t>
+          <t>مصطفى محمد على</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -4910,24 +4910,24 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>220794</t>
+          <t>220832</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
+          <t>احمد عبد الله نعمان محمد</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -4937,24 +4937,24 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>220795</t>
+          <t>220833</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
+          <t>رغد فيصل عقيل العمايري</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -4964,24 +4964,24 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>220796</t>
+          <t>220834</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
+          <t>احمد سليمان محمد</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -4991,24 +4991,24 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>220797</t>
+          <t>220838</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
+          <t>حمزه طارق الطراد</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -5018,24 +5018,24 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>220799</t>
+          <t>220839</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>هاجر احمد رمضان سعد الفرحاتى</t>
+          <t>عزام نبيل يحي العمير</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>220800</t>
+          <t>220848</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>هاجر عاطف سيد عبد الجيد احمد</t>
+          <t>عبد الله مسعود مصطفى</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -5072,24 +5072,24 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>220801</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>هايدى محمد حسين رفاعى فراج</t>
+          <t>قند عدي بدران</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -5099,24 +5099,24 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>220802</t>
+          <t>220856</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>هدى مدحت خيرى احمد فرج</t>
+          <t>ماسه بلال الدهبي</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -5126,24 +5126,24 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>220803</t>
+          <t>220857</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>هرمينا عبد الله جاد جرجس</t>
+          <t>محمد عبده علوي محمد</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -5153,24 +5153,24 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>220804</t>
+          <t>220867</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>هنا خليل عبد الرؤف محمد سعيد</t>
+          <t>شهد جمعه على عبد الفتاح</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -5180,24 +5180,24 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>220805</t>
+          <t>220876</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>وسام ايمن على الشريف</t>
+          <t>عبد المهيمن مهند سلمان</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -5207,24 +5207,24 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>220807</t>
+          <t>220878</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>وليد ياسر عبد الشافى محمود</t>
+          <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -5234,24 +5234,24 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>220808</t>
+          <t>220879</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>ياسمين عادل السيد الفرغلى حسن</t>
+          <t>علي بن محمد بن على المحمد صالح</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -5261,24 +5261,24 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>220809</t>
+          <t>221018</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>يحيى احمد محمد عبد الفتاح الزيات</t>
+          <t>رامي احمد الخطيب</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -5288,24 +5288,24 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>220810</t>
+          <t>221335</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>يحيى محمد يحى على</t>
+          <t>حذيفه طريف القطرنجى</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -5315,24 +5315,24 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>220813</t>
+          <t>220896</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
+          <t>احمد السر ميرغني عمر</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -5342,24 +5342,24 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>220814</t>
+          <t>220900</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>يوسف جلال محمد عبد الفتاح صالح</t>
+          <t>ديما حسن نصر الله الزاملي</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -5369,24 +5369,24 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>220815</t>
+          <t>220902</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>يوسف حمدى احمد طاجن</t>
+          <t>كاتيا منيمنة</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>220816</t>
+          <t>220908</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>يوسف عمرو على حفنى ابراهيم</t>
+          <t>عمرو زين العابدين طلعت عابدين</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -5423,24 +5423,24 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>220817</t>
+          <t>220909</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>يوسف فهيم عبد الحميد ابو عزيز</t>
+          <t>احمد جمال محمد عليمى محمد</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -5450,24 +5450,24 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>220818</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>يوسف محمد رضا جلال احمد سيد احمد</t>
+          <t>شيماء بدر زبير علي</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -5477,24 +5477,24 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220914</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>يوسف محمد محمد السيد البطه</t>
+          <t>محمد بن ضيف الله بن رزق الصبحى</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -5504,24 +5504,24 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>220820</t>
+          <t>220919</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>يوسف محمود محمد ابراهيم</t>
+          <t>احمد سليم عيسى ابو لاوى</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -5531,24 +5531,24 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>220821</t>
+          <t>220920</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>يوسف مصطفى محمد رسلان</t>
+          <t>دارين محمد طاهر</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -5558,24 +5558,24 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>220822</t>
+          <t>220925</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>يوسف مصطفى مصطفى محمد</t>
+          <t>دينا زياد ابراهيم زقماط</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -5585,24 +5585,24 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>220824</t>
+          <t>220927</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>يوسف وائل حامد ابراهيم العالم</t>
+          <t>سعيد احمد سعيد محمد عبدالسيد</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -5612,24 +5612,24 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>220825</t>
+          <t>220928</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>يوسف سيد محمد يوسف</t>
+          <t>ابراهيم عبدالفتاح ابراهيم السروري</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -5639,24 +5639,24 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>220826</t>
+          <t>220929</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>عبد الله خالد احمد باحاذق</t>
+          <t>الوليد بن عبدالله بن محمد عامر</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -5666,24 +5666,24 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>220827</t>
+          <t>220930</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>أبوبكر طارق أبوبكر رمضان</t>
+          <t>يوسف نبيل فريد شاهين</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -5693,24 +5693,24 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>220828</t>
+          <t>220937</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>سلمى مصطفى عبد العاطى حسن ناصف</t>
+          <t>اسيل يحيى محمد المزايده</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -5720,24 +5720,24 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>220829</t>
+          <t>220940</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>تبارك رائد حسن كميل</t>
+          <t>عبدالرحمن محمد محسن الزقري</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>220830</t>
+          <t>220942</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>مصطفى محمد على</t>
+          <t>عدي علي فلاح الحديد</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -5774,24 +5774,24 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>220832</t>
+          <t>220947</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>احمد عبد الله نعمان محمد</t>
+          <t>مهند عبد الفتاح سلام مقبل</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -5801,24 +5801,24 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>220833</t>
+          <t>220950</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>رغد فيصل عقيل العمايري</t>
+          <t>يوسف اسماعيل ابراهيم احمد</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -5828,24 +5828,24 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>220834</t>
+          <t>220951</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>احمد سليمان محمد</t>
+          <t>محمد تيسير محمد ياسين</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>220838</t>
+          <t>220954</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>حمزه طارق الطراد</t>
+          <t>طيف فرج علي العماري</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -5882,24 +5882,24 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>220839</t>
+          <t>220955</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>عزام نبيل يحي العمير</t>
+          <t>غاده عبدالاله عبدالكريم عبدالله</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -5909,24 +5909,24 @@
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>220845</t>
+          <t>220956</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>ريان تاج الدين عبد الله أحمد</t>
+          <t>نور الحسين أسعد جاسم العكيلي</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -5936,24 +5936,24 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>220848</t>
+          <t>220958</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>عبد الله مسعود مصطفى</t>
+          <t>محمد حميد حمود علي الديلي</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -5963,24 +5963,24 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>220853</t>
+          <t>220959</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>قند عدي بدران</t>
+          <t>ايليا سالم يعقوب المدانات</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -5990,24 +5990,24 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>220856</t>
+          <t>220961</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>ماسه بلال الدهبي</t>
+          <t>رهف نزار احمد الامام</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -6017,24 +6017,24 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>220857</t>
+          <t>220963</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>محمد عبده علوي محمد</t>
+          <t>شهد بنت عبدالله بن حسين ال الصومعي</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -6044,24 +6044,24 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>220867</t>
+          <t>220964</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>شهد جمعه على عبد الفتاح</t>
+          <t>ميس غسان مرشد مفارجة</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -6071,24 +6071,24 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>220876</t>
+          <t>220966</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>عبد المهيمن مهند سلمان</t>
+          <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -6098,24 +6098,24 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>220878</t>
+          <t>220762</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
+          <t>مؤيد وليد علي كرجه</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -6125,24 +6125,24 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>220879</t>
+          <t>220845</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>علي بن محمد بن على المحمد صالح</t>
+          <t>ريان تاج الدين عبد الله أحمد</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -6697,19 +6697,19 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>221018</t>
+          <t>221020</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>رامي احمد الخطيب</t>
+          <t>مي سلوم سالم لم يصعد</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>221020</t>
+          <t>221021</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>مي سلوم سالم لم يصعد</t>
+          <t>عثمان ابوالقاسم احمد حسن</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>221021</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>عثمان ابوالقاسم احمد حسن</t>
+          <t>مرام عبدالله محمد حامد</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>221023</t>
+          <t>221025</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>مرام عبدالله محمد حامد</t>
+          <t>بتول محمد يوسف</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>221029</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>بتول محمد يوسف</t>
+          <t>معتصم توفيق محمد بكرون</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>221029</t>
+          <t>221035</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>معتصم توفيق محمد بكرون</t>
+          <t>محمد بدر احمد علي مول الدويله</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>221035</t>
+          <t>221036</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>محمد بدر احمد علي مول الدويله</t>
+          <t>عبد السلام وليد عبد السلام ابو حلوان</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>221036</t>
+          <t>221037</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>عبد السلام وليد عبد السلام ابو حلوان</t>
+          <t>رنا بنت عبد الغني بن بكر برناوي</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>221037</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>رنا بنت عبد الغني بن بكر برناوي</t>
+          <t>محمد الطاهر محمد الطاهر</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -6940,19 +6940,19 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>221040</t>
+          <t>221046</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>محمد الطاهر محمد الطاهر</t>
+          <t>احمد مجدي امين محمد</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>221046</t>
+          <t>221047</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>احمد مجدي امين محمد</t>
+          <t>احمد محسن محمد ماهر ابو هاشم</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -6989,24 +6989,24 @@
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>A2-D2</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>221047</t>
+          <t>221048</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>احمد محسن محمد ماهر ابو هاشم</t>
+          <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>221048</t>
+          <t>221049</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
+          <t>ادهم عامر عبدالحافظ احمد محمد</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>221049</t>
+          <t>221050</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>ادهم عامر عبدالحافظ احمد محمد</t>
+          <t>اسراء احمد محمد عبد الصادق نور</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>221050</t>
+          <t>221052</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>اسراء احمد محمد عبد الصادق نور</t>
+          <t>امنيه سلامه عبده محمد</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -7102,19 +7102,19 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>221051</t>
+          <t>221053</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>اسراء هشام محمد عبد المنعم</t>
+          <t>امينه خالد عوض عفيفى تاج الدين</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -7129,19 +7129,19 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>221052</t>
+          <t>221054</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>امنيه سلامه عبده محمد</t>
+          <t>انجي علاء سعد الدين الشحات السيد</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>221053</t>
+          <t>221055</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>امينه خالد عوض عفيفى تاج الدين</t>
+          <t>ايلاري هاني سند ماضي</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -7183,19 +7183,19 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>221054</t>
+          <t>221056</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>انجي علاء سعد الدين الشحات السيد</t>
+          <t>إيريني وجدي عزمي عبدالمسيح</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>221055</t>
+          <t>221059</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>ايلاري هاني سند ماضي</t>
+          <t>أحمد عزت مختار عزت</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>221056</t>
+          <t>221060</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>إيريني وجدي عزمي عبدالمسيح</t>
+          <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>221059</t>
+          <t>221062</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>أحمد عزت مختار عزت</t>
+          <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -7291,19 +7291,19 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>221060</t>
+          <t>221063</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
+          <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -7318,19 +7318,19 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>221062</t>
+          <t>221064</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
+          <t>أكرم مصطفي فتحي محمد</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>221063</t>
+          <t>221066</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
+          <t>أية عبدالسميع محمد سليمان</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -7372,19 +7372,19 @@
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>221064</t>
+          <t>221067</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>أكرم مصطفي فتحي محمد</t>
+          <t>آيتن أحمد مصطفى محمد مصطفى</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -7399,19 +7399,19 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>221066</t>
+          <t>221068</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>أية عبدالسميع محمد سليمان</t>
+          <t>آيه حسن محمد مأمون</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -7426,19 +7426,19 @@
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>221067</t>
+          <t>221069</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>آيتن أحمد مصطفى محمد مصطفى</t>
+          <t>بثينه خالد ابراهيم محمد موسى</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -7453,19 +7453,19 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>221068</t>
+          <t>221070</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>آيه حسن محمد مأمون</t>
+          <t>بسمة علاء حسني زهران</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>221069</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>بثينه خالد ابراهيم محمد موسى</t>
+          <t>بسملة وسام صلاح أحمد</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -7507,19 +7507,19 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>221070</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>بسمة علاء حسني زهران</t>
+          <t>بسنت احمد شكرالله عبدالباسط</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>221073</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>بسملة وسام صلاح أحمد</t>
+          <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -7561,19 +7561,19 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>221072</t>
+          <t>221075</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>بسنت احمد شكرالله عبدالباسط</t>
+          <t>تسنيم اسامة يوسف نعيم</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -7588,19 +7588,19 @@
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>221073</t>
+          <t>221076</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
+          <t>تسنيم علاء ناجي عبدالراضي</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -7615,19 +7615,19 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>221075</t>
+          <t>221077</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>تسنيم اسامة يوسف نعيم</t>
+          <t>تقي محمود احمد السمكري</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -7642,19 +7642,19 @@
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>221076</t>
+          <t>221078</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>تسنيم علاء ناجي عبدالراضي</t>
+          <t>توماس نبيل سامي غطاس</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -7669,19 +7669,19 @@
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>221077</t>
+          <t>221079</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>تقي محمود احمد السمكري</t>
+          <t>جنا هاني احمد عبد القادر</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -7696,19 +7696,19 @@
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>221078</t>
+          <t>221080</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>توماس نبيل سامي غطاس</t>
+          <t>جنة الله علاء الدين أحمد عيد</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -7723,19 +7723,19 @@
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>221079</t>
+          <t>221084</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>جنا هاني احمد عبد القادر</t>
+          <t>جودي احمد السيد سليمان</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -7750,19 +7750,19 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>221080</t>
+          <t>220748</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>جنة الله علاء الدين أحمد عيد</t>
+          <t>ملك عمرو على حسن</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -7772,24 +7772,24 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>A2-E1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>221084</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>جودي احمد السيد سليمان</t>
+          <t>جوفانا روماني راشد شنوده</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -7799,24 +7799,24 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>A2-E1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>221086</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>جوفانا روماني راشد شنوده</t>
+          <t>جونسي صلاح اسماعيل حجازي</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -7831,19 +7831,19 @@
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>221086</t>
+          <t>221087</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>جونسي صلاح اسماعيل حجازي</t>
+          <t>جونى سامر صفوت فهمى ميخائيل</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -7858,19 +7858,19 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>221087</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>جونى سامر صفوت فهمى ميخائيل</t>
+          <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -7885,19 +7885,19 @@
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>221088</t>
+          <t>221089</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
+          <t>حبيبة زكي محمد زكي</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -7912,19 +7912,19 @@
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>221089</t>
+          <t>221090</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>حبيبة زكي محمد زكي</t>
+          <t>حبيبه محمد صابر عبدالعال</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -7939,19 +7939,19 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>221090</t>
+          <t>221091</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>حبيبه محمد صابر عبدالعال</t>
+          <t>حسن احمد حسن الصفتي</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -7966,19 +7966,19 @@
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>221091</t>
+          <t>221092</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>حسن احمد حسن الصفتي</t>
+          <t>حسن محمد حسن شمس الدين</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>221092</t>
+          <t>221093</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>حسن محمد حسن شمس الدين</t>
+          <t>حلا احمد محمد محمد فضل الله</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>221093</t>
+          <t>221095</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>حلا احمد محمد محمد فضل الله</t>
+          <t>حمزه هشام بكر ابو القميز</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>221095</t>
+          <t>221096</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>حمزه هشام بكر ابو القميز</t>
+          <t>حنين طارق محرم شلبي</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>221096</t>
+          <t>221097</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>حنين طارق محرم شلبي</t>
+          <t>خالد علاء عبد السميع عبدالله الديب</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>221097</t>
+          <t>221099</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>خالد علاء عبد السميع عبدالله الديب</t>
+          <t>دارين أحمد فرج القاصد</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>221099</t>
+          <t>221100</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>دارين أحمد فرج القاصد</t>
+          <t>دارين السيد مصيلحي مصيلحي</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>221100</t>
+          <t>221101</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>دارين السيد مصيلحي مصيلحي</t>
+          <t>دارين محمد ابراهيم ماضى</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>221101</t>
+          <t>221102</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>دارين محمد ابراهيم ماضى</t>
+          <t>دانا أسامة عبدالغني محمد</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>221102</t>
+          <t>221103</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>دانا أسامة عبدالغني محمد</t>
+          <t>دانه عبداللطيف فؤاد زيان</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>221103</t>
+          <t>221104</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>دانه عبداللطيف فؤاد زيان</t>
+          <t>دعاء أشرف أحمد عبد الله</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>221104</t>
+          <t>221106</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>دعاء أشرف أحمد عبد الله</t>
+          <t>دينا ناجي عبد المنعم الشيخ</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>221106</t>
+          <t>221108</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>دينا ناجي عبد المنعم الشيخ</t>
+          <t>رانيا عادل طلخان رزق</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>221108</t>
+          <t>221110</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>رانيا عادل طلخان رزق</t>
+          <t>رفيده أيمن مصطفى النحاس شحاته</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>221110</t>
+          <t>221111</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>رفيده أيمن مصطفى النحاس شحاته</t>
+          <t>رنا عمرو محمد شرايحي</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>221111</t>
+          <t>221112</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>رنا عمرو محمد شرايحي</t>
+          <t>رنيم ايمن علي علام</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>221112</t>
+          <t>221114</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>رنيم ايمن علي علام</t>
+          <t>روان محمد ياسر عبد العال ابو الوفا</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>221114</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>روان محمد ياسر عبد العال ابو الوفا</t>
+          <t>روينا محمد عبدالحكيم الاشموني</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>221117</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>روينا محمد عبدالحكيم الاشموني</t>
+          <t>رؤى طارق مرسى محمود</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>221117</t>
+          <t>221118</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>رؤى طارق مرسى محمود</t>
+          <t>ريم السيد صالح خليل</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -8506,19 +8506,19 @@
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>221118</t>
+          <t>221119</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>ريم السيد صالح خليل</t>
+          <t>زياد شريف حلمي الألفي</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -8533,19 +8533,19 @@
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>221119</t>
+          <t>221120</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>زياد شريف حلمي الألفي</t>
+          <t>سارة علاءالدين احمد محمد</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -8560,19 +8560,19 @@
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>221120</t>
+          <t>221121</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>سارة علاءالدين احمد محمد</t>
+          <t>سارة احمد محمد على خليل</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -8587,19 +8587,19 @@
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>221121</t>
+          <t>220449</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>سارة احمد محمد على خليل</t>
+          <t>حبيبة الله وائل البرماوى</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>A2-E2</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -9424,19 +9424,19 @@
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>221157</t>
+          <t>220828</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد عمر عيد</t>
+          <t>سلمى مصطفى عبد العاطى حسن ناصف</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>221158</t>
+          <t>221157</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>عبدالله حسن محمد السعيد عزازي</t>
+          <t>عبدالرحمن محمد عمر عيد</t>
         </is>
       </c>
       <c r="C334" s="3" t="inlineStr">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>221159</t>
+          <t>221158</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>عبدالله محمد مصطفى علي</t>
+          <t>عبدالله حسن محمد السعيد عزازي</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -9505,19 +9505,19 @@
       </c>
       <c r="E335" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>221160</t>
+          <t>221159</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>عزت حسام عبدالله عبدالعزيز</t>
+          <t>عبدالله محمد مصطفى علي</t>
         </is>
       </c>
       <c r="C336" s="3" t="inlineStr">
@@ -9532,19 +9532,19 @@
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>221161</t>
+          <t>221160</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>علاء هشام حسين ابوعلوان</t>
+          <t>عزت حسام عبدالله عبدالعزيز</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
@@ -9559,19 +9559,19 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>221162</t>
+          <t>221161</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>علي أحمد حامد أمين</t>
+          <t>علاء هشام حسين ابوعلوان</t>
         </is>
       </c>
       <c r="C338" s="3" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>221163</t>
+          <t>221162</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>عمار ياسر رشدي رجب</t>
+          <t>علي أحمد حامد أمين</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
@@ -9613,19 +9613,19 @@
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>221164</t>
+          <t>221163</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>عمر جمعة عبدالكريم محمد</t>
+          <t>عمار ياسر رشدي رجب</t>
         </is>
       </c>
       <c r="C340" s="3" t="inlineStr">
@@ -9640,19 +9640,19 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>221165</t>
+          <t>221164</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>عمر حمدي محمد طه</t>
+          <t>عمر جمعة عبدالكريم محمد</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
@@ -9667,19 +9667,19 @@
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>221166</t>
+          <t>221165</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>عمر عبد العزيز ابراهيم امين ابراهيم</t>
+          <t>عمر حمدي محمد طه</t>
         </is>
       </c>
       <c r="C342" s="3" t="inlineStr">
@@ -9694,19 +9694,19 @@
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>221167</t>
+          <t>221166</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>عمر عبدالعال غريب عبدالعال</t>
+          <t>عمر عبد العزيز ابراهيم امين ابراهيم</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
@@ -9721,19 +9721,19 @@
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>221168</t>
+          <t>221167</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>عمر محمد احمد احمد السيد فايد</t>
+          <t>عمر عبدالعال غريب عبدالعال</t>
         </is>
       </c>
       <c r="C344" s="3" t="inlineStr">
@@ -9748,19 +9748,19 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>221169</t>
+          <t>221168</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>اروى ابراهيم احمد تهامى</t>
+          <t>عمر محمد احمد احمد السيد فايد</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
@@ -9775,19 +9775,19 @@
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>221170</t>
+          <t>221169</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>فادى عمرو فاروق العراقى</t>
+          <t>اروى ابراهيم احمد تهامى</t>
         </is>
       </c>
       <c r="C346" s="3" t="inlineStr">
@@ -9802,19 +9802,19 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>221174</t>
+          <t>221170</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>فريدة خالد ابوالفتوح احمد</t>
+          <t>فادى عمرو فاروق العراقى</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
@@ -9829,19 +9829,19 @@
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>221179</t>
+          <t>221174</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>لجين عمرو عبدالرازق محمد الطاهر</t>
+          <t>فريدة خالد ابوالفتوح احمد</t>
         </is>
       </c>
       <c r="C348" s="3" t="inlineStr">
@@ -9856,19 +9856,19 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>221181</t>
+          <t>221179</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>لوجين محمد صبري محمد سعد القاضي</t>
+          <t>لجين عمرو عبدالرازق محمد الطاهر</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
@@ -9883,19 +9883,19 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>221202</t>
+          <t>221181</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>مرهان محمد عوض الديب</t>
+          <t>لوجين محمد صبري محمد سعد القاضي</t>
         </is>
       </c>
       <c r="C350" s="3" t="inlineStr">
@@ -9910,19 +9910,19 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>221206</t>
+          <t>221202</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>مريم هشام طلعت حسين</t>
+          <t>مرهان محمد عوض الديب</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
@@ -9937,19 +9937,19 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>221211</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>ملك مصطفي ابراهيم ابراهيم</t>
+          <t>مريم هشام طلعت حسين</t>
         </is>
       </c>
       <c r="C352" s="3" t="inlineStr">
@@ -9964,19 +9964,19 @@
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>221214</t>
+          <t>221211</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>مها محمد سلامة عامر</t>
+          <t>ملك مصطفي ابراهيم ابراهيم</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
@@ -9991,19 +9991,19 @@
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>221217</t>
+          <t>221214</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>ميرا اشرف بساده سعيد</t>
+          <t>مها محمد سلامة عامر</t>
         </is>
       </c>
       <c r="C354" s="3" t="inlineStr">
@@ -10018,19 +10018,19 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>221224</t>
+          <t>221217</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>نور عمرو محمد احمد حسن</t>
+          <t>ميرا اشرف بساده سعيد</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
@@ -10045,19 +10045,19 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>221228</t>
+          <t>221224</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>نوران ممدوح سيد بهجت</t>
+          <t>نور عمرو محمد احمد حسن</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
@@ -10072,19 +10072,19 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>221234</t>
+          <t>221228</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>يارا هانى عبد الرحمن علام</t>
+          <t>نوران ممدوح سيد بهجت</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -10099,19 +10099,19 @@
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>221237</t>
+          <t>221234</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>يمني تحسين عبدالمحيد سيداحمد</t>
+          <t>يارا هانى عبد الرحمن علام</t>
         </is>
       </c>
       <c r="C358" s="3" t="inlineStr">
@@ -10126,19 +10126,19 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>221335</t>
+          <t>221237</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>حذيفه طريف القطرنجى</t>
+          <t>يمني تحسين عبدالمحيد سيداحمد</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>A2.xlsx</t>
+          <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
         </is>
       </c>
     </row>

--- a/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
+++ b/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
@@ -872,12 +872,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>220550</t>
+          <t>220577</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>شيماء شريف محمد عبد الرحمن احمد</t>
+          <t>عبدالرحمن محمد عبداللطيف شهاب</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>220577</t>
+          <t>220615</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد عبداللطيف شهاب</t>
+          <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -926,12 +926,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>220616</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
+          <t>غاده احمد احمد احمد الشريف</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -953,12 +953,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>220616</t>
+          <t>220623</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>غاده احمد احمد احمد الشريف</t>
+          <t>فاطمه احمد محمد محمود كرم</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -980,12 +980,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>220623</t>
+          <t>220624</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>فاطمه احمد محمد محمود كرم</t>
+          <t>فاطمه السيد محمد فتحى عطيه الله</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>220624</t>
+          <t>220625</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>فاطمه السيد محمد فتحى عطيه الله</t>
+          <t>فاطمه حموده على عبد الحميد حموده</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1034,12 +1034,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>220625</t>
+          <t>220627</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>فاطمه حموده على عبد الحميد حموده</t>
+          <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1061,12 +1061,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>220627</t>
+          <t>220628</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
+          <t>فاطمه محمود محمد امام</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>220628</t>
+          <t>220629</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>فاطمه محمود محمد امام</t>
+          <t>فتحى محمد فتحى السيد عبد الله</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1115,12 +1115,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>220629</t>
+          <t>220630</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>فتحى محمد فتحى السيد عبد الله</t>
+          <t>فريده محمود فؤاد محمود</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1142,12 +1142,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>220630</t>
+          <t>220635</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>فريده محمود فؤاد محمود</t>
+          <t>كريم ايمن محمد مصطفى ابراهيم</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1169,12 +1169,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>220635</t>
+          <t>220636</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>كريم ايمن محمد مصطفى ابراهيم</t>
+          <t>كريم سعيد احمد ابراهيم الحريزى</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1196,12 +1196,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>220636</t>
+          <t>220639</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>كريم سعيد احمد ابراهيم الحريزى</t>
+          <t>كريم مصطفى عبد الرحمن على سعد</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1223,12 +1223,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>220639</t>
+          <t>220645</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>كريم مصطفى عبد الرحمن على سعد</t>
+          <t>لجين احمد عبد الله البسطويسى</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1250,12 +1250,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>220645</t>
+          <t>220646</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>لجين احمد عبد الله البسطويسى</t>
+          <t>لجين اشرف جلال عبد الرحمن السمرى</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1277,12 +1277,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>220646</t>
+          <t>220647</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>لجين اشرف جلال عبد الرحمن السمرى</t>
+          <t>لوجين السيد محروس اسماعيل</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>A2-A1</t>
+          <t>A2-A2</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1304,12 +1304,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>220647</t>
+          <t>220648</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>لوجين السيد محروس اسماعيل</t>
+          <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1331,12 +1331,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>220649</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
+          <t>لؤى على حسين حسن ابو صفيه</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1358,12 +1358,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>220649</t>
+          <t>220651</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>لؤى على حسين حسن ابو صفيه</t>
+          <t>ليلى اشرف وصفى</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1385,12 +1385,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>220651</t>
+          <t>220653</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ليلى اشرف وصفى</t>
+          <t>ماجد حسنى السيد التلاوى</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1412,12 +1412,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>220653</t>
+          <t>220655</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ماجد حسنى السيد التلاوى</t>
+          <t>مارى مجدى منير عبده</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>220655</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>مارى مجدى منير عبده</t>
+          <t>مالك محمود على محمود زين الدين</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>220659</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>مالك محمود على محمود زين الدين</t>
+          <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1493,12 +1493,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>220662</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
+          <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1520,12 +1520,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>220662</t>
+          <t>220666</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
+          <t>محمد احمد فتحى احمد احمد</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>220666</t>
+          <t>220667</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>محمد احمد فتحى احمد احمد</t>
+          <t>محمد اسامه علاء الدين اللو</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1574,12 +1574,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>220667</t>
+          <t>220669</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>محمد اسامه علاء الدين اللو</t>
+          <t>محمد السعيد السعيد محمد شعبان</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>220669</t>
+          <t>220670</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>محمد السعيد السعيد محمد شعبان</t>
+          <t>محمد السعيد مسعد مصطفى حراز</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1628,12 +1628,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>220670</t>
+          <t>220672</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>محمد السعيد مسعد مصطفى حراز</t>
+          <t>محمد الشحات على احمد سرور</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>220672</t>
+          <t>220673</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>محمد الشحات على احمد سرور</t>
+          <t>محمد أيمن محمد أحمد ناصف</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>220673</t>
+          <t>220674</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>محمد أيمن محمد أحمد ناصف</t>
+          <t>محمد باسم عبد الكريم محمود</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -1709,12 +1709,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>220674</t>
+          <t>220678</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>محمد باسم عبد الكريم محمود</t>
+          <t>محمد بهاء عبد الحميد عبد الغفار</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1736,12 +1736,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>220678</t>
+          <t>220679</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>محمد بهاء عبد الحميد عبد الغفار</t>
+          <t>محمد جابر توفيق الشافعى</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>220679</t>
+          <t>220680</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>محمد جابر توفيق الشافعى</t>
+          <t>محمد حسن جلال عبد المجيد وهدان</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -1790,12 +1790,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>220680</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>محمد حسن جلال عبد المجيد وهدان</t>
+          <t>محمد سعيد محمود عبد المنعم محمود</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1817,12 +1817,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>220683</t>
+          <t>220684</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>محمد سعيد محمود عبد المنعم محمود</t>
+          <t>محمد صبرى جوده عبد الله خضر</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1844,12 +1844,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>220684</t>
+          <t>220685</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>محمد صبرى جوده عبد الله خضر</t>
+          <t>محمد صلاح حسن عبد الله حسن</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>220685</t>
+          <t>220686</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>محمد صلاح حسن عبد الله حسن</t>
+          <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>220686</t>
+          <t>220687</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
+          <t>محمد طارق محمد عبد الرحمن العرينى</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>220687</t>
+          <t>220688</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>محمد طارق محمد عبد الرحمن العرينى</t>
+          <t>محمد عبد الحفيظ عبد الله محمد على</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1952,12 +1952,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>220688</t>
+          <t>220689</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>محمد عبد الحفيظ عبد الله محمد على</t>
+          <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1979,12 +1979,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>220689</t>
+          <t>220690</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
+          <t>محمد عبد النبى عطيه ابو شعيشع</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2006,12 +2006,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>220690</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>محمد عبد النبى عطيه ابو شعيشع</t>
+          <t>محمد عبدالهادى عبدالمنعم عمر</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2033,12 +2033,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>220691</t>
+          <t>220693</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>محمد عبدالهادى عبدالمنعم عمر</t>
+          <t>محمد علاء محمد عبد العزيز عبد الله</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -2060,12 +2060,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>220693</t>
+          <t>220694</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>محمد علاء محمد عبد العزيز عبد الله</t>
+          <t>محمد على محمد احمد محمد</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>220694</t>
+          <t>220698</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>محمد على محمد احمد محمد</t>
+          <t>محمد محمد احمد الفتيانى</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>A2-A2</t>
+          <t>A2-B1</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2114,12 +2114,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>220698</t>
+          <t>220700</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>محمد محمد احمد الفتيانى</t>
+          <t>محمد محمد عبد الله التهامي</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2141,12 +2141,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>220701</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>محمد محمد عبد الله التهامي</t>
+          <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2168,12 +2168,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>220701</t>
+          <t>220702</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
+          <t>محمد محيى الدين محمد سيد مكاوى</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2195,12 +2195,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>220702</t>
+          <t>220703</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>محمد محيى الدين محمد سيد مكاوى</t>
+          <t>محمد مختار شعبان هلالى سليمان</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2222,12 +2222,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>220703</t>
+          <t>220705</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>محمد مختار شعبان هلالى سليمان</t>
+          <t>محمد مفرح عبد الباسط عبد الحليم</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>220705</t>
+          <t>220706</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>محمد مفرح عبد الباسط عبد الحليم</t>
+          <t>محمد وائل محمد العيسوى</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2276,12 +2276,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>220706</t>
+          <t>220707</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>محمد وائل محمد العيسوى</t>
+          <t>محمد وحيد محمد رزق</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2303,12 +2303,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>220707</t>
+          <t>220708</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>محمد وحيد محمد رزق</t>
+          <t>محمد ياسر الشافعى محمد على</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2330,12 +2330,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>220708</t>
+          <t>220709</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>محمد ياسر الشافعى محمد على</t>
+          <t>محمد ياسر حامد دياب حمد</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>220709</t>
+          <t>220710</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>محمد ياسر حامد دياب حمد</t>
+          <t>محمود جمال حسين محمد رسلان</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>220710</t>
+          <t>220711</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>محمود جمال حسين محمد رسلان</t>
+          <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>220711</t>
+          <t>220712</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
+          <t>محمود حسن عبد النبى حسين</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2438,12 +2438,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>220712</t>
+          <t>220714</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>محمود حسن عبد النبى حسين</t>
+          <t>محمود كريم شحاته حسن كرد</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>220714</t>
+          <t>220717</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>محمود كريم شحاته حسن كرد</t>
+          <t>محمود منصور محمود محمد السيد يعقوب</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2492,12 +2492,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>220717</t>
+          <t>220720</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>محمود منصور محمود محمد السيد يعقوب</t>
+          <t>مروان صبحى ابو الحسن محمد على</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2519,12 +2519,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>220720</t>
+          <t>220721</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>مروان صبحى ابو الحسن محمد على</t>
+          <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>220722</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
+          <t>مروه عبد الحميد على حسن ايوب</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2573,12 +2573,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>220722</t>
+          <t>220723</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>مروه عبد الحميد على حسن ايوب</t>
+          <t>مريم ابراهيم احمد ابراهيم مبارك</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2600,12 +2600,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>220723</t>
+          <t>220724</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>مريم ابراهيم احمد ابراهيم مبارك</t>
+          <t>مريم الحسن احمد ابراهيم بيومى</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>220724</t>
+          <t>220725</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>مريم الحسن احمد ابراهيم بيومى</t>
+          <t>مريم ايمن عبد الله محمود فخرى</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2654,12 +2654,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>220725</t>
+          <t>220726</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>مريم ايمن عبد الله محمود فخرى</t>
+          <t>مريم ايمن فؤاد عبدالستار</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2681,12 +2681,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>220726</t>
+          <t>220727</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>مريم ايمن فؤاد عبدالستار</t>
+          <t>مريم ايهاب ملاك ثابت</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>220727</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>مريم ايهاب ملاك ثابت</t>
+          <t>مريم رضا محمد ابراهيم صبره</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -2735,12 +2735,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>220729</t>
+          <t>220730</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>مريم رضا محمد ابراهيم صبره</t>
+          <t>مريم شعبان مصباح خليفه</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2762,12 +2762,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>220730</t>
+          <t>220731</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>مريم شعبان مصباح خليفه</t>
+          <t>مريم شفيق صبحى شفيق حنا</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -2789,12 +2789,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>220731</t>
+          <t>220732</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>مريم شفيق صبحى شفيق حنا</t>
+          <t>مريم عمرو يحيى عبده مدنى</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>220732</t>
+          <t>220733</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>مريم عمرو يحيى عبده مدنى</t>
+          <t>مريم محمد احمد فاروق الديب الشريف</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>220733</t>
+          <t>220734</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد احمد فاروق الديب الشريف</t>
+          <t>مريم محمد احمد محمد عبد المنعم</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>220734</t>
+          <t>220735</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد احمد محمد عبد المنعم</t>
+          <t>مريم محمد ثروت صايم مصطفى</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -2897,12 +2897,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>220735</t>
+          <t>221051</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد ثروت صايم مصطفى</t>
+          <t>اسراء هشام محمد عبد المنعم</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -2924,12 +2924,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>221051</t>
+          <t>220736</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>اسراء هشام محمد عبد المنعم</t>
+          <t>مريم محمد عطيه عبد السلام</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>A2-B1</t>
+          <t>A2-B2</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -2951,12 +2951,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>220736</t>
+          <t>220737</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>مريم محمد عطيه عبد السلام</t>
+          <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2978,12 +2978,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>220737</t>
+          <t>220740</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
+          <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3005,12 +3005,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>220740</t>
+          <t>220742</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
+          <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>220742</t>
+          <t>220744</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
+          <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>220744</t>
+          <t>220745</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
+          <t>مصطفى محمود مصطفى محمود</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -3086,12 +3086,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>220745</t>
+          <t>220746</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>مصطفى محمود مصطفى محمود</t>
+          <t>معاذ طاهر محمد شبانه على</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3113,12 +3113,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>220746</t>
+          <t>220747</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>معاذ طاهر محمد شبانه على</t>
+          <t>ملك عبدالغنى احمد حسن</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3140,12 +3140,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>220747</t>
+          <t>220749</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>ملك عبدالغنى احمد حسن</t>
+          <t>ملك ياسر عبد الوهاب محمد الغندور</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -3167,12 +3167,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>220749</t>
+          <t>220751</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>ملك ياسر عبد الوهاب محمد الغندور</t>
+          <t>منة الله هانى عبد السميع شكرى</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3194,12 +3194,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>220751</t>
+          <t>220752</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>منة الله هانى عبد السميع شكرى</t>
+          <t>منصور هانى منصور عبدالله</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>220752</t>
+          <t>220753</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>منصور هانى منصور عبدالله</t>
+          <t>منه الله احمد محمد جمعه عثمان</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -3248,12 +3248,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>220753</t>
+          <t>220754</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>منه الله احمد محمد جمعه عثمان</t>
+          <t>منه الله محمد صالح محمد النور</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>220754</t>
+          <t>220755</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>منه الله محمد صالح محمد النور</t>
+          <t>منه الله محمد عبد الرازق سالم غاليه</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>220755</t>
+          <t>220756</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>منه الله محمد عبد الرازق سالم غاليه</t>
+          <t>منه عبد الوهاب عبدالله مصطفى</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -3329,12 +3329,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>220756</t>
+          <t>220758</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>منه عبد الوهاب عبدالله مصطفى</t>
+          <t>منه محمود محمد احمد</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -3356,12 +3356,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>220758</t>
+          <t>220759</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>منه محمود محمد احمد</t>
+          <t>منى عبد الحميد ناصف سيف</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3383,12 +3383,12 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>220759</t>
+          <t>220760</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>منى عبد الحميد ناصف سيف</t>
+          <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>220760</t>
+          <t>220764</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
+          <t>مياده سلامه قاسم محمد السيد</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>220764</t>
+          <t>220765</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>مياده سلامه قاسم محمد السيد</t>
+          <t>ميار احمد صبحى السيد السيد</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -3464,12 +3464,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>220765</t>
+          <t>220767</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ميار احمد صبحى السيد السيد</t>
+          <t>ميار صلاح محمد سليمان سليمان</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -3491,12 +3491,12 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>220767</t>
+          <t>220772</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>ميار صلاح محمد سليمان سليمان</t>
+          <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>220772</t>
+          <t>220773</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
+          <t>ندى اشرف عبد الله ابراهيم</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3545,12 +3545,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>220773</t>
+          <t>220774</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>ندى اشرف عبد الله ابراهيم</t>
+          <t>ندى اشرف محمد محمد</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -3572,12 +3572,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>220774</t>
+          <t>220775</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ندى اشرف محمد محمد</t>
+          <t>ندى حسن السيد احمد عطا الله</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>220775</t>
+          <t>220776</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>ندى حسن السيد احمد عطا الله</t>
+          <t>ندى عاطف محمد محمد عبده الشيمى</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -3626,12 +3626,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>220776</t>
+          <t>220777</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ندى عاطف محمد محمد عبده الشيمى</t>
+          <t>ندى على زيد عبد الرحمن</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3653,12 +3653,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>220777</t>
+          <t>220778</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>ندى على زيد عبد الرحمن</t>
+          <t>ندى محمد احمد حامد عامر</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3680,12 +3680,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>220778</t>
+          <t>220779</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ندى محمد احمد حامد عامر</t>
+          <t>نزار عمرو حسن عبد الغنى</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>A2-B2</t>
+          <t>A2-C1</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -3707,12 +3707,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>220779</t>
+          <t>220780</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>نزار عمرو حسن عبد الغنى</t>
+          <t>نصر الدين الابراهيم</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>220780</t>
+          <t>220781</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>نصر الدين الابراهيم</t>
+          <t>نظمى مصطفى نظمى على عبد النبى</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -3761,12 +3761,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>220781</t>
+          <t>220782</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>نظمى مصطفى نظمى على عبد النبى</t>
+          <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -3788,12 +3788,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>220782</t>
+          <t>220783</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
+          <t>نهى احمد ابراهيم محمد عيطه</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -3815,12 +3815,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>220783</t>
+          <t>220784</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>نهى احمد ابراهيم محمد عيطه</t>
+          <t>نهى على عبد الرحمن على</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -3842,12 +3842,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>220787</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>نهى على عبد الرحمن على</t>
+          <t>نور محمد عبد الجليل محمد</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -3869,12 +3869,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>220787</t>
+          <t>220788</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>نور محمد عبد الجليل محمد</t>
+          <t>نوران اسامه محمد محمود</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3896,12 +3896,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>220788</t>
+          <t>220789</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>نوران اسامه محمد محمود</t>
+          <t>نوران فوزى شعبان فوزى علام</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -3923,12 +3923,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>220789</t>
+          <t>220790</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>نوران فوزى شعبان فوزى علام</t>
+          <t>نورهان حسن عبد الرحمن حسن محمد</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -3950,12 +3950,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>220790</t>
+          <t>220791</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>نورهان حسن عبد الرحمن حسن محمد</t>
+          <t>نورهان محمد عبد العزيز حسن</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>220791</t>
+          <t>220792</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>نورهان محمد عبد العزيز حسن</t>
+          <t>نورهان محمود السيد محمود اللقانى</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -4004,12 +4004,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>220792</t>
+          <t>220793</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>نورهان محمود السيد محمود اللقانى</t>
+          <t>نورين احمد عبد الحكيم رضوان</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -4031,12 +4031,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>220793</t>
+          <t>220794</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>نورين احمد عبد الحكيم رضوان</t>
+          <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>220794</t>
+          <t>220795</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
+          <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -4085,12 +4085,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>220795</t>
+          <t>220796</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
+          <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -4112,12 +4112,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>220796</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
+          <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>220797</t>
+          <t>220799</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
+          <t>هاجر احمد رمضان سعد الفرحاتى</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>220799</t>
+          <t>220800</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>هاجر احمد رمضان سعد الفرحاتى</t>
+          <t>هاجر عاطف سيد عبد الجيد احمد</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4193,12 +4193,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>220800</t>
+          <t>220801</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>هاجر عاطف سيد عبد الجيد احمد</t>
+          <t>هايدى محمد حسين رفاعى فراج</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>220801</t>
+          <t>220802</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>هايدى محمد حسين رفاعى فراج</t>
+          <t>هدى مدحت خيرى احمد فرج</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>220802</t>
+          <t>220803</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>هدى مدحت خيرى احمد فرج</t>
+          <t>هرمينا عبد الله جاد جرجس</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -4274,12 +4274,12 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>220803</t>
+          <t>220804</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>هرمينا عبد الله جاد جرجس</t>
+          <t>هنا خليل عبد الرؤف محمد سعيد</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -4301,12 +4301,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>220804</t>
+          <t>220805</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>هنا خليل عبد الرؤف محمد سعيد</t>
+          <t>وسام ايمن على الشريف</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -4328,12 +4328,12 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>220805</t>
+          <t>220807</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>وسام ايمن على الشريف</t>
+          <t>وليد ياسر عبد الشافى محمود</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>220807</t>
+          <t>220808</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>وليد ياسر عبد الشافى محمود</t>
+          <t>ياسمين عادل السيد الفرغلى حسن</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>220808</t>
+          <t>220809</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ياسمين عادل السيد الفرغلى حسن</t>
+          <t>يحيى احمد محمد عبد الفتاح الزيات</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -4409,12 +4409,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>220809</t>
+          <t>220810</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>يحيى احمد محمد عبد الفتاح الزيات</t>
+          <t>يحيى محمد يحى على</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -4436,12 +4436,12 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>220810</t>
+          <t>220813</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>يحيى محمد يحى على</t>
+          <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>220813</t>
+          <t>220814</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
+          <t>يوسف جلال محمد عبد الفتاح صالح</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -4490,12 +4490,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>220814</t>
+          <t>220890</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>يوسف جلال محمد عبد الفتاح صالح</t>
+          <t>يوسف حسين ناجي الصرايره</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>220890</t>
+          <t>220815</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>يوسف حسين ناجي الصرايره</t>
+          <t>يوسف حمدى احمد طاجن</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>A2-C1</t>
+          <t>A2-C2</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -4544,12 +4544,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>220815</t>
+          <t>220816</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>يوسف حمدى احمد طاجن</t>
+          <t>يوسف عمرو على حفنى ابراهيم</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -4571,12 +4571,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>220816</t>
+          <t>220817</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>يوسف عمرو على حفنى ابراهيم</t>
+          <t>يوسف فهيم عبد الحميد ابو عزيز</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -4598,12 +4598,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>220817</t>
+          <t>220818</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>يوسف فهيم عبد الحميد ابو عزيز</t>
+          <t>يوسف محمد رضا جلال احمد سيد احمد</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>220818</t>
+          <t>220819</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>يوسف محمد رضا جلال احمد سيد احمد</t>
+          <t>يوسف محمد محمد السيد البطه</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -4652,12 +4652,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>220819</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>يوسف محمد محمد السيد البطه</t>
+          <t>يوسف محمود محمد ابراهيم</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -4679,12 +4679,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>220820</t>
+          <t>220821</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>يوسف محمود محمد ابراهيم</t>
+          <t>يوسف مصطفى محمد رسلان</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -4706,12 +4706,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>220821</t>
+          <t>220822</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>يوسف مصطفى محمد رسلان</t>
+          <t>يوسف مصطفى مصطفى محمد</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -4733,12 +4733,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>220822</t>
+          <t>220824</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>يوسف مصطفى مصطفى محمد</t>
+          <t>يوسف وائل حامد ابراهيم العالم</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4760,12 +4760,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>220824</t>
+          <t>220825</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>يوسف وائل حامد ابراهيم العالم</t>
+          <t>يوسف سيد محمد يوسف</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -4787,12 +4787,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>220825</t>
+          <t>220826</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>يوسف سيد محمد يوسف</t>
+          <t>عبد الله خالد احمد باحاذق</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -4814,12 +4814,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>220826</t>
+          <t>220827</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>عبد الله خالد احمد باحاذق</t>
+          <t>أبوبكر طارق أبوبكر رمضان</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -4841,12 +4841,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>220827</t>
+          <t>220829</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>أبوبكر طارق أبوبكر رمضان</t>
+          <t>تبارك رائد حسن كميل</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -4868,12 +4868,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>220829</t>
+          <t>220830</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>تبارك رائد حسن كميل</t>
+          <t>مصطفى محمد على</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -4895,12 +4895,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>220830</t>
+          <t>220832</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>مصطفى محمد على</t>
+          <t>احمد عبد الله نعمان محمد</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -4922,12 +4922,12 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>220832</t>
+          <t>220833</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>احمد عبد الله نعمان محمد</t>
+          <t>رغد فيصل عقيل العمايري</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -4949,12 +4949,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>220833</t>
+          <t>220834</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>رغد فيصل عقيل العمايري</t>
+          <t>احمد سليمان محمد</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -4976,12 +4976,12 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>220834</t>
+          <t>220838</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>احمد سليمان محمد</t>
+          <t>حمزه طارق الطراد</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>220838</t>
+          <t>220839</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>حمزه طارق الطراد</t>
+          <t>عزام نبيل يحي العمير</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -5030,12 +5030,12 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>220839</t>
+          <t>220848</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>عزام نبيل يحي العمير</t>
+          <t>عبد الله مسعود مصطفى</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5057,12 +5057,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>220848</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>عبد الله مسعود مصطفى</t>
+          <t>قند عدي بدران</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -5084,12 +5084,12 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>220853</t>
+          <t>220856</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>قند عدي بدران</t>
+          <t>ماسه بلال الدهبي</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -5111,12 +5111,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>220856</t>
+          <t>220857</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>ماسه بلال الدهبي</t>
+          <t>محمد عبده علوي محمد</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -5138,12 +5138,12 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>220857</t>
+          <t>220867</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>محمد عبده علوي محمد</t>
+          <t>شهد جمعه على عبد الفتاح</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -5165,12 +5165,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>220867</t>
+          <t>220876</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>شهد جمعه على عبد الفتاح</t>
+          <t>عبد المهيمن مهند سلمان</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -5192,12 +5192,12 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>220876</t>
+          <t>220878</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>عبد المهيمن مهند سلمان</t>
+          <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -5219,12 +5219,12 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>220878</t>
+          <t>220879</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
+          <t>علي بن محمد بن على المحمد صالح</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -5246,12 +5246,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>220879</t>
+          <t>221018</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>علي بن محمد بن على المحمد صالح</t>
+          <t>رامي احمد الخطيب</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -5273,12 +5273,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>221018</t>
+          <t>221335</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>رامي احمد الخطيب</t>
+          <t>حذيفه طريف القطرنجى</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -5300,12 +5300,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>221335</t>
+          <t>220896</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>حذيفه طريف القطرنجى</t>
+          <t>احمد السر ميرغني عمر</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>A2-C2</t>
+          <t>A2-D1</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -5327,12 +5327,12 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>220896</t>
+          <t>220900</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>احمد السر ميرغني عمر</t>
+          <t>ديما حسن نصر الله الزاملي</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>220900</t>
+          <t>220902</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>ديما حسن نصر الله الزاملي</t>
+          <t>كاتيا منيمنة</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>220902</t>
+          <t>220908</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>كاتيا منيمنة</t>
+          <t>عمرو زين العابدين طلعت عابدين</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>220908</t>
+          <t>220909</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>عمرو زين العابدين طلعت عابدين</t>
+          <t>احمد جمال محمد عليمى محمد</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -5435,12 +5435,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>220909</t>
+          <t>220912</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>احمد جمال محمد عليمى محمد</t>
+          <t>شيماء بدر زبير علي</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -5462,12 +5462,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>220912</t>
+          <t>220914</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>شيماء بدر زبير علي</t>
+          <t>محمد بن ضيف الله بن رزق الصبحى</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>220914</t>
+          <t>220919</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>محمد بن ضيف الله بن رزق الصبحى</t>
+          <t>احمد سليم عيسى ابو لاوى</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -5516,12 +5516,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>220919</t>
+          <t>220920</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>احمد سليم عيسى ابو لاوى</t>
+          <t>دارين محمد طاهر</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -5543,12 +5543,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>220925</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>دارين محمد طاهر</t>
+          <t>دينا زياد ابراهيم زقماط</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -5570,12 +5570,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>220925</t>
+          <t>220927</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>دينا زياد ابراهيم زقماط</t>
+          <t>سعيد احمد سعيد محمد عبدالسيد</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -5597,12 +5597,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>220927</t>
+          <t>220928</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>سعيد احمد سعيد محمد عبدالسيد</t>
+          <t>ابراهيم عبدالفتاح ابراهيم السروري</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>220928</t>
+          <t>220929</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>ابراهيم عبدالفتاح ابراهيم السروري</t>
+          <t>الوليد بن عبدالله بن محمد عامر</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -5651,12 +5651,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>220929</t>
+          <t>220930</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>الوليد بن عبدالله بن محمد عامر</t>
+          <t>يوسف نبيل فريد شاهين</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -5678,12 +5678,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>220930</t>
+          <t>220937</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>يوسف نبيل فريد شاهين</t>
+          <t>اسيل يحيى محمد المزايده</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -5705,12 +5705,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>220937</t>
+          <t>220940</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>اسيل يحيى محمد المزايده</t>
+          <t>عبدالرحمن محمد محسن الزقري</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>220940</t>
+          <t>220942</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>عبدالرحمن محمد محسن الزقري</t>
+          <t>عدي علي فلاح الحديد</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -5759,12 +5759,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>220942</t>
+          <t>220947</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>عدي علي فلاح الحديد</t>
+          <t>مهند عبد الفتاح سلام مقبل</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -5786,12 +5786,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>220947</t>
+          <t>220950</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>مهند عبد الفتاح سلام مقبل</t>
+          <t>يوسف اسماعيل ابراهيم احمد</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -5813,12 +5813,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>220950</t>
+          <t>220951</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>يوسف اسماعيل ابراهيم احمد</t>
+          <t>محمد تيسير محمد ياسين</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -5840,12 +5840,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>220951</t>
+          <t>220954</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>محمد تيسير محمد ياسين</t>
+          <t>طيف فرج علي العماري</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -5867,12 +5867,12 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>220954</t>
+          <t>220955</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>طيف فرج علي العماري</t>
+          <t>غاده عبدالاله عبدالكريم عبدالله</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -5894,12 +5894,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>220955</t>
+          <t>220956</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>غاده عبدالاله عبدالكريم عبدالله</t>
+          <t>نور الحسين أسعد جاسم العكيلي</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -5921,12 +5921,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>220956</t>
+          <t>220958</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>نور الحسين أسعد جاسم العكيلي</t>
+          <t>محمد حميد حمود علي الديلي</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -5948,12 +5948,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>220958</t>
+          <t>220959</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>محمد حميد حمود علي الديلي</t>
+          <t>ايليا سالم يعقوب المدانات</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -5975,12 +5975,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>220959</t>
+          <t>220961</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>ايليا سالم يعقوب المدانات</t>
+          <t>رهف نزار احمد الامام</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -6002,12 +6002,12 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>220961</t>
+          <t>220963</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>رهف نزار احمد الامام</t>
+          <t>شهد بنت عبدالله بن حسين ال الصومعي</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>220963</t>
+          <t>220964</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>شهد بنت عبدالله بن حسين ال الصومعي</t>
+          <t>ميس غسان مرشد مفارجة</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -6056,12 +6056,12 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>220964</t>
+          <t>220966</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>ميس غسان مرشد مفارجة</t>
+          <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -6083,12 +6083,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>220966</t>
+          <t>220762</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
+          <t>مؤيد وليد علي كرجه</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>A2-D1</t>
+          <t>A2-D2</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -6110,12 +6110,12 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>220762</t>
+          <t>220845</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>مؤيد وليد علي كرجه</t>
+          <t>ريان تاج الدين عبد الله أحمد</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -6137,12 +6137,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>220845</t>
+          <t>220889</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>ريان تاج الدين عبد الله أحمد</t>
+          <t>سجى السر ميرغني عمر</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -6164,12 +6164,12 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>220889</t>
+          <t>220969</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>سجى السر ميرغني عمر</t>
+          <t>نهال حسام زهره</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -6191,12 +6191,12 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>220969</t>
+          <t>220970</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>نهال حسام زهره</t>
+          <t>مبارك حسن ابراهيم</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -6218,12 +6218,12 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>220970</t>
+          <t>220971</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>مبارك حسن ابراهيم</t>
+          <t>فراس حسين نعيم الكوز</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -6245,12 +6245,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>220971</t>
+          <t>220972</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>فراس حسين نعيم الكوز</t>
+          <t>عاصم عبدالحكيم محمد سعيد ناصر</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -6272,12 +6272,12 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>220972</t>
+          <t>220974</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>عاصم عبدالحكيم محمد سعيد ناصر</t>
+          <t>مايا رضوان احمد سالم</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -6299,12 +6299,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>220974</t>
+          <t>220979</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>مايا رضوان احمد سالم</t>
+          <t>محمد حسين محمد الحامد</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>220979</t>
+          <t>220983</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>محمد حسين محمد الحامد</t>
+          <t>حسام محمد احمد الكوز</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>220983</t>
+          <t>220986</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>حسام محمد احمد الكوز</t>
+          <t>هاشم احمد صالح الشرجي</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -6380,12 +6380,12 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>220986</t>
+          <t>220989</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>هاشم احمد صالح الشرجي</t>
+          <t>مشاري محمد يحيي الكحلاني</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>220989</t>
+          <t>220991</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>مشاري محمد يحيي الكحلاني</t>
+          <t>عمر حسام الدين الزيبق</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -6434,12 +6434,12 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>220991</t>
+          <t>220992</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>عمر حسام الدين الزيبق</t>
+          <t>يحيى عبدالغني بني</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -6461,12 +6461,12 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>220992</t>
+          <t>220996</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>يحيى عبدالغني بني</t>
+          <t>صفية وفائي</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -6488,12 +6488,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>220996</t>
+          <t>220997</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>صفية وفائي</t>
+          <t>احمد عماد الدين محمد عبد الرحمن</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -6515,12 +6515,12 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>220997</t>
+          <t>221002</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>احمد عماد الدين محمد عبد الرحمن</t>
+          <t>هاجر مؤيد السلوم</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -6542,12 +6542,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>221002</t>
+          <t>221006</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>هاجر مؤيد السلوم</t>
+          <t>فهد هارون ادم محمد</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -6569,12 +6569,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>221006</t>
+          <t>221008</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>فهد هارون ادم محمد</t>
+          <t>وفاق عبدالوهاب محمد ابراهيم</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -6596,12 +6596,12 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>221008</t>
+          <t>221012</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>وفاق عبدالوهاب محمد ابراهيم</t>
+          <t>اسامه الشيخ احمد الامام</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -6623,12 +6623,12 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>221012</t>
+          <t>221015</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>اسامه الشيخ احمد الامام</t>
+          <t>وفاء حسين ميرغنى محمود</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -6650,12 +6650,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>221015</t>
+          <t>221016</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>وفاء حسين ميرغنى محمود</t>
+          <t>ايمن ناصر محمد ابو ديه</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -6677,12 +6677,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>221016</t>
+          <t>221020</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>ايمن ناصر محمد ابو ديه</t>
+          <t>مي سلوم سالم لم يصعد</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -6704,12 +6704,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>221020</t>
+          <t>221021</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>مي سلوم سالم لم يصعد</t>
+          <t>عثمان ابوالقاسم احمد حسن</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>221021</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>عثمان ابوالقاسم احمد حسن</t>
+          <t>مرام عبدالله محمد حامد</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6758,12 +6758,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>221023</t>
+          <t>221025</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>مرام عبدالله محمد حامد</t>
+          <t>بتول محمد يوسف</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -6785,12 +6785,12 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>221029</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>بتول محمد يوسف</t>
+          <t>معتصم توفيق محمد بكرون</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -6812,12 +6812,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>221029</t>
+          <t>221035</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>معتصم توفيق محمد بكرون</t>
+          <t>محمد بدر احمد علي مول الدويله</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -6839,12 +6839,12 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>221035</t>
+          <t>221036</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>محمد بدر احمد علي مول الدويله</t>
+          <t>عبد السلام وليد عبد السلام ابو حلوان</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -6866,12 +6866,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>221036</t>
+          <t>221037</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>عبد السلام وليد عبد السلام ابو حلوان</t>
+          <t>رنا بنت عبد الغني بن بكر برناوي</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>221037</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>رنا بنت عبد الغني بن بكر برناوي</t>
+          <t>محمد الطاهر محمد الطاهر</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -6920,12 +6920,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>221040</t>
+          <t>221046</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>محمد الطاهر محمد الطاهر</t>
+          <t>احمد مجدي امين محمد</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -6947,12 +6947,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>221046</t>
+          <t>221047</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>احمد مجدي امين محمد</t>
+          <t>احمد محسن محمد ماهر ابو هاشم</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>A2-D2</t>
+          <t>A2-E1</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -6974,12 +6974,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>221047</t>
+          <t>221048</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>احمد محسن محمد ماهر ابو هاشم</t>
+          <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -7001,12 +7001,12 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>221048</t>
+          <t>221049</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
+          <t>ادهم عامر عبدالحافظ احمد محمد</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -7028,12 +7028,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>221049</t>
+          <t>221050</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>ادهم عامر عبدالحافظ احمد محمد</t>
+          <t>اسراء احمد محمد عبد الصادق نور</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -7055,12 +7055,12 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>221050</t>
+          <t>221052</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>اسراء احمد محمد عبد الصادق نور</t>
+          <t>امنيه سلامه عبده محمد</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -7082,12 +7082,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>221052</t>
+          <t>221053</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>امنيه سلامه عبده محمد</t>
+          <t>امينه خالد عوض عفيفى تاج الدين</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -7109,12 +7109,12 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>221053</t>
+          <t>221054</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>امينه خالد عوض عفيفى تاج الدين</t>
+          <t>انجي علاء سعد الدين الشحات السيد</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -7136,12 +7136,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>221054</t>
+          <t>221055</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>انجي علاء سعد الدين الشحات السيد</t>
+          <t>ايلاري هاني سند ماضي</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -7163,12 +7163,12 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>221055</t>
+          <t>221056</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>ايلاري هاني سند ماضي</t>
+          <t>إيريني وجدي عزمي عبدالمسيح</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -7190,12 +7190,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>221056</t>
+          <t>221059</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>إيريني وجدي عزمي عبدالمسيح</t>
+          <t>أحمد عزت مختار عزت</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -7217,12 +7217,12 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>221059</t>
+          <t>221060</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>أحمد عزت مختار عزت</t>
+          <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -7244,12 +7244,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>221060</t>
+          <t>221062</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
+          <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -7271,12 +7271,12 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>221062</t>
+          <t>221063</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
+          <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -7298,12 +7298,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>221063</t>
+          <t>221064</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
+          <t>أكرم مصطفي فتحي محمد</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -7325,12 +7325,12 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>221064</t>
+          <t>221066</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>أكرم مصطفي فتحي محمد</t>
+          <t>أية عبدالسميع محمد سليمان</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -7352,12 +7352,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>221066</t>
+          <t>221067</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>أية عبدالسميع محمد سليمان</t>
+          <t>آيتن أحمد مصطفى محمد مصطفى</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -7379,12 +7379,12 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>221067</t>
+          <t>221068</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>آيتن أحمد مصطفى محمد مصطفى</t>
+          <t>آيه حسن محمد مأمون</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -7406,12 +7406,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>221068</t>
+          <t>221069</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>آيه حسن محمد مأمون</t>
+          <t>بثينه خالد ابراهيم محمد موسى</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -7433,12 +7433,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>221069</t>
+          <t>221070</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>بثينه خالد ابراهيم محمد موسى</t>
+          <t>بسمة علاء حسني زهران</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>221070</t>
+          <t>221071</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>بسمة علاء حسني زهران</t>
+          <t>بسملة وسام صلاح أحمد</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>بسملة وسام صلاح أحمد</t>
+          <t>بسنت احمد شكرالله عبدالباسط</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -7514,12 +7514,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>221072</t>
+          <t>221073</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>بسنت احمد شكرالله عبدالباسط</t>
+          <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -7541,12 +7541,12 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>221073</t>
+          <t>221075</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
+          <t>تسنيم اسامة يوسف نعيم</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -7568,12 +7568,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>221075</t>
+          <t>221076</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>تسنيم اسامة يوسف نعيم</t>
+          <t>تسنيم علاء ناجي عبدالراضي</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -7595,12 +7595,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>221076</t>
+          <t>221077</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>تسنيم علاء ناجي عبدالراضي</t>
+          <t>تقي محمود احمد السمكري</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -7622,12 +7622,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>221077</t>
+          <t>221078</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>تقي محمود احمد السمكري</t>
+          <t>توماس نبيل سامي غطاس</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -7649,12 +7649,12 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>221078</t>
+          <t>221079</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>توماس نبيل سامي غطاس</t>
+          <t>جنا هاني احمد عبد القادر</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -7676,12 +7676,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>221079</t>
+          <t>221080</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>جنا هاني احمد عبد القادر</t>
+          <t>جنة الله علاء الدين أحمد عيد</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -7703,12 +7703,12 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>221080</t>
+          <t>221084</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>جنة الله علاء الدين أحمد عيد</t>
+          <t>جودي احمد السيد سليمان</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -7730,12 +7730,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>221084</t>
+          <t>220748</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>جودي احمد السيد سليمان</t>
+          <t>ملك عمرو على حسن</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>A2-E1</t>
+          <t>A2-E2</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
@@ -7757,12 +7757,12 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>220748</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>ملك عمرو على حسن</t>
+          <t>جوفانا روماني راشد شنوده</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -7784,12 +7784,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>221086</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>جوفانا روماني راشد شنوده</t>
+          <t>جونسي صلاح اسماعيل حجازي</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -7811,12 +7811,12 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>221086</t>
+          <t>221087</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>جونسي صلاح اسماعيل حجازي</t>
+          <t>جونى سامر صفوت فهمى ميخائيل</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -7838,12 +7838,12 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>221087</t>
+          <t>221088</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>جونى سامر صفوت فهمى ميخائيل</t>
+          <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -7865,12 +7865,12 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>221088</t>
+          <t>221089</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
+          <t>حبيبة زكي محمد زكي</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -7892,12 +7892,12 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>221089</t>
+          <t>221090</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>حبيبة زكي محمد زكي</t>
+          <t>حبيبه محمد صابر عبدالعال</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -7919,12 +7919,12 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>221090</t>
+          <t>221091</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>حبيبه محمد صابر عبدالعال</t>
+          <t>حسن احمد حسن الصفتي</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -7946,12 +7946,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>221091</t>
+          <t>221092</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>حسن احمد حسن الصفتي</t>
+          <t>حسن محمد حسن شمس الدين</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -7973,12 +7973,12 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>221092</t>
+          <t>221093</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>حسن محمد حسن شمس الدين</t>
+          <t>حلا احمد محمد محمد فضل الله</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>221093</t>
+          <t>221095</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>حلا احمد محمد محمد فضل الله</t>
+          <t>حمزه هشام بكر ابو القميز</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -8027,12 +8027,12 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>221095</t>
+          <t>221096</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>حمزه هشام بكر ابو القميز</t>
+          <t>حنين طارق محرم شلبي</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -8054,12 +8054,12 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>221096</t>
+          <t>221097</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>حنين طارق محرم شلبي</t>
+          <t>خالد علاء عبد السميع عبدالله الديب</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -8081,12 +8081,12 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>221097</t>
+          <t>221099</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>خالد علاء عبد السميع عبدالله الديب</t>
+          <t>دارين أحمد فرج القاصد</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>221099</t>
+          <t>221100</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>دارين أحمد فرج القاصد</t>
+          <t>دارين السيد مصيلحي مصيلحي</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -8135,12 +8135,12 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>221100</t>
+          <t>221101</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>دارين السيد مصيلحي مصيلحي</t>
+          <t>دارين محمد ابراهيم ماضى</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -8162,12 +8162,12 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>221101</t>
+          <t>221102</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>دارين محمد ابراهيم ماضى</t>
+          <t>دانا أسامة عبدالغني محمد</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -8189,12 +8189,12 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>221102</t>
+          <t>221103</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>دانا أسامة عبدالغني محمد</t>
+          <t>دانه عبداللطيف فؤاد زيان</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -8216,12 +8216,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>221103</t>
+          <t>221104</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>دانه عبداللطيف فؤاد زيان</t>
+          <t>دعاء أشرف أحمد عبد الله</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -8243,12 +8243,12 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>221104</t>
+          <t>221106</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>دعاء أشرف أحمد عبد الله</t>
+          <t>دينا ناجي عبد المنعم الشيخ</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -8270,12 +8270,12 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>221106</t>
+          <t>221108</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>دينا ناجي عبد المنعم الشيخ</t>
+          <t>رانيا عادل طلخان رزق</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -8297,12 +8297,12 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>221108</t>
+          <t>221110</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>رانيا عادل طلخان رزق</t>
+          <t>رفيده أيمن مصطفى النحاس شحاته</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -8324,12 +8324,12 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>221110</t>
+          <t>221111</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>رفيده أيمن مصطفى النحاس شحاته</t>
+          <t>رنا عمرو محمد شرايحي</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -8351,12 +8351,12 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>221111</t>
+          <t>221112</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>رنا عمرو محمد شرايحي</t>
+          <t>رنيم ايمن علي علام</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -8378,12 +8378,12 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>221112</t>
+          <t>221114</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>رنيم ايمن علي علام</t>
+          <t>روان محمد ياسر عبد العال ابو الوفا</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -8405,12 +8405,12 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>221114</t>
+          <t>221116</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>روان محمد ياسر عبد العال ابو الوفا</t>
+          <t>روينا محمد عبدالحكيم الاشموني</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -8432,12 +8432,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>221117</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>روينا محمد عبدالحكيم الاشموني</t>
+          <t>رؤى طارق مرسى محمود</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -8459,12 +8459,12 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>221117</t>
+          <t>221118</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>رؤى طارق مرسى محمود</t>
+          <t>ريم السيد صالح خليل</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -8486,12 +8486,12 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>221118</t>
+          <t>221119</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>ريم السيد صالح خليل</t>
+          <t>زياد شريف حلمي الألفي</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -8513,12 +8513,12 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>221119</t>
+          <t>221120</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>زياد شريف حلمي الألفي</t>
+          <t>سارة علاءالدين احمد محمد</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -8540,12 +8540,12 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>221120</t>
+          <t>221121</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>سارة علاءالدين احمد محمد</t>
+          <t>سارة احمد محمد على خليل</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -8567,12 +8567,12 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>221121</t>
+          <t>220449</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>سارة احمد محمد على خليل</t>
+          <t>حبيبة الله وائل البرماوى</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>A2-E2</t>
+          <t>A2-F1</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -8594,12 +8594,12 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>220449</t>
+          <t>220550</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>حبيبة الله وائل البرماوى</t>
+          <t>شيماء شريف محمد عبد الرحمن احمد</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">

--- a/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
+++ b/reference_data/Y4_B2526_General_&_Special_Surgery_1_A2_reference_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B793A120-1E76-4E4C-BD5A-DCE60F090257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4BEE282-54CE-454C-8AAD-F6B55DB501F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,19 +48,1096 @@
     <t>Source File</t>
   </si>
   <si>
+    <t>180289</t>
+  </si>
+  <si>
+    <t>عبد الرحمن سلامة حنفى</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>A2-A1</t>
+  </si>
+  <si>
+    <t>Y4_B2526_General_&amp;_Special_Surgery_1_A2_reference_data.xlsx</t>
+  </si>
+  <si>
+    <t>200302</t>
+  </si>
+  <si>
+    <t>ساره هانى منصور سيد رزق</t>
+  </si>
+  <si>
+    <t>200502</t>
+  </si>
+  <si>
+    <t>مازن ايمن محمود عبدربه</t>
+  </si>
+  <si>
+    <t>200891</t>
+  </si>
+  <si>
+    <t>احمد جمال القبانى</t>
+  </si>
+  <si>
+    <t>211139</t>
+  </si>
+  <si>
+    <t>احمد يعقوب عمر طرايره</t>
+  </si>
+  <si>
+    <t>211513</t>
+  </si>
+  <si>
+    <t>ايه محمد سعد الدين العدوى</t>
+  </si>
+  <si>
+    <t>211701</t>
+  </si>
+  <si>
+    <t>فادى عبدالله جميل شورى</t>
+  </si>
+  <si>
+    <t>220321</t>
+  </si>
+  <si>
+    <t>احمد عبد الرحمن جابر سالمان</t>
+  </si>
+  <si>
+    <t>220392</t>
+  </si>
+  <si>
+    <t>انس محمد محمد صوابى هيكل</t>
+  </si>
+  <si>
+    <t>220452</t>
+  </si>
+  <si>
+    <t>حبيبه شريف احمد عبدالعليم عبدالحميد</t>
+  </si>
+  <si>
+    <t>220494</t>
+  </si>
+  <si>
+    <t>رودينا تامر محمد الدهان</t>
+  </si>
+  <si>
+    <t>220501</t>
+  </si>
+  <si>
+    <t>ريماس سامر العطائي</t>
+  </si>
+  <si>
+    <t>220516</t>
+  </si>
+  <si>
+    <t>سلمى حسين عبد المنعم عبد الحميد محمد</t>
+  </si>
+  <si>
+    <t>220537</t>
+  </si>
+  <si>
+    <t>شروق هانى مبروك على السيد النجار</t>
+  </si>
+  <si>
+    <t>220577</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد عبداللطيف شهاب</t>
+  </si>
+  <si>
+    <t>220615</t>
+  </si>
+  <si>
+    <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
+  </si>
+  <si>
+    <t>220616</t>
+  </si>
+  <si>
+    <t>غاده احمد احمد احمد الشريف</t>
+  </si>
+  <si>
+    <t>220623</t>
+  </si>
+  <si>
+    <t>فاطمه احمد محمد محمود كرم</t>
+  </si>
+  <si>
+    <t>220624</t>
+  </si>
+  <si>
+    <t>فاطمه السيد محمد فتحى عطيه الله</t>
+  </si>
+  <si>
+    <t>220625</t>
+  </si>
+  <si>
+    <t>فاطمه حموده على عبد الحميد حموده</t>
+  </si>
+  <si>
+    <t>220627</t>
+  </si>
+  <si>
+    <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
+  </si>
+  <si>
+    <t>220628</t>
+  </si>
+  <si>
+    <t>فاطمه محمود محمد امام</t>
+  </si>
+  <si>
+    <t>220629</t>
+  </si>
+  <si>
+    <t>فتحى محمد فتحى السيد عبد الله</t>
+  </si>
+  <si>
+    <t>220630</t>
+  </si>
+  <si>
+    <t>فريده محمود فؤاد محمود</t>
+  </si>
+  <si>
+    <t>220635</t>
+  </si>
+  <si>
+    <t>كريم ايمن محمد مصطفى ابراهيم</t>
+  </si>
+  <si>
+    <t>220636</t>
+  </si>
+  <si>
+    <t>كريم سعيد احمد ابراهيم الحريزى</t>
+  </si>
+  <si>
+    <t>220639</t>
+  </si>
+  <si>
+    <t>كريم مصطفى عبد الرحمن على سعد</t>
+  </si>
+  <si>
+    <t>220645</t>
+  </si>
+  <si>
+    <t>لجين احمد عبد الله البسطويسى</t>
+  </si>
+  <si>
+    <t>220646</t>
+  </si>
+  <si>
+    <t>لجين اشرف جلال عبد الرحمن السمرى</t>
+  </si>
+  <si>
+    <t>220647</t>
+  </si>
+  <si>
+    <t>لوجين السيد محروس اسماعيل</t>
+  </si>
+  <si>
+    <t>A2-A2</t>
+  </si>
+  <si>
+    <t>220648</t>
+  </si>
+  <si>
+    <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
+  </si>
+  <si>
+    <t>220649</t>
+  </si>
+  <si>
+    <t>لؤى على حسين حسن ابو صفيه</t>
+  </si>
+  <si>
+    <t>220651</t>
+  </si>
+  <si>
+    <t>ليلى اشرف وصفى</t>
+  </si>
+  <si>
+    <t>220653</t>
+  </si>
+  <si>
+    <t>ماجد حسنى السيد التلاوى</t>
+  </si>
+  <si>
+    <t>220655</t>
+  </si>
+  <si>
+    <t>مارى مجدى منير عبده</t>
+  </si>
+  <si>
+    <t>220659</t>
+  </si>
+  <si>
+    <t>مالك محمود على محمود زين الدين</t>
+  </si>
+  <si>
+    <t>220661</t>
+  </si>
+  <si>
+    <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
+  </si>
+  <si>
+    <t>220662</t>
+  </si>
+  <si>
+    <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
+  </si>
+  <si>
+    <t>220666</t>
+  </si>
+  <si>
+    <t>محمد احمد فتحى احمد احمد</t>
+  </si>
+  <si>
+    <t>220667</t>
+  </si>
+  <si>
+    <t>محمد اسامه علاء الدين اللو</t>
+  </si>
+  <si>
+    <t>220669</t>
+  </si>
+  <si>
+    <t>محمد السعيد السعيد محمد شعبان</t>
+  </si>
+  <si>
+    <t>220670</t>
+  </si>
+  <si>
+    <t>محمد السعيد مسعد مصطفى حراز</t>
+  </si>
+  <si>
+    <t>220672</t>
+  </si>
+  <si>
+    <t>محمد الشحات على احمد سرور</t>
+  </si>
+  <si>
+    <t>220673</t>
+  </si>
+  <si>
+    <t>محمد أيمن محمد أحمد ناصف</t>
+  </si>
+  <si>
+    <t>220674</t>
+  </si>
+  <si>
+    <t>محمد باسم عبد الكريم محمود</t>
+  </si>
+  <si>
+    <t>220678</t>
+  </si>
+  <si>
+    <t>محمد بهاء عبد الحميد عبد الغفار</t>
+  </si>
+  <si>
+    <t>220679</t>
+  </si>
+  <si>
+    <t>محمد جابر توفيق الشافعى</t>
+  </si>
+  <si>
+    <t>220680</t>
+  </si>
+  <si>
+    <t>محمد حسن جلال عبد المجيد وهدان</t>
+  </si>
+  <si>
+    <t>220683</t>
+  </si>
+  <si>
+    <t>محمد سعيد محمود عبد المنعم محمود</t>
+  </si>
+  <si>
+    <t>220684</t>
+  </si>
+  <si>
+    <t>محمد صبرى جوده عبد الله خضر</t>
+  </si>
+  <si>
+    <t>220685</t>
+  </si>
+  <si>
+    <t>محمد صلاح حسن عبد الله حسن</t>
+  </si>
+  <si>
+    <t>220686</t>
+  </si>
+  <si>
+    <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
+  </si>
+  <si>
+    <t>220687</t>
+  </si>
+  <si>
+    <t>محمد طارق محمد عبد الرحمن العرينى</t>
+  </si>
+  <si>
+    <t>220688</t>
+  </si>
+  <si>
+    <t>محمد عبد الحفيظ عبد الله محمد على</t>
+  </si>
+  <si>
+    <t>220689</t>
+  </si>
+  <si>
+    <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
+  </si>
+  <si>
+    <t>220690</t>
+  </si>
+  <si>
+    <t>محمد عبد النبى عطيه ابو شعيشع</t>
+  </si>
+  <si>
+    <t>220691</t>
+  </si>
+  <si>
+    <t>محمد عبدالهادى عبدالمنعم عمر</t>
+  </si>
+  <si>
+    <t>220693</t>
+  </si>
+  <si>
+    <t>محمد علاء محمد عبد العزيز عبد الله</t>
+  </si>
+  <si>
+    <t>220694</t>
+  </si>
+  <si>
+    <t>محمد على محمد احمد محمد</t>
+  </si>
+  <si>
+    <t>220698</t>
+  </si>
+  <si>
+    <t>محمد محمد احمد الفتيانى</t>
+  </si>
+  <si>
+    <t>A2-B1</t>
+  </si>
+  <si>
+    <t>220700</t>
+  </si>
+  <si>
+    <t>محمد محمد عبد الله التهامي</t>
+  </si>
+  <si>
+    <t>220701</t>
+  </si>
+  <si>
+    <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
+  </si>
+  <si>
+    <t>220702</t>
+  </si>
+  <si>
+    <t>محمد محيى الدين محمد سيد مكاوى</t>
+  </si>
+  <si>
+    <t>220703</t>
+  </si>
+  <si>
+    <t>محمد مختار شعبان هلالى سليمان</t>
+  </si>
+  <si>
+    <t>220705</t>
+  </si>
+  <si>
+    <t>محمد مفرح عبد الباسط عبد الحليم</t>
+  </si>
+  <si>
+    <t>220706</t>
+  </si>
+  <si>
+    <t>محمد وائل محمد العيسوى</t>
+  </si>
+  <si>
+    <t>220707</t>
+  </si>
+  <si>
+    <t>محمد وحيد محمد رزق</t>
+  </si>
+  <si>
+    <t>220708</t>
+  </si>
+  <si>
+    <t>محمد ياسر الشافعى محمد على</t>
+  </si>
+  <si>
+    <t>220709</t>
+  </si>
+  <si>
+    <t>محمد ياسر حامد دياب حمد</t>
+  </si>
+  <si>
+    <t>220710</t>
+  </si>
+  <si>
+    <t>محمود جمال حسين محمد رسلان</t>
+  </si>
+  <si>
+    <t>220711</t>
+  </si>
+  <si>
+    <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
+  </si>
+  <si>
+    <t>220712</t>
+  </si>
+  <si>
+    <t>محمود حسن عبد النبى حسين</t>
+  </si>
+  <si>
+    <t>220714</t>
+  </si>
+  <si>
+    <t>محمود كريم شحاته حسن كرد</t>
+  </si>
+  <si>
+    <t>220717</t>
+  </si>
+  <si>
+    <t>محمود منصور محمود محمد السيد يعقوب</t>
+  </si>
+  <si>
+    <t>220720</t>
+  </si>
+  <si>
+    <t>مروان صبحى ابو الحسن محمد على</t>
+  </si>
+  <si>
+    <t>220721</t>
+  </si>
+  <si>
+    <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
+  </si>
+  <si>
+    <t>220722</t>
+  </si>
+  <si>
+    <t>مروه عبد الحميد على حسن ايوب</t>
+  </si>
+  <si>
+    <t>220723</t>
+  </si>
+  <si>
+    <t>مريم ابراهيم احمد ابراهيم مبارك</t>
+  </si>
+  <si>
+    <t>220724</t>
+  </si>
+  <si>
+    <t>مريم الحسن احمد ابراهيم بيومى</t>
+  </si>
+  <si>
+    <t>220725</t>
+  </si>
+  <si>
+    <t>مريم ايمن عبد الله محمود فخرى</t>
+  </si>
+  <si>
+    <t>220726</t>
+  </si>
+  <si>
+    <t>مريم ايمن فؤاد عبدالستار</t>
+  </si>
+  <si>
+    <t>220727</t>
+  </si>
+  <si>
+    <t>مريم ايهاب ملاك ثابت</t>
+  </si>
+  <si>
+    <t>220729</t>
+  </si>
+  <si>
+    <t>مريم رضا محمد ابراهيم صبره</t>
+  </si>
+  <si>
+    <t>220730</t>
+  </si>
+  <si>
+    <t>مريم شعبان مصباح خليفه</t>
+  </si>
+  <si>
+    <t>220731</t>
+  </si>
+  <si>
+    <t>مريم شفيق صبحى شفيق حنا</t>
+  </si>
+  <si>
+    <t>220732</t>
+  </si>
+  <si>
+    <t>مريم عمرو يحيى عبده مدنى</t>
+  </si>
+  <si>
+    <t>220733</t>
+  </si>
+  <si>
+    <t>مريم محمد احمد فاروق الديب الشريف</t>
+  </si>
+  <si>
+    <t>220734</t>
+  </si>
+  <si>
+    <t>مريم محمد احمد محمد عبد المنعم</t>
+  </si>
+  <si>
+    <t>220735</t>
+  </si>
+  <si>
+    <t>مريم محمد ثروت صايم مصطفى</t>
+  </si>
+  <si>
+    <t>221051</t>
+  </si>
+  <si>
+    <t>اسراء هشام محمد عبد المنعم</t>
+  </si>
+  <si>
+    <t>220736</t>
+  </si>
+  <si>
+    <t>مريم محمد عطيه عبد السلام</t>
+  </si>
+  <si>
+    <t>A2-B2</t>
+  </si>
+  <si>
+    <t>220737</t>
+  </si>
+  <si>
+    <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
+  </si>
+  <si>
+    <t>220740</t>
+  </si>
+  <si>
+    <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
+  </si>
+  <si>
+    <t>220742</t>
+  </si>
+  <si>
+    <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
+  </si>
+  <si>
+    <t>220744</t>
+  </si>
+  <si>
+    <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
+  </si>
+  <si>
+    <t>220745</t>
+  </si>
+  <si>
+    <t>مصطفى محمود مصطفى محمود</t>
+  </si>
+  <si>
+    <t>220746</t>
+  </si>
+  <si>
+    <t>معاذ طاهر محمد شبانه على</t>
+  </si>
+  <si>
+    <t>220747</t>
+  </si>
+  <si>
+    <t>ملك عبدالغنى احمد حسن</t>
+  </si>
+  <si>
+    <t>220749</t>
+  </si>
+  <si>
+    <t>ملك ياسر عبد الوهاب محمد الغندور</t>
+  </si>
+  <si>
+    <t>220751</t>
+  </si>
+  <si>
+    <t>منة الله هانى عبد السميع شكرى</t>
+  </si>
+  <si>
+    <t>220752</t>
+  </si>
+  <si>
+    <t>منصور هانى منصور عبدالله</t>
+  </si>
+  <si>
+    <t>220753</t>
+  </si>
+  <si>
+    <t>منه الله احمد محمد جمعه عثمان</t>
+  </si>
+  <si>
+    <t>220754</t>
+  </si>
+  <si>
+    <t>منه الله محمد صالح محمد النور</t>
+  </si>
+  <si>
+    <t>220755</t>
+  </si>
+  <si>
+    <t>منه الله محمد عبد الرازق سالم غاليه</t>
+  </si>
+  <si>
+    <t>220756</t>
+  </si>
+  <si>
+    <t>منه عبد الوهاب عبدالله مصطفى</t>
+  </si>
+  <si>
+    <t>220758</t>
+  </si>
+  <si>
+    <t>منه محمود محمد احمد</t>
+  </si>
+  <si>
+    <t>220759</t>
+  </si>
+  <si>
+    <t>منى عبد الحميد ناصف سيف</t>
+  </si>
+  <si>
+    <t>220760</t>
+  </si>
+  <si>
+    <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
+  </si>
+  <si>
+    <t>220764</t>
+  </si>
+  <si>
+    <t>مياده سلامه قاسم محمد السيد</t>
+  </si>
+  <si>
+    <t>220765</t>
+  </si>
+  <si>
+    <t>ميار احمد صبحى السيد السيد</t>
+  </si>
+  <si>
+    <t>220767</t>
+  </si>
+  <si>
+    <t>ميار صلاح محمد سليمان سليمان</t>
+  </si>
+  <si>
+    <t>220772</t>
+  </si>
+  <si>
+    <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
+  </si>
+  <si>
+    <t>220773</t>
+  </si>
+  <si>
+    <t>ندى اشرف عبد الله ابراهيم</t>
+  </si>
+  <si>
+    <t>220774</t>
+  </si>
+  <si>
+    <t>ندى اشرف محمد محمد</t>
+  </si>
+  <si>
+    <t>220775</t>
+  </si>
+  <si>
+    <t>ندى حسن السيد احمد عطا الله</t>
+  </si>
+  <si>
+    <t>220776</t>
+  </si>
+  <si>
+    <t>ندى عاطف محمد محمد عبده الشيمى</t>
+  </si>
+  <si>
+    <t>220777</t>
+  </si>
+  <si>
+    <t>ندى على زيد عبد الرحمن</t>
+  </si>
+  <si>
+    <t>220778</t>
+  </si>
+  <si>
+    <t>ندى محمد احمد حامد عامر</t>
+  </si>
+  <si>
+    <t>220779</t>
+  </si>
+  <si>
+    <t>نزار عمرو حسن عبد الغنى</t>
+  </si>
+  <si>
+    <t>A2-C1</t>
+  </si>
+  <si>
+    <t>220780</t>
+  </si>
+  <si>
+    <t>نصر الدين الابراهيم</t>
+  </si>
+  <si>
+    <t>220781</t>
+  </si>
+  <si>
+    <t>نظمى مصطفى نظمى على عبد النبى</t>
+  </si>
+  <si>
+    <t>220782</t>
+  </si>
+  <si>
+    <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
+  </si>
+  <si>
+    <t>220783</t>
+  </si>
+  <si>
+    <t>نهى احمد ابراهيم محمد عيطه</t>
+  </si>
+  <si>
+    <t>220784</t>
+  </si>
+  <si>
+    <t>نهى على عبد الرحمن على</t>
+  </si>
+  <si>
+    <t>220787</t>
+  </si>
+  <si>
+    <t>نور محمد عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>220788</t>
+  </si>
+  <si>
+    <t>نوران اسامه محمد محمود</t>
+  </si>
+  <si>
+    <t>220789</t>
+  </si>
+  <si>
+    <t>نوران فوزى شعبان فوزى علام</t>
+  </si>
+  <si>
+    <t>220790</t>
+  </si>
+  <si>
+    <t>نورهان حسن عبد الرحمن حسن محمد</t>
+  </si>
+  <si>
+    <t>220791</t>
+  </si>
+  <si>
+    <t>نورهان محمد عبد العزيز حسن</t>
+  </si>
+  <si>
+    <t>220792</t>
+  </si>
+  <si>
+    <t>نورهان محمود السيد محمود اللقانى</t>
+  </si>
+  <si>
+    <t>220793</t>
+  </si>
+  <si>
+    <t>نورين احمد عبد الحكيم رضوان</t>
+  </si>
+  <si>
+    <t>220794</t>
+  </si>
+  <si>
+    <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
+  </si>
+  <si>
+    <t>220795</t>
+  </si>
+  <si>
+    <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
+  </si>
+  <si>
+    <t>220796</t>
+  </si>
+  <si>
+    <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
+  </si>
+  <si>
+    <t>220797</t>
+  </si>
+  <si>
+    <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
+  </si>
+  <si>
+    <t>220799</t>
+  </si>
+  <si>
+    <t>هاجر احمد رمضان سعد الفرحاتى</t>
+  </si>
+  <si>
+    <t>220800</t>
+  </si>
+  <si>
+    <t>هاجر عاطف سيد عبد الجيد احمد</t>
+  </si>
+  <si>
+    <t>220801</t>
+  </si>
+  <si>
+    <t>هايدى محمد حسين رفاعى فراج</t>
+  </si>
+  <si>
+    <t>220802</t>
+  </si>
+  <si>
+    <t>هدى مدحت خيرى احمد فرج</t>
+  </si>
+  <si>
+    <t>220803</t>
+  </si>
+  <si>
+    <t>هرمينا عبد الله جاد جرجس</t>
+  </si>
+  <si>
+    <t>220804</t>
+  </si>
+  <si>
+    <t>هنا خليل عبد الرؤف محمد سعيد</t>
+  </si>
+  <si>
+    <t>220805</t>
+  </si>
+  <si>
+    <t>وسام ايمن على الشريف</t>
+  </si>
+  <si>
+    <t>220807</t>
+  </si>
+  <si>
+    <t>وليد ياسر عبد الشافى محمود</t>
+  </si>
+  <si>
+    <t>220808</t>
+  </si>
+  <si>
+    <t>ياسمين عادل السيد الفرغلى حسن</t>
+  </si>
+  <si>
+    <t>220809</t>
+  </si>
+  <si>
+    <t>يحيى احمد محمد عبد الفتاح الزيات</t>
+  </si>
+  <si>
+    <t>220810</t>
+  </si>
+  <si>
+    <t>يحيى محمد يحى على</t>
+  </si>
+  <si>
+    <t>220813</t>
+  </si>
+  <si>
+    <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
+  </si>
+  <si>
+    <t>220814</t>
+  </si>
+  <si>
+    <t>يوسف جلال محمد عبد الفتاح صالح</t>
+  </si>
+  <si>
     <t>220890</t>
   </si>
   <si>
     <t>يوسف حسين ناجي الصرايره</t>
   </si>
   <si>
-    <t>Year 4</t>
-  </si>
-  <si>
-    <t>A1-D1</t>
-  </si>
-  <si>
-    <t>A2.xlsx</t>
+    <t>220815</t>
+  </si>
+  <si>
+    <t>يوسف حمدى احمد طاجن</t>
+  </si>
+  <si>
+    <t>A2-C2</t>
+  </si>
+  <si>
+    <t>220816</t>
+  </si>
+  <si>
+    <t>يوسف عمرو على حفنى ابراهيم</t>
+  </si>
+  <si>
+    <t>220817</t>
+  </si>
+  <si>
+    <t>يوسف فهيم عبد الحميد ابو عزيز</t>
+  </si>
+  <si>
+    <t>220818</t>
+  </si>
+  <si>
+    <t>يوسف محمد رضا جلال احمد سيد احمد</t>
+  </si>
+  <si>
+    <t>220819</t>
+  </si>
+  <si>
+    <t>يوسف محمد محمد السيد البطه</t>
+  </si>
+  <si>
+    <t>220820</t>
+  </si>
+  <si>
+    <t>يوسف محمود محمد ابراهيم</t>
+  </si>
+  <si>
+    <t>220821</t>
+  </si>
+  <si>
+    <t>يوسف مصطفى محمد رسلان</t>
+  </si>
+  <si>
+    <t>220822</t>
+  </si>
+  <si>
+    <t>يوسف مصطفى مصطفى محمد</t>
+  </si>
+  <si>
+    <t>220824</t>
+  </si>
+  <si>
+    <t>يوسف وائل حامد ابراهيم العالم</t>
+  </si>
+  <si>
+    <t>220825</t>
+  </si>
+  <si>
+    <t>يوسف سيد محمد يوسف</t>
+  </si>
+  <si>
+    <t>220826</t>
+  </si>
+  <si>
+    <t>عبد الله خالد احمد باحاذق</t>
+  </si>
+  <si>
+    <t>220827</t>
+  </si>
+  <si>
+    <t>أبوبكر طارق أبوبكر رمضان</t>
+  </si>
+  <si>
+    <t>220829</t>
+  </si>
+  <si>
+    <t>تبارك رائد حسن كميل</t>
+  </si>
+  <si>
+    <t>220830</t>
+  </si>
+  <si>
+    <t>مصطفى محمد على</t>
+  </si>
+  <si>
+    <t>220832</t>
+  </si>
+  <si>
+    <t>احمد عبد الله نعمان محمد</t>
+  </si>
+  <si>
+    <t>220833</t>
+  </si>
+  <si>
+    <t>رغد فيصل عقيل العمايري</t>
+  </si>
+  <si>
+    <t>220834</t>
+  </si>
+  <si>
+    <t>احمد سليمان محمد</t>
+  </si>
+  <si>
+    <t>220838</t>
+  </si>
+  <si>
+    <t>حمزه طارق الطراد</t>
+  </si>
+  <si>
+    <t>220839</t>
+  </si>
+  <si>
+    <t>عزام نبيل يحي العمير</t>
+  </si>
+  <si>
+    <t>220848</t>
+  </si>
+  <si>
+    <t>عبد الله مسعود مصطفى</t>
+  </si>
+  <si>
+    <t>220853</t>
+  </si>
+  <si>
+    <t>قند عدي بدران</t>
+  </si>
+  <si>
+    <t>220856</t>
+  </si>
+  <si>
+    <t>ماسه بلال الدهبي</t>
+  </si>
+  <si>
+    <t>220857</t>
+  </si>
+  <si>
+    <t>محمد عبده علوي محمد</t>
+  </si>
+  <si>
+    <t>220867</t>
+  </si>
+  <si>
+    <t>شهد جمعه على عبد الفتاح</t>
+  </si>
+  <si>
+    <t>220876</t>
+  </si>
+  <si>
+    <t>عبد المهيمن مهند سلمان</t>
+  </si>
+  <si>
+    <t>220878</t>
+  </si>
+  <si>
+    <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
+  </si>
+  <si>
+    <t>220879</t>
+  </si>
+  <si>
+    <t>علي بن محمد بن على المحمد صالح</t>
+  </si>
+  <si>
+    <t>221018</t>
+  </si>
+  <si>
+    <t>رامي احمد الخطيب</t>
+  </si>
+  <si>
+    <t>221335</t>
+  </si>
+  <si>
+    <t>حذيفه طريف القطرنجى</t>
   </si>
   <si>
     <t>220896</t>
@@ -69,6 +1146,9 @@
     <t>احمد السر ميرغني عمر</t>
   </si>
   <si>
+    <t>A2-D1</t>
+  </si>
+  <si>
     <t>220900</t>
   </si>
   <si>
@@ -237,61 +1317,565 @@
     <t>عبدالقادر يوسف عبدالقادر ابوسعدة</t>
   </si>
   <si>
-    <t>180289</t>
-  </si>
-  <si>
-    <t>عبد الرحمن سلامة حنفى</t>
-  </si>
-  <si>
-    <t>A2-A1</t>
-  </si>
-  <si>
-    <t>200302</t>
-  </si>
-  <si>
-    <t>ساره هانى منصور سيد رزق</t>
-  </si>
-  <si>
-    <t>200502</t>
-  </si>
-  <si>
-    <t>مازن ايمن محمود عبدربه</t>
-  </si>
-  <si>
-    <t>200891</t>
-  </si>
-  <si>
-    <t>احمد جمال القبانى</t>
-  </si>
-  <si>
-    <t>211139</t>
-  </si>
-  <si>
-    <t>احمد يعقوب عمر طرايره</t>
-  </si>
-  <si>
-    <t>211513</t>
-  </si>
-  <si>
-    <t>ايه محمد سعد الدين العدوى</t>
-  </si>
-  <si>
-    <t>211701</t>
-  </si>
-  <si>
-    <t>فادى عبدالله جميل شورى</t>
-  </si>
-  <si>
-    <t>220321</t>
-  </si>
-  <si>
-    <t>احمد عبد الرحمن جابر سالمان</t>
-  </si>
-  <si>
-    <t>220392</t>
-  </si>
-  <si>
-    <t>انس محمد محمد صوابى هيكل</t>
+    <t>220762</t>
+  </si>
+  <si>
+    <t>مؤيد وليد علي كرجه</t>
+  </si>
+  <si>
+    <t>A2-D2</t>
+  </si>
+  <si>
+    <t>220845</t>
+  </si>
+  <si>
+    <t>ريان تاج الدين عبد الله أحمد</t>
+  </si>
+  <si>
+    <t>220889</t>
+  </si>
+  <si>
+    <t>سجى السر ميرغني عمر</t>
+  </si>
+  <si>
+    <t>220969</t>
+  </si>
+  <si>
+    <t>نهال حسام زهره</t>
+  </si>
+  <si>
+    <t>220970</t>
+  </si>
+  <si>
+    <t>مبارك حسن ابراهيم</t>
+  </si>
+  <si>
+    <t>220971</t>
+  </si>
+  <si>
+    <t>فراس حسين نعيم الكوز</t>
+  </si>
+  <si>
+    <t>220972</t>
+  </si>
+  <si>
+    <t>عاصم عبدالحكيم محمد سعيد ناصر</t>
+  </si>
+  <si>
+    <t>220974</t>
+  </si>
+  <si>
+    <t>مايا رضوان احمد سالم</t>
+  </si>
+  <si>
+    <t>220979</t>
+  </si>
+  <si>
+    <t>محمد حسين محمد الحامد</t>
+  </si>
+  <si>
+    <t>220983</t>
+  </si>
+  <si>
+    <t>حسام محمد احمد الكوز</t>
+  </si>
+  <si>
+    <t>220986</t>
+  </si>
+  <si>
+    <t>هاشم احمد صالح الشرجي</t>
+  </si>
+  <si>
+    <t>220989</t>
+  </si>
+  <si>
+    <t>مشاري محمد يحيي الكحلاني</t>
+  </si>
+  <si>
+    <t>220991</t>
+  </si>
+  <si>
+    <t>عمر حسام الدين الزيبق</t>
+  </si>
+  <si>
+    <t>220992</t>
+  </si>
+  <si>
+    <t>يحيى عبدالغني بني</t>
+  </si>
+  <si>
+    <t>220996</t>
+  </si>
+  <si>
+    <t>صفية وفائي</t>
+  </si>
+  <si>
+    <t>220997</t>
+  </si>
+  <si>
+    <t>احمد عماد الدين محمد عبد الرحمن</t>
+  </si>
+  <si>
+    <t>221002</t>
+  </si>
+  <si>
+    <t>هاجر مؤيد السلوم</t>
+  </si>
+  <si>
+    <t>221006</t>
+  </si>
+  <si>
+    <t>فهد هارون ادم محمد</t>
+  </si>
+  <si>
+    <t>221008</t>
+  </si>
+  <si>
+    <t>وفاق عبدالوهاب محمد ابراهيم</t>
+  </si>
+  <si>
+    <t>221012</t>
+  </si>
+  <si>
+    <t>اسامه الشيخ احمد الامام</t>
+  </si>
+  <si>
+    <t>221015</t>
+  </si>
+  <si>
+    <t>وفاء حسين ميرغنى محمود</t>
+  </si>
+  <si>
+    <t>221016</t>
+  </si>
+  <si>
+    <t>ايمن ناصر محمد ابو ديه</t>
+  </si>
+  <si>
+    <t>221020</t>
+  </si>
+  <si>
+    <t>مي سلوم سالم لم يصعد</t>
+  </si>
+  <si>
+    <t>221021</t>
+  </si>
+  <si>
+    <t>عثمان ابوالقاسم احمد حسن</t>
+  </si>
+  <si>
+    <t>221023</t>
+  </si>
+  <si>
+    <t>مرام عبدالله محمد حامد</t>
+  </si>
+  <si>
+    <t>221025</t>
+  </si>
+  <si>
+    <t>بتول محمد يوسف</t>
+  </si>
+  <si>
+    <t>221029</t>
+  </si>
+  <si>
+    <t>معتصم توفيق محمد بكرون</t>
+  </si>
+  <si>
+    <t>221035</t>
+  </si>
+  <si>
+    <t>محمد بدر احمد علي مول الدويله</t>
+  </si>
+  <si>
+    <t>221036</t>
+  </si>
+  <si>
+    <t>عبد السلام وليد عبد السلام ابو حلوان</t>
+  </si>
+  <si>
+    <t>221037</t>
+  </si>
+  <si>
+    <t>رنا بنت عبد الغني بن بكر برناوي</t>
+  </si>
+  <si>
+    <t>221040</t>
+  </si>
+  <si>
+    <t>محمد الطاهر محمد الطاهر</t>
+  </si>
+  <si>
+    <t>221046</t>
+  </si>
+  <si>
+    <t>احمد مجدي امين محمد</t>
+  </si>
+  <si>
+    <t>221047</t>
+  </si>
+  <si>
+    <t>احمد محسن محمد ماهر ابو هاشم</t>
+  </si>
+  <si>
+    <t>A2-E1</t>
+  </si>
+  <si>
+    <t>221048</t>
+  </si>
+  <si>
+    <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
+  </si>
+  <si>
+    <t>221049</t>
+  </si>
+  <si>
+    <t>ادهم عامر عبدالحافظ احمد محمد</t>
+  </si>
+  <si>
+    <t>221050</t>
+  </si>
+  <si>
+    <t>اسراء احمد محمد عبد الصادق نور</t>
+  </si>
+  <si>
+    <t>221052</t>
+  </si>
+  <si>
+    <t>امنيه سلامه عبده محمد</t>
+  </si>
+  <si>
+    <t>221053</t>
+  </si>
+  <si>
+    <t>امينه خالد عوض عفيفى تاج الدين</t>
+  </si>
+  <si>
+    <t>221054</t>
+  </si>
+  <si>
+    <t>انجي علاء سعد الدين الشحات السيد</t>
+  </si>
+  <si>
+    <t>221055</t>
+  </si>
+  <si>
+    <t>ايلاري هاني سند ماضي</t>
+  </si>
+  <si>
+    <t>221056</t>
+  </si>
+  <si>
+    <t>إيريني وجدي عزمي عبدالمسيح</t>
+  </si>
+  <si>
+    <t>221059</t>
+  </si>
+  <si>
+    <t>أحمد عزت مختار عزت</t>
+  </si>
+  <si>
+    <t>221060</t>
+  </si>
+  <si>
+    <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
+  </si>
+  <si>
+    <t>221062</t>
+  </si>
+  <si>
+    <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
+  </si>
+  <si>
+    <t>221063</t>
+  </si>
+  <si>
+    <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
+  </si>
+  <si>
+    <t>221064</t>
+  </si>
+  <si>
+    <t>أكرم مصطفي فتحي محمد</t>
+  </si>
+  <si>
+    <t>221066</t>
+  </si>
+  <si>
+    <t>أية عبدالسميع محمد سليمان</t>
+  </si>
+  <si>
+    <t>221067</t>
+  </si>
+  <si>
+    <t>آيتن أحمد مصطفى محمد مصطفى</t>
+  </si>
+  <si>
+    <t>221068</t>
+  </si>
+  <si>
+    <t>آيه حسن محمد مأمون</t>
+  </si>
+  <si>
+    <t>221069</t>
+  </si>
+  <si>
+    <t>بثينه خالد ابراهيم محمد موسى</t>
+  </si>
+  <si>
+    <t>221070</t>
+  </si>
+  <si>
+    <t>بسمة علاء حسني زهران</t>
+  </si>
+  <si>
+    <t>221071</t>
+  </si>
+  <si>
+    <t>بسملة وسام صلاح أحمد</t>
+  </si>
+  <si>
+    <t>221072</t>
+  </si>
+  <si>
+    <t>بسنت احمد شكرالله عبدالباسط</t>
+  </si>
+  <si>
+    <t>221073</t>
+  </si>
+  <si>
+    <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
+  </si>
+  <si>
+    <t>221075</t>
+  </si>
+  <si>
+    <t>تسنيم اسامة يوسف نعيم</t>
+  </si>
+  <si>
+    <t>221076</t>
+  </si>
+  <si>
+    <t>تسنيم علاء ناجي عبدالراضي</t>
+  </si>
+  <si>
+    <t>221077</t>
+  </si>
+  <si>
+    <t>تقي محمود احمد السمكري</t>
+  </si>
+  <si>
+    <t>221078</t>
+  </si>
+  <si>
+    <t>توماس نبيل سامي غطاس</t>
+  </si>
+  <si>
+    <t>221079</t>
+  </si>
+  <si>
+    <t>جنا هاني احمد عبد القادر</t>
+  </si>
+  <si>
+    <t>221080</t>
+  </si>
+  <si>
+    <t>جنة الله علاء الدين أحمد عيد</t>
+  </si>
+  <si>
+    <t>221084</t>
+  </si>
+  <si>
+    <t>جودي احمد السيد سليمان</t>
+  </si>
+  <si>
+    <t>220748</t>
+  </si>
+  <si>
+    <t>ملك عمرو على حسن</t>
+  </si>
+  <si>
+    <t>A2-E2</t>
+  </si>
+  <si>
+    <t>221085</t>
+  </si>
+  <si>
+    <t>جوفانا روماني راشد شنوده</t>
+  </si>
+  <si>
+    <t>221086</t>
+  </si>
+  <si>
+    <t>جونسي صلاح اسماعيل حجازي</t>
+  </si>
+  <si>
+    <t>221087</t>
+  </si>
+  <si>
+    <t>جونى سامر صفوت فهمى ميخائيل</t>
+  </si>
+  <si>
+    <t>221088</t>
+  </si>
+  <si>
+    <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
+  </si>
+  <si>
+    <t>221089</t>
+  </si>
+  <si>
+    <t>حبيبة زكي محمد زكي</t>
+  </si>
+  <si>
+    <t>221090</t>
+  </si>
+  <si>
+    <t>حبيبه محمد صابر عبدالعال</t>
+  </si>
+  <si>
+    <t>221091</t>
+  </si>
+  <si>
+    <t>حسن احمد حسن الصفتي</t>
+  </si>
+  <si>
+    <t>221092</t>
+  </si>
+  <si>
+    <t>حسن محمد حسن شمس الدين</t>
+  </si>
+  <si>
+    <t>221093</t>
+  </si>
+  <si>
+    <t>حلا احمد محمد محمد فضل الله</t>
+  </si>
+  <si>
+    <t>221095</t>
+  </si>
+  <si>
+    <t>حمزه هشام بكر ابو القميز</t>
+  </si>
+  <si>
+    <t>221096</t>
+  </si>
+  <si>
+    <t>حنين طارق محرم شلبي</t>
+  </si>
+  <si>
+    <t>221097</t>
+  </si>
+  <si>
+    <t>خالد علاء عبد السميع عبدالله الديب</t>
+  </si>
+  <si>
+    <t>221099</t>
+  </si>
+  <si>
+    <t>دارين أحمد فرج القاصد</t>
+  </si>
+  <si>
+    <t>221100</t>
+  </si>
+  <si>
+    <t>دارين السيد مصيلحي مصيلحي</t>
+  </si>
+  <si>
+    <t>221101</t>
+  </si>
+  <si>
+    <t>دارين محمد ابراهيم ماضى</t>
+  </si>
+  <si>
+    <t>221102</t>
+  </si>
+  <si>
+    <t>دانا أسامة عبدالغني محمد</t>
+  </si>
+  <si>
+    <t>221103</t>
+  </si>
+  <si>
+    <t>دانه عبداللطيف فؤاد زيان</t>
+  </si>
+  <si>
+    <t>221104</t>
+  </si>
+  <si>
+    <t>دعاء أشرف أحمد عبد الله</t>
+  </si>
+  <si>
+    <t>221106</t>
+  </si>
+  <si>
+    <t>دينا ناجي عبد المنعم الشيخ</t>
+  </si>
+  <si>
+    <t>221108</t>
+  </si>
+  <si>
+    <t>رانيا عادل طلخان رزق</t>
+  </si>
+  <si>
+    <t>221110</t>
+  </si>
+  <si>
+    <t>رفيده أيمن مصطفى النحاس شحاته</t>
+  </si>
+  <si>
+    <t>221111</t>
+  </si>
+  <si>
+    <t>رنا عمرو محمد شرايحي</t>
+  </si>
+  <si>
+    <t>221112</t>
+  </si>
+  <si>
+    <t>رنيم ايمن علي علام</t>
+  </si>
+  <si>
+    <t>221114</t>
+  </si>
+  <si>
+    <t>روان محمد ياسر عبد العال ابو الوفا</t>
+  </si>
+  <si>
+    <t>221116</t>
+  </si>
+  <si>
+    <t>روينا محمد عبدالحكيم الاشموني</t>
+  </si>
+  <si>
+    <t>221117</t>
+  </si>
+  <si>
+    <t>رؤى طارق مرسى محمود</t>
+  </si>
+  <si>
+    <t>221118</t>
+  </si>
+  <si>
+    <t>ريم السيد صالح خليل</t>
+  </si>
+  <si>
+    <t>221119</t>
+  </si>
+  <si>
+    <t>زياد شريف حلمي الألفي</t>
+  </si>
+  <si>
+    <t>221120</t>
+  </si>
+  <si>
+    <t>سارة علاءالدين احمد محمد</t>
+  </si>
+  <si>
+    <t>221121</t>
+  </si>
+  <si>
+    <t>سارة احمد محمد على خليل</t>
   </si>
   <si>
     <t>220449</t>
@@ -300,34 +1884,7 @@
     <t>حبيبة الله وائل البرماوى</t>
   </si>
   <si>
-    <t>220452</t>
-  </si>
-  <si>
-    <t>حبيبه شريف احمد عبدالعليم عبدالحميد</t>
-  </si>
-  <si>
-    <t>220494</t>
-  </si>
-  <si>
-    <t>رودينا تامر محمد الدهان</t>
-  </si>
-  <si>
-    <t>220501</t>
-  </si>
-  <si>
-    <t>ريماس سامر العطائي</t>
-  </si>
-  <si>
-    <t>220516</t>
-  </si>
-  <si>
-    <t>سلمى حسين عبد المنعم عبد الحميد محمد</t>
-  </si>
-  <si>
-    <t>220537</t>
-  </si>
-  <si>
-    <t>شروق هانى مبروك على السيد النجار</t>
+    <t>A2-F1</t>
   </si>
   <si>
     <t>220550</t>
@@ -336,901 +1893,184 @@
     <t>شيماء شريف محمد عبد الرحمن احمد</t>
   </si>
   <si>
-    <t>220577</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد عبداللطيف شهاب</t>
-  </si>
-  <si>
-    <t>220615</t>
-  </si>
-  <si>
-    <t>غاده ابو العلا فتحي ابو العلا ابو الروس</t>
-  </si>
-  <si>
-    <t>220616</t>
-  </si>
-  <si>
-    <t>غاده احمد احمد احمد الشريف</t>
-  </si>
-  <si>
-    <t>220623</t>
-  </si>
-  <si>
-    <t>فاطمه احمد محمد محمود كرم</t>
-  </si>
-  <si>
-    <t>220624</t>
-  </si>
-  <si>
-    <t>فاطمه السيد محمد فتحى عطيه الله</t>
-  </si>
-  <si>
-    <t>220625</t>
-  </si>
-  <si>
-    <t>فاطمه حموده على عبد الحميد حموده</t>
-  </si>
-  <si>
-    <t>220627</t>
-  </si>
-  <si>
-    <t>فاطمه عمرو السيد ابراهيم عبد الله</t>
-  </si>
-  <si>
-    <t>220628</t>
-  </si>
-  <si>
-    <t>فاطمه محمود محمد امام</t>
-  </si>
-  <si>
-    <t>220629</t>
-  </si>
-  <si>
-    <t>فتحى محمد فتحى السيد عبد الله</t>
-  </si>
-  <si>
-    <t>220630</t>
-  </si>
-  <si>
-    <t>فريده محمود فؤاد محمود</t>
-  </si>
-  <si>
-    <t>220635</t>
-  </si>
-  <si>
-    <t>كريم ايمن محمد مصطفى ابراهيم</t>
-  </si>
-  <si>
-    <t>220636</t>
-  </si>
-  <si>
-    <t>كريم سعيد احمد ابراهيم الحريزى</t>
-  </si>
-  <si>
-    <t>220639</t>
-  </si>
-  <si>
-    <t>كريم مصطفى عبد الرحمن على سعد</t>
-  </si>
-  <si>
-    <t>220645</t>
-  </si>
-  <si>
-    <t>لجين احمد عبد الله البسطويسى</t>
-  </si>
-  <si>
-    <t>220646</t>
-  </si>
-  <si>
-    <t>لجين اشرف جلال عبد الرحمن السمرى</t>
-  </si>
-  <si>
-    <t>220647</t>
-  </si>
-  <si>
-    <t>لوجين السيد محروس اسماعيل</t>
-  </si>
-  <si>
-    <t>A2-A2</t>
-  </si>
-  <si>
-    <t>220648</t>
-  </si>
-  <si>
-    <t>لؤى اكرم عبد الله عبد الفتاح عمر</t>
-  </si>
-  <si>
-    <t>220649</t>
-  </si>
-  <si>
-    <t>لؤى على حسين حسن ابو صفيه</t>
-  </si>
-  <si>
-    <t>220651</t>
-  </si>
-  <si>
-    <t>ليلى اشرف وصفى</t>
-  </si>
-  <si>
-    <t>220653</t>
-  </si>
-  <si>
-    <t>ماجد حسنى السيد التلاوى</t>
-  </si>
-  <si>
-    <t>220655</t>
-  </si>
-  <si>
-    <t>مارى مجدى منير عبده</t>
-  </si>
-  <si>
-    <t>220659</t>
-  </si>
-  <si>
-    <t>مالك محمود على محمود زين الدين</t>
-  </si>
-  <si>
-    <t>220661</t>
-  </si>
-  <si>
-    <t>مبارك السيد إبراهيم بسطويسى جاد الله</t>
-  </si>
-  <si>
-    <t>220662</t>
-  </si>
-  <si>
-    <t>مجدى عزوز سعيد عطوه عطيه البنا</t>
-  </si>
-  <si>
-    <t>220666</t>
-  </si>
-  <si>
-    <t>محمد احمد فتحى احمد احمد</t>
-  </si>
-  <si>
-    <t>220667</t>
-  </si>
-  <si>
-    <t>محمد اسامه علاء الدين اللو</t>
-  </si>
-  <si>
-    <t>220669</t>
-  </si>
-  <si>
-    <t>محمد السعيد السعيد محمد شعبان</t>
-  </si>
-  <si>
-    <t>220670</t>
-  </si>
-  <si>
-    <t>محمد السعيد مسعد مصطفى حراز</t>
-  </si>
-  <si>
-    <t>220672</t>
-  </si>
-  <si>
-    <t>محمد الشحات على احمد سرور</t>
-  </si>
-  <si>
-    <t>220673</t>
-  </si>
-  <si>
-    <t>محمد أيمن محمد أحمد ناصف</t>
-  </si>
-  <si>
-    <t>220674</t>
-  </si>
-  <si>
-    <t>محمد باسم عبد الكريم محمود</t>
-  </si>
-  <si>
-    <t>220678</t>
-  </si>
-  <si>
-    <t>محمد بهاء عبد الحميد عبد الغفار</t>
-  </si>
-  <si>
-    <t>220679</t>
-  </si>
-  <si>
-    <t>محمد جابر توفيق الشافعى</t>
-  </si>
-  <si>
-    <t>220680</t>
-  </si>
-  <si>
-    <t>محمد حسن جلال عبد المجيد وهدان</t>
-  </si>
-  <si>
-    <t>220683</t>
-  </si>
-  <si>
-    <t>محمد سعيد محمود عبد المنعم محمود</t>
-  </si>
-  <si>
-    <t>220684</t>
-  </si>
-  <si>
-    <t>محمد صبرى جوده عبد الله خضر</t>
-  </si>
-  <si>
-    <t>220685</t>
-  </si>
-  <si>
-    <t>محمد صلاح حسن عبد الله حسن</t>
-  </si>
-  <si>
-    <t>220686</t>
-  </si>
-  <si>
-    <t>محمد ضياء الدين محمد شوقى السيد ابراهيم موسى</t>
-  </si>
-  <si>
-    <t>220687</t>
-  </si>
-  <si>
-    <t>محمد طارق محمد عبد الرحمن العرينى</t>
-  </si>
-  <si>
-    <t>220688</t>
-  </si>
-  <si>
-    <t>محمد عبد الحفيظ عبد الله محمد على</t>
-  </si>
-  <si>
-    <t>220689</t>
-  </si>
-  <si>
-    <t>محمد عبد الغفور صبحى عبد الغفور نصير</t>
-  </si>
-  <si>
-    <t>220690</t>
-  </si>
-  <si>
-    <t>محمد عبد النبى عطيه ابو شعيشع</t>
-  </si>
-  <si>
-    <t>220691</t>
-  </si>
-  <si>
-    <t>محمد عبدالهادى عبدالمنعم عمر</t>
-  </si>
-  <si>
-    <t>220693</t>
-  </si>
-  <si>
-    <t>محمد علاء محمد عبد العزيز عبد الله</t>
-  </si>
-  <si>
-    <t>220694</t>
-  </si>
-  <si>
-    <t>محمد على محمد احمد محمد</t>
-  </si>
-  <si>
-    <t>220698</t>
-  </si>
-  <si>
-    <t>محمد محمد احمد الفتيانى</t>
-  </si>
-  <si>
-    <t>A2-B1</t>
-  </si>
-  <si>
-    <t>220700</t>
-  </si>
-  <si>
-    <t>محمد محمد عبد الله التهامي</t>
-  </si>
-  <si>
-    <t>220701</t>
-  </si>
-  <si>
-    <t>محمد محمد عبد الونيس عبد التواب حسن القارب</t>
-  </si>
-  <si>
-    <t>220702</t>
-  </si>
-  <si>
-    <t>محمد محيى الدين محمد سيد مكاوى</t>
-  </si>
-  <si>
-    <t>220703</t>
-  </si>
-  <si>
-    <t>محمد مختار شعبان هلالى سليمان</t>
-  </si>
-  <si>
-    <t>220705</t>
-  </si>
-  <si>
-    <t>محمد مفرح عبد الباسط عبد الحليم</t>
-  </si>
-  <si>
-    <t>220706</t>
-  </si>
-  <si>
-    <t>محمد وائل محمد العيسوى</t>
-  </si>
-  <si>
-    <t>220707</t>
-  </si>
-  <si>
-    <t>محمد وحيد محمد رزق</t>
-  </si>
-  <si>
-    <t>220708</t>
-  </si>
-  <si>
-    <t>محمد ياسر الشافعى محمد على</t>
-  </si>
-  <si>
-    <t>220709</t>
-  </si>
-  <si>
-    <t>محمد ياسر حامد دياب حمد</t>
-  </si>
-  <si>
-    <t>220710</t>
-  </si>
-  <si>
-    <t>محمود جمال حسين محمد رسلان</t>
-  </si>
-  <si>
-    <t>220711</t>
-  </si>
-  <si>
-    <t>مصطفى احمد عبد الخالق عبد العزيز عطعوط</t>
-  </si>
-  <si>
-    <t>220712</t>
-  </si>
-  <si>
-    <t>محمود حسن عبد النبى حسين</t>
-  </si>
-  <si>
-    <t>220714</t>
-  </si>
-  <si>
-    <t>محمود كريم شحاته حسن كرد</t>
-  </si>
-  <si>
-    <t>220717</t>
-  </si>
-  <si>
-    <t>محمود منصور محمود محمد السيد يعقوب</t>
-  </si>
-  <si>
-    <t>220720</t>
-  </si>
-  <si>
-    <t>مروان صبحى ابو الحسن محمد على</t>
-  </si>
-  <si>
-    <t>220721</t>
-  </si>
-  <si>
-    <t>مروان وليد عبدالمنعم عبد القادر ادريس</t>
-  </si>
-  <si>
-    <t>220722</t>
-  </si>
-  <si>
-    <t>مروه عبد الحميد على حسن ايوب</t>
-  </si>
-  <si>
-    <t>220723</t>
-  </si>
-  <si>
-    <t>مريم ابراهيم احمد ابراهيم مبارك</t>
-  </si>
-  <si>
-    <t>220724</t>
-  </si>
-  <si>
-    <t>مريم الحسن احمد ابراهيم بيومى</t>
-  </si>
-  <si>
-    <t>220725</t>
-  </si>
-  <si>
-    <t>مريم ايمن عبد الله محمود فخرى</t>
-  </si>
-  <si>
-    <t>220726</t>
-  </si>
-  <si>
-    <t>مريم ايمن فؤاد عبدالستار</t>
-  </si>
-  <si>
-    <t>220727</t>
-  </si>
-  <si>
-    <t>مريم ايهاب ملاك ثابت</t>
-  </si>
-  <si>
-    <t>220729</t>
-  </si>
-  <si>
-    <t>مريم رضا محمد ابراهيم صبره</t>
-  </si>
-  <si>
-    <t>220730</t>
-  </si>
-  <si>
-    <t>مريم شعبان مصباح خليفه</t>
-  </si>
-  <si>
-    <t>220731</t>
-  </si>
-  <si>
-    <t>مريم شفيق صبحى شفيق حنا</t>
-  </si>
-  <si>
-    <t>220732</t>
-  </si>
-  <si>
-    <t>مريم عمرو يحيى عبده مدنى</t>
-  </si>
-  <si>
-    <t>220733</t>
-  </si>
-  <si>
-    <t>مريم محمد احمد فاروق الديب الشريف</t>
-  </si>
-  <si>
-    <t>220734</t>
-  </si>
-  <si>
-    <t>مريم محمد احمد محمد عبد المنعم</t>
-  </si>
-  <si>
-    <t>220735</t>
-  </si>
-  <si>
-    <t>مريم محمد ثروت صايم مصطفى</t>
-  </si>
-  <si>
-    <t>220736</t>
-  </si>
-  <si>
-    <t>مريم محمد عطيه عبد السلام</t>
-  </si>
-  <si>
-    <t>A2-B2</t>
-  </si>
-  <si>
-    <t>220737</t>
-  </si>
-  <si>
-    <t>مريم محمد محسن عبد الحافظ عبد العظيم</t>
-  </si>
-  <si>
-    <t>220740</t>
-  </si>
-  <si>
-    <t>مصطفى امجد عبد الحليم عبد اللطيف شعبان</t>
-  </si>
-  <si>
-    <t>220742</t>
-  </si>
-  <si>
-    <t>مصطفى عبد الفتاح محمد محمود عبد الفتاح</t>
-  </si>
-  <si>
-    <t>220744</t>
-  </si>
-  <si>
-    <t>مصطفى محمد عبد الله حواش احمد شلبى</t>
-  </si>
-  <si>
-    <t>220745</t>
-  </si>
-  <si>
-    <t>مصطفى محمود مصطفى محمود</t>
-  </si>
-  <si>
-    <t>220746</t>
-  </si>
-  <si>
-    <t>معاذ طاهر محمد شبانه على</t>
-  </si>
-  <si>
-    <t>220747</t>
-  </si>
-  <si>
-    <t>ملك عبدالغنى احمد حسن</t>
-  </si>
-  <si>
-    <t>220748</t>
-  </si>
-  <si>
-    <t>ملك عمرو على حسن</t>
-  </si>
-  <si>
-    <t>220749</t>
-  </si>
-  <si>
-    <t>ملك ياسر عبد الوهاب محمد الغندور</t>
-  </si>
-  <si>
-    <t>220751</t>
-  </si>
-  <si>
-    <t>منة الله هانى عبد السميع شكرى</t>
-  </si>
-  <si>
-    <t>220752</t>
-  </si>
-  <si>
-    <t>منصور هانى منصور عبدالله</t>
-  </si>
-  <si>
-    <t>220753</t>
-  </si>
-  <si>
-    <t>منه الله احمد محمد جمعه عثمان</t>
-  </si>
-  <si>
-    <t>220754</t>
-  </si>
-  <si>
-    <t>منه الله محمد صالح محمد النور</t>
-  </si>
-  <si>
-    <t>220755</t>
-  </si>
-  <si>
-    <t>منه الله محمد عبد الرازق سالم غاليه</t>
-  </si>
-  <si>
-    <t>220756</t>
-  </si>
-  <si>
-    <t>منه عبد الوهاب عبدالله مصطفى</t>
-  </si>
-  <si>
-    <t>220758</t>
-  </si>
-  <si>
-    <t>منه محمود محمد احمد</t>
-  </si>
-  <si>
-    <t>220759</t>
-  </si>
-  <si>
-    <t>منى عبد الحميد ناصف سيف</t>
-  </si>
-  <si>
-    <t>220760</t>
-  </si>
-  <si>
-    <t>مهند ابراهيم محمود عبد اللطيف السيد صقر</t>
-  </si>
-  <si>
-    <t>220762</t>
-  </si>
-  <si>
-    <t>مؤيد وليد علي كرجه</t>
-  </si>
-  <si>
-    <t>220764</t>
-  </si>
-  <si>
-    <t>مياده سلامه قاسم محمد السيد</t>
-  </si>
-  <si>
-    <t>220765</t>
-  </si>
-  <si>
-    <t>ميار احمد صبحى السيد السيد</t>
-  </si>
-  <si>
-    <t>220767</t>
-  </si>
-  <si>
-    <t>ميار صلاح محمد سليمان سليمان</t>
-  </si>
-  <si>
-    <t>220772</t>
-  </si>
-  <si>
-    <t>نجلاء خالد احمد عبد الحميد عبد الواحد</t>
-  </si>
-  <si>
-    <t>220773</t>
-  </si>
-  <si>
-    <t>ندى اشرف عبد الله ابراهيم</t>
-  </si>
-  <si>
-    <t>220774</t>
-  </si>
-  <si>
-    <t>ندى اشرف محمد محمد</t>
-  </si>
-  <si>
-    <t>220775</t>
-  </si>
-  <si>
-    <t>ندى حسن السيد احمد عطا الله</t>
-  </si>
-  <si>
-    <t>220776</t>
-  </si>
-  <si>
-    <t>ندى عاطف محمد محمد عبده الشيمى</t>
-  </si>
-  <si>
-    <t>220777</t>
-  </si>
-  <si>
-    <t>ندى على زيد عبد الرحمن</t>
-  </si>
-  <si>
-    <t>220778</t>
-  </si>
-  <si>
-    <t>ندى محمد احمد حامد عامر</t>
-  </si>
-  <si>
-    <t>220779</t>
-  </si>
-  <si>
-    <t>نزار عمرو حسن عبد الغنى</t>
-  </si>
-  <si>
-    <t>A2-C1</t>
-  </si>
-  <si>
-    <t>220780</t>
-  </si>
-  <si>
-    <t>نصر الدين الابراهيم</t>
-  </si>
-  <si>
-    <t>220781</t>
-  </si>
-  <si>
-    <t>نظمى مصطفى نظمى على عبد النبى</t>
-  </si>
-  <si>
-    <t>220782</t>
-  </si>
-  <si>
-    <t>نفيسه محمد محمود عبد الوهاب عبد الفتاح</t>
-  </si>
-  <si>
-    <t>220783</t>
-  </si>
-  <si>
-    <t>نهى احمد ابراهيم محمد عيطه</t>
-  </si>
-  <si>
-    <t>220784</t>
-  </si>
-  <si>
-    <t>نهى على عبد الرحمن على</t>
-  </si>
-  <si>
-    <t>220787</t>
-  </si>
-  <si>
-    <t>نور محمد عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>220788</t>
-  </si>
-  <si>
-    <t>نوران اسامه محمد محمود</t>
-  </si>
-  <si>
-    <t>220789</t>
-  </si>
-  <si>
-    <t>نوران فوزى شعبان فوزى علام</t>
-  </si>
-  <si>
-    <t>220790</t>
-  </si>
-  <si>
-    <t>نورهان حسن عبد الرحمن حسن محمد</t>
-  </si>
-  <si>
-    <t>220791</t>
-  </si>
-  <si>
-    <t>نورهان محمد عبد العزيز حسن</t>
-  </si>
-  <si>
-    <t>220792</t>
-  </si>
-  <si>
-    <t>نورهان محمود السيد محمود اللقانى</t>
-  </si>
-  <si>
-    <t>220793</t>
-  </si>
-  <si>
-    <t>نورين احمد عبد الحكيم رضوان</t>
-  </si>
-  <si>
-    <t>220794</t>
-  </si>
-  <si>
-    <t>نورين احمد عوده سليمان محمد الشرقاوى</t>
-  </si>
-  <si>
-    <t>220795</t>
-  </si>
-  <si>
-    <t>نيرمين ياسر عبد الجواد احمد عبد الجواد</t>
-  </si>
-  <si>
-    <t>220796</t>
-  </si>
-  <si>
-    <t>نيره فوزى فؤاد عبد المنعم ابراهيم</t>
-  </si>
-  <si>
-    <t>220797</t>
-  </si>
-  <si>
-    <t>نيفين احمد سعيد عبد الرحمن الليثى</t>
-  </si>
-  <si>
-    <t>220799</t>
-  </si>
-  <si>
-    <t>هاجر احمد رمضان سعد الفرحاتى</t>
-  </si>
-  <si>
-    <t>220800</t>
-  </si>
-  <si>
-    <t>هاجر عاطف سيد عبد الجيد احمد</t>
-  </si>
-  <si>
-    <t>220801</t>
-  </si>
-  <si>
-    <t>هايدى محمد حسين رفاعى فراج</t>
-  </si>
-  <si>
-    <t>220802</t>
-  </si>
-  <si>
-    <t>هدى مدحت خيرى احمد فرج</t>
-  </si>
-  <si>
-    <t>220803</t>
-  </si>
-  <si>
-    <t>هرمينا عبد الله جاد جرجس</t>
-  </si>
-  <si>
-    <t>220804</t>
-  </si>
-  <si>
-    <t>هنا خليل عبد الرؤف محمد سعيد</t>
-  </si>
-  <si>
-    <t>220805</t>
-  </si>
-  <si>
-    <t>وسام ايمن على الشريف</t>
-  </si>
-  <si>
-    <t>220807</t>
-  </si>
-  <si>
-    <t>وليد ياسر عبد الشافى محمود</t>
-  </si>
-  <si>
-    <t>220808</t>
-  </si>
-  <si>
-    <t>ياسمين عادل السيد الفرغلى حسن</t>
-  </si>
-  <si>
-    <t>220809</t>
-  </si>
-  <si>
-    <t>يحيى احمد محمد عبد الفتاح الزيات</t>
-  </si>
-  <si>
-    <t>220810</t>
-  </si>
-  <si>
-    <t>يحيى محمد يحى على</t>
-  </si>
-  <si>
-    <t>220813</t>
-  </si>
-  <si>
-    <t>يمنى صلاح عبد الغفار محيسن دسوقى</t>
-  </si>
-  <si>
-    <t>220814</t>
-  </si>
-  <si>
-    <t>يوسف جلال محمد عبد الفتاح صالح</t>
-  </si>
-  <si>
-    <t>220815</t>
-  </si>
-  <si>
-    <t>يوسف حمدى احمد طاجن</t>
-  </si>
-  <si>
-    <t>A2-C2</t>
-  </si>
-  <si>
-    <t>220816</t>
-  </si>
-  <si>
-    <t>يوسف عمرو على حفنى ابراهيم</t>
-  </si>
-  <si>
-    <t>220817</t>
-  </si>
-  <si>
-    <t>يوسف فهيم عبد الحميد ابو عزيز</t>
-  </si>
-  <si>
-    <t>220818</t>
-  </si>
-  <si>
-    <t>يوسف محمد رضا جلال احمد سيد احمد</t>
-  </si>
-  <si>
-    <t>220819</t>
-  </si>
-  <si>
-    <t>يوسف محمد محمد السيد البطه</t>
-  </si>
-  <si>
-    <t>220820</t>
-  </si>
-  <si>
-    <t>يوسف محمود محمد ابراهيم</t>
-  </si>
-  <si>
-    <t>220821</t>
-  </si>
-  <si>
-    <t>يوسف مصطفى محمد رسلان</t>
-  </si>
-  <si>
-    <t>220822</t>
-  </si>
-  <si>
-    <t>يوسف مصطفى مصطفى محمد</t>
-  </si>
-  <si>
-    <t>220824</t>
-  </si>
-  <si>
-    <t>يوسف وائل حامد ابراهيم العالم</t>
-  </si>
-  <si>
-    <t>220825</t>
-  </si>
-  <si>
-    <t>يوسف سيد محمد يوسف</t>
-  </si>
-  <si>
-    <t>220826</t>
-  </si>
-  <si>
-    <t>عبد الله خالد احمد باحاذق</t>
-  </si>
-  <si>
-    <t>220827</t>
-  </si>
-  <si>
-    <t>أبوبكر طارق أبوبكر رمضان</t>
+    <t>221122</t>
+  </si>
+  <si>
+    <t>سارة أشرف السيد عباسي</t>
+  </si>
+  <si>
+    <t>221123</t>
+  </si>
+  <si>
+    <t>ساره عاطف محمد الصادق</t>
+  </si>
+  <si>
+    <t>221124</t>
+  </si>
+  <si>
+    <t>ساره نسيم فرج بكر</t>
+  </si>
+  <si>
+    <t>221125</t>
+  </si>
+  <si>
+    <t>ساره طارق زكريا حامد</t>
+  </si>
+  <si>
+    <t>221126</t>
+  </si>
+  <si>
+    <t>سامى السيد لبيب قاسم</t>
+  </si>
+  <si>
+    <t>221127</t>
+  </si>
+  <si>
+    <t>ساندرا سامي عبدالملاك ملوكه</t>
+  </si>
+  <si>
+    <t>221128</t>
+  </si>
+  <si>
+    <t>سلمى السيد أحمد فتيح</t>
+  </si>
+  <si>
+    <t>221129</t>
+  </si>
+  <si>
+    <t>سلمى ايمن سعيد محمد</t>
+  </si>
+  <si>
+    <t>221130</t>
+  </si>
+  <si>
+    <t>سلمي احمد رمضان مخيمر</t>
+  </si>
+  <si>
+    <t>221131</t>
+  </si>
+  <si>
+    <t>سلمي احمد موسي احمد الصحصاح</t>
+  </si>
+  <si>
+    <t>221132</t>
+  </si>
+  <si>
+    <t>سلمي محمد السيد حسين</t>
+  </si>
+  <si>
+    <t>221133</t>
+  </si>
+  <si>
+    <t>سما حسام الدين عبدالفتاح محمود ناصف</t>
+  </si>
+  <si>
+    <t>221134</t>
+  </si>
+  <si>
+    <t>سما سامح سعد الشريفي</t>
+  </si>
+  <si>
+    <t>221136</t>
+  </si>
+  <si>
+    <t>سما محمد عبد السلام الرافعي</t>
+  </si>
+  <si>
+    <t>221137</t>
+  </si>
+  <si>
+    <t>سما ممدوح حسن عطيه ممدوح حسن عطيه حسن عطيه القاضي عطيه القاضي</t>
+  </si>
+  <si>
+    <t>221138</t>
+  </si>
+  <si>
+    <t>سماء اكرامي محمود عبد السميع</t>
+  </si>
+  <si>
+    <t>221139</t>
+  </si>
+  <si>
+    <t>سماح محمد ابراهيم يوسف</t>
+  </si>
+  <si>
+    <t>221140</t>
+  </si>
+  <si>
+    <t>سندس رفعت السيد بسيوني علي</t>
+  </si>
+  <si>
+    <t>221141</t>
+  </si>
+  <si>
+    <t>سيف الدين اشرف صالح سليمان</t>
+  </si>
+  <si>
+    <t>221144</t>
+  </si>
+  <si>
+    <t>شاهي أحمد محمد عز الدين ابراهيم مهران</t>
+  </si>
+  <si>
+    <t>221145</t>
+  </si>
+  <si>
+    <t>شروق أحمد عبد الرؤف عبد العال</t>
+  </si>
+  <si>
+    <t>221146</t>
+  </si>
+  <si>
+    <t>شريف أحمد محمد صديق الخولي</t>
+  </si>
+  <si>
+    <t>221147</t>
+  </si>
+  <si>
+    <t>شهد انصاري عبدالرؤوف الانصاري</t>
+  </si>
+  <si>
+    <t>221148</t>
+  </si>
+  <si>
+    <t>شهد محمد عطيه الشبراوى</t>
+  </si>
+  <si>
+    <t>221149</t>
+  </si>
+  <si>
+    <t>شيري أشرف نصيف ميخائيل</t>
+  </si>
+  <si>
+    <t>221150</t>
+  </si>
+  <si>
+    <t>شيماء يسري سعد بدري</t>
+  </si>
+  <si>
+    <t>221151</t>
+  </si>
+  <si>
+    <t>عبد الرحمن علاء فهمى سرج</t>
+  </si>
+  <si>
+    <t>221152</t>
+  </si>
+  <si>
+    <t>عبد الرحمن ايمن حسنى محمد عبد الرحمن</t>
+  </si>
+  <si>
+    <t>221153</t>
+  </si>
+  <si>
+    <t>عبد العزيز عصام عبد التواب فرج</t>
+  </si>
+  <si>
+    <t>221154</t>
+  </si>
+  <si>
+    <t>عبدالرحمن احمد سعد محمد عبدالخالق</t>
   </si>
   <si>
     <t>220828</t>
@@ -1239,838 +2079,7 @@
     <t>سلمى مصطفى عبد العاطى حسن ناصف</t>
   </si>
   <si>
-    <t>220829</t>
-  </si>
-  <si>
-    <t>تبارك رائد حسن كميل</t>
-  </si>
-  <si>
-    <t>220830</t>
-  </si>
-  <si>
-    <t>مصطفى محمد على</t>
-  </si>
-  <si>
-    <t>220832</t>
-  </si>
-  <si>
-    <t>احمد عبد الله نعمان محمد</t>
-  </si>
-  <si>
-    <t>220833</t>
-  </si>
-  <si>
-    <t>رغد فيصل عقيل العمايري</t>
-  </si>
-  <si>
-    <t>220834</t>
-  </si>
-  <si>
-    <t>احمد سليمان محمد</t>
-  </si>
-  <si>
-    <t>220838</t>
-  </si>
-  <si>
-    <t>حمزه طارق الطراد</t>
-  </si>
-  <si>
-    <t>220839</t>
-  </si>
-  <si>
-    <t>عزام نبيل يحي العمير</t>
-  </si>
-  <si>
-    <t>220845</t>
-  </si>
-  <si>
-    <t>ريان تاج الدين عبد الله أحمد</t>
-  </si>
-  <si>
-    <t>220848</t>
-  </si>
-  <si>
-    <t>عبد الله مسعود مصطفى</t>
-  </si>
-  <si>
-    <t>220853</t>
-  </si>
-  <si>
-    <t>قند عدي بدران</t>
-  </si>
-  <si>
-    <t>220856</t>
-  </si>
-  <si>
-    <t>ماسه بلال الدهبي</t>
-  </si>
-  <si>
-    <t>220857</t>
-  </si>
-  <si>
-    <t>محمد عبده علوي محمد</t>
-  </si>
-  <si>
-    <t>220867</t>
-  </si>
-  <si>
-    <t>شهد جمعه على عبد الفتاح</t>
-  </si>
-  <si>
-    <t>220876</t>
-  </si>
-  <si>
-    <t>عبد المهيمن مهند سلمان</t>
-  </si>
-  <si>
-    <t>220878</t>
-  </si>
-  <si>
-    <t>عاصم بن عبد الرحمن بن احمد بامعلم</t>
-  </si>
-  <si>
-    <t>220879</t>
-  </si>
-  <si>
-    <t>علي بن محمد بن على المحمد صالح</t>
-  </si>
-  <si>
-    <t>220889</t>
-  </si>
-  <si>
-    <t>سجى السر ميرغني عمر</t>
-  </si>
-  <si>
-    <t>220969</t>
-  </si>
-  <si>
-    <t>نهال حسام زهره</t>
-  </si>
-  <si>
-    <t>A2-D2</t>
-  </si>
-  <si>
-    <t>220970</t>
-  </si>
-  <si>
-    <t>مبارك حسن ابراهيم</t>
-  </si>
-  <si>
-    <t>220971</t>
-  </si>
-  <si>
-    <t>فراس حسين نعيم الكوز</t>
-  </si>
-  <si>
-    <t>220972</t>
-  </si>
-  <si>
-    <t>عاصم عبدالحكيم محمد سعيد ناصر</t>
-  </si>
-  <si>
-    <t>220974</t>
-  </si>
-  <si>
-    <t>مايا رضوان احمد سالم</t>
-  </si>
-  <si>
-    <t>220979</t>
-  </si>
-  <si>
-    <t>محمد حسين محمد الحامد</t>
-  </si>
-  <si>
-    <t>220983</t>
-  </si>
-  <si>
-    <t>حسام محمد احمد الكوز</t>
-  </si>
-  <si>
-    <t>220986</t>
-  </si>
-  <si>
-    <t>هاشم احمد صالح الشرجي</t>
-  </si>
-  <si>
-    <t>220989</t>
-  </si>
-  <si>
-    <t>مشاري محمد يحيي الكحلاني</t>
-  </si>
-  <si>
-    <t>220991</t>
-  </si>
-  <si>
-    <t>عمر حسام الدين الزيبق</t>
-  </si>
-  <si>
-    <t>220992</t>
-  </si>
-  <si>
-    <t>يحيى عبدالغني بني</t>
-  </si>
-  <si>
-    <t>220996</t>
-  </si>
-  <si>
-    <t>صفية وفائي</t>
-  </si>
-  <si>
-    <t>220997</t>
-  </si>
-  <si>
-    <t>احمد عماد الدين محمد عبد الرحمن</t>
-  </si>
-  <si>
-    <t>221002</t>
-  </si>
-  <si>
-    <t>هاجر مؤيد السلوم</t>
-  </si>
-  <si>
-    <t>221006</t>
-  </si>
-  <si>
-    <t>فهد هارون ادم محمد</t>
-  </si>
-  <si>
-    <t>221008</t>
-  </si>
-  <si>
-    <t>وفاق عبدالوهاب محمد ابراهيم</t>
-  </si>
-  <si>
-    <t>221012</t>
-  </si>
-  <si>
-    <t>اسامه الشيخ احمد الامام</t>
-  </si>
-  <si>
-    <t>221015</t>
-  </si>
-  <si>
-    <t>وفاء حسين ميرغنى محمود</t>
-  </si>
-  <si>
-    <t>221016</t>
-  </si>
-  <si>
-    <t>ايمن ناصر محمد ابو ديه</t>
-  </si>
-  <si>
-    <t>221018</t>
-  </si>
-  <si>
-    <t>رامي احمد الخطيب</t>
-  </si>
-  <si>
-    <t>221020</t>
-  </si>
-  <si>
-    <t>مي سلوم سالم لم يصعد</t>
-  </si>
-  <si>
-    <t>221021</t>
-  </si>
-  <si>
-    <t>عثمان ابوالقاسم احمد حسن</t>
-  </si>
-  <si>
-    <t>221023</t>
-  </si>
-  <si>
-    <t>مرام عبدالله محمد حامد</t>
-  </si>
-  <si>
-    <t>221025</t>
-  </si>
-  <si>
-    <t>بتول محمد يوسف</t>
-  </si>
-  <si>
-    <t>221029</t>
-  </si>
-  <si>
-    <t>معتصم توفيق محمد بكرون</t>
-  </si>
-  <si>
-    <t>221035</t>
-  </si>
-  <si>
-    <t>محمد بدر احمد علي مول الدويله</t>
-  </si>
-  <si>
-    <t>221036</t>
-  </si>
-  <si>
-    <t>عبد السلام وليد عبد السلام ابو حلوان</t>
-  </si>
-  <si>
-    <t>221037</t>
-  </si>
-  <si>
-    <t>رنا بنت عبد الغني بن بكر برناوي</t>
-  </si>
-  <si>
-    <t>221040</t>
-  </si>
-  <si>
-    <t>محمد الطاهر محمد الطاهر</t>
-  </si>
-  <si>
-    <t>221046</t>
-  </si>
-  <si>
-    <t>احمد مجدي امين محمد</t>
-  </si>
-  <si>
-    <t>221047</t>
-  </si>
-  <si>
-    <t>احمد محسن محمد ماهر ابو هاشم</t>
-  </si>
-  <si>
-    <t>A2-E1</t>
-  </si>
-  <si>
-    <t>221048</t>
-  </si>
-  <si>
-    <t>احمد محمد اسامة احمد عبدالخالق احمد</t>
-  </si>
-  <si>
-    <t>221049</t>
-  </si>
-  <si>
-    <t>ادهم عامر عبدالحافظ احمد محمد</t>
-  </si>
-  <si>
-    <t>221050</t>
-  </si>
-  <si>
-    <t>اسراء احمد محمد عبد الصادق نور</t>
-  </si>
-  <si>
-    <t>221051</t>
-  </si>
-  <si>
-    <t>اسراء هشام محمد عبد المنعم</t>
-  </si>
-  <si>
-    <t>221052</t>
-  </si>
-  <si>
-    <t>امنيه سلامه عبده محمد</t>
-  </si>
-  <si>
-    <t>221053</t>
-  </si>
-  <si>
-    <t>امينه خالد عوض عفيفى تاج الدين</t>
-  </si>
-  <si>
-    <t>221054</t>
-  </si>
-  <si>
-    <t>انجي علاء سعد الدين الشحات السيد</t>
-  </si>
-  <si>
-    <t>221055</t>
-  </si>
-  <si>
-    <t>ايلاري هاني سند ماضي</t>
-  </si>
-  <si>
-    <t>221056</t>
-  </si>
-  <si>
-    <t>إيريني وجدي عزمي عبدالمسيح</t>
-  </si>
-  <si>
-    <t>221059</t>
-  </si>
-  <si>
-    <t>أحمد عزت مختار عزت</t>
-  </si>
-  <si>
-    <t>221060</t>
-  </si>
-  <si>
-    <t>أحمد مصطفى السيد سالم عبد الرحيم</t>
-  </si>
-  <si>
-    <t>221062</t>
-  </si>
-  <si>
-    <t>أسراء محمد هانى محمد رشدى خليل غفيفى</t>
-  </si>
-  <si>
-    <t>221063</t>
-  </si>
-  <si>
-    <t>أسماء أحمد عبدالله عبد المقصود أحمد</t>
-  </si>
-  <si>
-    <t>221064</t>
-  </si>
-  <si>
-    <t>أكرم مصطفي فتحي محمد</t>
-  </si>
-  <si>
-    <t>221066</t>
-  </si>
-  <si>
-    <t>أية عبدالسميع محمد سليمان</t>
-  </si>
-  <si>
-    <t>221067</t>
-  </si>
-  <si>
-    <t>آيتن أحمد مصطفى محمد مصطفى</t>
-  </si>
-  <si>
-    <t>221068</t>
-  </si>
-  <si>
-    <t>آيه حسن محمد مأمون</t>
-  </si>
-  <si>
-    <t>221069</t>
-  </si>
-  <si>
-    <t>بثينه خالد ابراهيم محمد موسى</t>
-  </si>
-  <si>
-    <t>221070</t>
-  </si>
-  <si>
-    <t>بسمة علاء حسني زهران</t>
-  </si>
-  <si>
-    <t>221071</t>
-  </si>
-  <si>
-    <t>بسملة وسام صلاح أحمد</t>
-  </si>
-  <si>
-    <t>221072</t>
-  </si>
-  <si>
-    <t>بسنت احمد شكرالله عبدالباسط</t>
-  </si>
-  <si>
-    <t>221073</t>
-  </si>
-  <si>
-    <t>بلال لبيب يسري عبد اللطيف عبد الغني</t>
-  </si>
-  <si>
-    <t>221075</t>
-  </si>
-  <si>
-    <t>تسنيم اسامة يوسف نعيم</t>
-  </si>
-  <si>
-    <t>221076</t>
-  </si>
-  <si>
-    <t>تسنيم علاء ناجي عبدالراضي</t>
-  </si>
-  <si>
-    <t>221077</t>
-  </si>
-  <si>
-    <t>تقي محمود احمد السمكري</t>
-  </si>
-  <si>
-    <t>221078</t>
-  </si>
-  <si>
-    <t>توماس نبيل سامي غطاس</t>
-  </si>
-  <si>
-    <t>221079</t>
-  </si>
-  <si>
-    <t>جنا هاني احمد عبد القادر</t>
-  </si>
-  <si>
-    <t>221080</t>
-  </si>
-  <si>
-    <t>جنة الله علاء الدين أحمد عيد</t>
-  </si>
-  <si>
-    <t>221084</t>
-  </si>
-  <si>
-    <t>جودي احمد السيد سليمان</t>
-  </si>
-  <si>
-    <t>221085</t>
-  </si>
-  <si>
-    <t>جوفانا روماني راشد شنوده</t>
-  </si>
-  <si>
-    <t>A2-E2</t>
-  </si>
-  <si>
-    <t>221086</t>
-  </si>
-  <si>
-    <t>جونسي صلاح اسماعيل حجازي</t>
-  </si>
-  <si>
-    <t>221087</t>
-  </si>
-  <si>
-    <t>جونى سامر صفوت فهمى ميخائيل</t>
-  </si>
-  <si>
-    <t>221088</t>
-  </si>
-  <si>
-    <t>حبيبة اسماعيل محمد سعيد اسماعيل محرم</t>
-  </si>
-  <si>
-    <t>221089</t>
-  </si>
-  <si>
-    <t>حبيبة زكي محمد زكي</t>
-  </si>
-  <si>
-    <t>221090</t>
-  </si>
-  <si>
-    <t>حبيبه محمد صابر عبدالعال</t>
-  </si>
-  <si>
-    <t>221091</t>
-  </si>
-  <si>
-    <t>حسن احمد حسن الصفتي</t>
-  </si>
-  <si>
-    <t>221092</t>
-  </si>
-  <si>
-    <t>حسن محمد حسن شمس الدين</t>
-  </si>
-  <si>
-    <t>221093</t>
-  </si>
-  <si>
-    <t>حلا احمد محمد محمد فضل الله</t>
-  </si>
-  <si>
-    <t>221095</t>
-  </si>
-  <si>
-    <t>حمزه هشام بكر ابو القميز</t>
-  </si>
-  <si>
-    <t>221096</t>
-  </si>
-  <si>
-    <t>حنين طارق محرم شلبي</t>
-  </si>
-  <si>
-    <t>221097</t>
-  </si>
-  <si>
-    <t>خالد علاء عبد السميع عبدالله الديب</t>
-  </si>
-  <si>
-    <t>221099</t>
-  </si>
-  <si>
-    <t>دارين أحمد فرج القاصد</t>
-  </si>
-  <si>
-    <t>221100</t>
-  </si>
-  <si>
-    <t>دارين السيد مصيلحي مصيلحي</t>
-  </si>
-  <si>
-    <t>221101</t>
-  </si>
-  <si>
-    <t>دارين محمد ابراهيم ماضى</t>
-  </si>
-  <si>
-    <t>221102</t>
-  </si>
-  <si>
-    <t>دانا أسامة عبدالغني محمد</t>
-  </si>
-  <si>
-    <t>221103</t>
-  </si>
-  <si>
-    <t>دانه عبداللطيف فؤاد زيان</t>
-  </si>
-  <si>
-    <t>221104</t>
-  </si>
-  <si>
-    <t>دعاء أشرف أحمد عبد الله</t>
-  </si>
-  <si>
-    <t>221106</t>
-  </si>
-  <si>
-    <t>دينا ناجي عبد المنعم الشيخ</t>
-  </si>
-  <si>
-    <t>221108</t>
-  </si>
-  <si>
-    <t>رانيا عادل طلخان رزق</t>
-  </si>
-  <si>
-    <t>221110</t>
-  </si>
-  <si>
-    <t>رفيده أيمن مصطفى النحاس شحاته</t>
-  </si>
-  <si>
-    <t>221111</t>
-  </si>
-  <si>
-    <t>رنا عمرو محمد شرايحي</t>
-  </si>
-  <si>
-    <t>221112</t>
-  </si>
-  <si>
-    <t>رنيم ايمن علي علام</t>
-  </si>
-  <si>
-    <t>221114</t>
-  </si>
-  <si>
-    <t>روان محمد ياسر عبد العال ابو الوفا</t>
-  </si>
-  <si>
-    <t>221116</t>
-  </si>
-  <si>
-    <t>روينا محمد عبدالحكيم الاشموني</t>
-  </si>
-  <si>
-    <t>221117</t>
-  </si>
-  <si>
-    <t>رؤى طارق مرسى محمود</t>
-  </si>
-  <si>
-    <t>221118</t>
-  </si>
-  <si>
-    <t>ريم السيد صالح خليل</t>
-  </si>
-  <si>
-    <t>221119</t>
-  </si>
-  <si>
-    <t>زياد شريف حلمي الألفي</t>
-  </si>
-  <si>
-    <t>221120</t>
-  </si>
-  <si>
-    <t>سارة علاءالدين احمد محمد</t>
-  </si>
-  <si>
-    <t>221121</t>
-  </si>
-  <si>
-    <t>سارة احمد محمد على خليل</t>
-  </si>
-  <si>
-    <t>221122</t>
-  </si>
-  <si>
-    <t>سارة أشرف السيد عباسي</t>
-  </si>
-  <si>
-    <t>A2-F1</t>
-  </si>
-  <si>
-    <t>221123</t>
-  </si>
-  <si>
-    <t>ساره عاطف محمد الصادق</t>
-  </si>
-  <si>
-    <t>221124</t>
-  </si>
-  <si>
-    <t>ساره نسيم فرج بكر</t>
-  </si>
-  <si>
-    <t>221125</t>
-  </si>
-  <si>
-    <t>ساره طارق زكريا حامد</t>
-  </si>
-  <si>
-    <t>221126</t>
-  </si>
-  <si>
-    <t>سامى السيد لبيب قاسم</t>
-  </si>
-  <si>
-    <t>221127</t>
-  </si>
-  <si>
-    <t>ساندرا سامي عبدالملاك ملوكه</t>
-  </si>
-  <si>
-    <t>221128</t>
-  </si>
-  <si>
-    <t>سلمى السيد أحمد فتيح</t>
-  </si>
-  <si>
-    <t>221129</t>
-  </si>
-  <si>
-    <t>سلمى ايمن سعيد محمد</t>
-  </si>
-  <si>
-    <t>221130</t>
-  </si>
-  <si>
-    <t>سلمي احمد رمضان مخيمر</t>
-  </si>
-  <si>
-    <t>221131</t>
-  </si>
-  <si>
-    <t>سلمي احمد موسي احمد الصحصاح</t>
-  </si>
-  <si>
-    <t>221132</t>
-  </si>
-  <si>
-    <t>سلمي محمد السيد حسين</t>
-  </si>
-  <si>
-    <t>221133</t>
-  </si>
-  <si>
-    <t>سما حسام الدين عبدالفتاح محمود ناصف</t>
-  </si>
-  <si>
-    <t>221134</t>
-  </si>
-  <si>
-    <t>سما سامح سعد الشريفي</t>
-  </si>
-  <si>
-    <t>221136</t>
-  </si>
-  <si>
-    <t>سما محمد عبد السلام الرافعي</t>
-  </si>
-  <si>
-    <t>221137</t>
-  </si>
-  <si>
-    <t>سما ممدوح حسن عطيه ممدوح حسن عطيه حسن عطيه القاضي عطيه القاضي</t>
-  </si>
-  <si>
-    <t>221138</t>
-  </si>
-  <si>
-    <t>سماء اكرامي محمود عبد السميع</t>
-  </si>
-  <si>
-    <t>221139</t>
-  </si>
-  <si>
-    <t>سماح محمد ابراهيم يوسف</t>
-  </si>
-  <si>
-    <t>221140</t>
-  </si>
-  <si>
-    <t>سندس رفعت السيد بسيوني علي</t>
-  </si>
-  <si>
-    <t>221141</t>
-  </si>
-  <si>
-    <t>سيف الدين اشرف صالح سليمان</t>
-  </si>
-  <si>
-    <t>221144</t>
-  </si>
-  <si>
-    <t>شاهي أحمد محمد عز الدين ابراهيم مهران</t>
-  </si>
-  <si>
-    <t>221145</t>
-  </si>
-  <si>
-    <t>شروق أحمد عبد الرؤف عبد العال</t>
-  </si>
-  <si>
-    <t>221146</t>
-  </si>
-  <si>
-    <t>شريف أحمد محمد صديق الخولي</t>
-  </si>
-  <si>
-    <t>221147</t>
-  </si>
-  <si>
-    <t>شهد انصاري عبدالرؤوف الانصاري</t>
-  </si>
-  <si>
-    <t>221148</t>
-  </si>
-  <si>
-    <t>شهد محمد عطيه الشبراوى</t>
-  </si>
-  <si>
-    <t>221149</t>
-  </si>
-  <si>
-    <t>شيري أشرف نصيف ميخائيل</t>
-  </si>
-  <si>
-    <t>221150</t>
-  </si>
-  <si>
-    <t>شيماء يسري سعد بدري</t>
-  </si>
-  <si>
-    <t>221151</t>
-  </si>
-  <si>
-    <t>عبد الرحمن علاء فهمى سرج</t>
-  </si>
-  <si>
-    <t>221152</t>
-  </si>
-  <si>
-    <t>عبد الرحمن ايمن حسنى محمد عبد الرحمن</t>
-  </si>
-  <si>
-    <t>221153</t>
-  </si>
-  <si>
-    <t>عبد العزيز عصام عبد التواب فرج</t>
-  </si>
-  <si>
-    <t>221154</t>
-  </si>
-  <si>
-    <t>عبدالرحمن احمد سعد محمد عبدالخالق</t>
+    <t>A2-F2</t>
   </si>
   <si>
     <t>221157</t>
@@ -2079,9 +2088,6 @@
     <t>عبدالرحمن محمد عمر عيد</t>
   </si>
   <si>
-    <t>A2-F2</t>
-  </si>
-  <si>
     <t>221158</t>
   </si>
   <si>
@@ -2230,12 +2236,6 @@
   </si>
   <si>
     <t>يمني تحسين عبدالمحيد سيداحمد</t>
-  </si>
-  <si>
-    <t>221335</t>
-  </si>
-  <si>
-    <t>حذيفه طريف القطرنجى</t>
   </si>
   <si>
     <t>221541</t>
@@ -2640,7 +2640,7 @@
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3164,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>9</v>
@@ -3172,16 +3172,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>9</v>
@@ -3198,7 +3198,7 @@
         <v>7</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>9</v>
@@ -3215,7 +3215,7 @@
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>9</v>
@@ -3232,7 +3232,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>9</v>
@@ -3249,7 +3249,7 @@
         <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>9</v>
@@ -3266,7 +3266,7 @@
         <v>7</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>9</v>
@@ -3283,7 +3283,7 @@
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>9</v>
@@ -3300,7 +3300,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>9</v>
@@ -3317,7 +3317,7 @@
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>9</v>
@@ -3334,7 +3334,7 @@
         <v>7</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>9</v>
@@ -3351,7 +3351,7 @@
         <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>9</v>
@@ -3368,7 +3368,7 @@
         <v>7</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>9</v>
@@ -3385,7 +3385,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>9</v>
@@ -3402,7 +3402,7 @@
         <v>7</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>9</v>
@@ -3419,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>9</v>
@@ -3436,7 +3436,7 @@
         <v>7</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>9</v>
@@ -3453,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>9</v>
@@ -3470,7 +3470,7 @@
         <v>7</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>9</v>
@@ -3487,7 +3487,7 @@
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>9</v>
@@ -3504,7 +3504,7 @@
         <v>7</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>9</v>
@@ -3521,7 +3521,7 @@
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>9</v>
@@ -3538,7 +3538,7 @@
         <v>7</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>9</v>
@@ -3555,7 +3555,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>9</v>
@@ -3572,7 +3572,7 @@
         <v>7</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>9</v>
@@ -3589,7 +3589,7 @@
         <v>7</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>9</v>
@@ -3606,7 +3606,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>9</v>
@@ -3623,7 +3623,7 @@
         <v>7</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>9</v>
@@ -3640,7 +3640,7 @@
         <v>7</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>9</v>
@@ -3657,7 +3657,7 @@
         <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>9</v>
@@ -3674,7 +3674,7 @@
         <v>7</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>9</v>
@@ -3682,16 +3682,16 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>9</v>
@@ -3699,16 +3699,16 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>9</v>
@@ -3725,7 +3725,7 @@
         <v>7</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>9</v>
@@ -3742,7 +3742,7 @@
         <v>7</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>9</v>
@@ -3759,7 +3759,7 @@
         <v>7</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>9</v>
@@ -3776,7 +3776,7 @@
         <v>7</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>9</v>
@@ -3793,7 +3793,7 @@
         <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>9</v>
@@ -3810,7 +3810,7 @@
         <v>7</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>9</v>
@@ -3827,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>9</v>
@@ -3844,7 +3844,7 @@
         <v>7</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>9</v>
@@ -3861,7 +3861,7 @@
         <v>7</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>9</v>
@@ -3878,7 +3878,7 @@
         <v>7</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>9</v>
@@ -3895,7 +3895,7 @@
         <v>7</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>9</v>
@@ -3912,7 +3912,7 @@
         <v>7</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>9</v>
@@ -3929,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>9</v>
@@ -3946,7 +3946,7 @@
         <v>7</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>9</v>
@@ -3963,7 +3963,7 @@
         <v>7</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>9</v>
@@ -3980,7 +3980,7 @@
         <v>7</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>9</v>
@@ -3997,7 +3997,7 @@
         <v>7</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>9</v>
@@ -4014,7 +4014,7 @@
         <v>7</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>9</v>
@@ -4031,7 +4031,7 @@
         <v>7</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>9</v>
@@ -4048,7 +4048,7 @@
         <v>7</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>9</v>
@@ -4065,7 +4065,7 @@
         <v>7</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>9</v>
@@ -4082,7 +4082,7 @@
         <v>7</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>9</v>
@@ -4099,7 +4099,7 @@
         <v>7</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>9</v>
@@ -4116,7 +4116,7 @@
         <v>7</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>9</v>
@@ -4133,7 +4133,7 @@
         <v>7</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>9</v>
@@ -4150,7 +4150,7 @@
         <v>7</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>9</v>
@@ -4167,7 +4167,7 @@
         <v>7</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>9</v>
@@ -4184,7 +4184,7 @@
         <v>7</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>9</v>
@@ -4201,7 +4201,7 @@
         <v>7</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>9</v>
@@ -4209,16 +4209,16 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>9</v>
@@ -4235,7 +4235,7 @@
         <v>7</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>9</v>
@@ -4252,7 +4252,7 @@
         <v>7</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>9</v>
@@ -4269,7 +4269,7 @@
         <v>7</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>9</v>
@@ -4286,7 +4286,7 @@
         <v>7</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>9</v>
@@ -4303,7 +4303,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>9</v>
@@ -4320,7 +4320,7 @@
         <v>7</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>9</v>
@@ -4337,7 +4337,7 @@
         <v>7</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>9</v>
@@ -4354,7 +4354,7 @@
         <v>7</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>9</v>
@@ -4371,7 +4371,7 @@
         <v>7</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>9</v>
@@ -4388,7 +4388,7 @@
         <v>7</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>9</v>
@@ -4405,7 +4405,7 @@
         <v>7</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>9</v>
@@ -4422,7 +4422,7 @@
         <v>7</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>9</v>
@@ -4439,7 +4439,7 @@
         <v>7</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>9</v>
@@ -4456,7 +4456,7 @@
         <v>7</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>9</v>
@@ -4473,7 +4473,7 @@
         <v>7</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>9</v>
@@ -4490,7 +4490,7 @@
         <v>7</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>9</v>
@@ -4507,7 +4507,7 @@
         <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>9</v>
@@ -4524,7 +4524,7 @@
         <v>7</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>9</v>
@@ -4541,7 +4541,7 @@
         <v>7</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>9</v>
@@ -4558,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>9</v>
@@ -4575,7 +4575,7 @@
         <v>7</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>9</v>
@@ -4592,7 +4592,7 @@
         <v>7</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>9</v>
@@ -4609,7 +4609,7 @@
         <v>7</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>9</v>
@@ -4626,7 +4626,7 @@
         <v>7</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>9</v>
@@ -4643,7 +4643,7 @@
         <v>7</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>9</v>
@@ -4660,7 +4660,7 @@
         <v>7</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>9</v>
@@ -4677,7 +4677,7 @@
         <v>7</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>9</v>
@@ -4685,16 +4685,16 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>9</v>
@@ -4702,16 +4702,16 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>9</v>
@@ -4719,16 +4719,16 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>9</v>
@@ -4745,7 +4745,7 @@
         <v>7</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>9</v>
@@ -4762,7 +4762,7 @@
         <v>7</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>9</v>
@@ -4779,7 +4779,7 @@
         <v>7</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>9</v>
@@ -4796,7 +4796,7 @@
         <v>7</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>9</v>
@@ -4813,7 +4813,7 @@
         <v>7</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>9</v>
@@ -4830,7 +4830,7 @@
         <v>7</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>9</v>
@@ -4847,7 +4847,7 @@
         <v>7</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>9</v>
@@ -4864,7 +4864,7 @@
         <v>7</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>9</v>
@@ -4881,7 +4881,7 @@
         <v>7</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>9</v>
@@ -4898,7 +4898,7 @@
         <v>7</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>9</v>
@@ -4915,7 +4915,7 @@
         <v>7</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>9</v>
@@ -4932,7 +4932,7 @@
         <v>7</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>9</v>
@@ -4949,7 +4949,7 @@
         <v>7</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>9</v>
@@ -4966,7 +4966,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>9</v>
@@ -4983,7 +4983,7 @@
         <v>7</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>9</v>
@@ -5000,7 +5000,7 @@
         <v>7</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>9</v>
@@ -5017,7 +5017,7 @@
         <v>7</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>9</v>
@@ -5034,7 +5034,7 @@
         <v>7</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>9</v>
@@ -5051,7 +5051,7 @@
         <v>7</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>9</v>
@@ -5068,7 +5068,7 @@
         <v>7</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>9</v>
@@ -5085,7 +5085,7 @@
         <v>7</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>9</v>
@@ -5102,7 +5102,7 @@
         <v>7</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>9</v>
@@ -5119,7 +5119,7 @@
         <v>7</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>9</v>
@@ -5136,7 +5136,7 @@
         <v>7</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>9</v>
@@ -5153,7 +5153,7 @@
         <v>7</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>9</v>
@@ -5170,7 +5170,7 @@
         <v>7</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>9</v>
@@ -5187,7 +5187,7 @@
         <v>7</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>9</v>
@@ -5204,7 +5204,7 @@
         <v>7</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>9</v>
@@ -5212,16 +5212,16 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>9</v>
@@ -5229,16 +5229,16 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>9</v>
@@ -5255,7 +5255,7 @@
         <v>7</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>9</v>
@@ -5272,7 +5272,7 @@
         <v>7</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>9</v>
@@ -5289,7 +5289,7 @@
         <v>7</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>9</v>
@@ -5306,7 +5306,7 @@
         <v>7</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>9</v>
@@ -5323,7 +5323,7 @@
         <v>7</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>9</v>
@@ -5340,7 +5340,7 @@
         <v>7</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>9</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>9</v>
@@ -5374,7 +5374,7 @@
         <v>7</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>9</v>
@@ -5391,7 +5391,7 @@
         <v>7</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>9</v>
@@ -5408,7 +5408,7 @@
         <v>7</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>9</v>
@@ -5425,7 +5425,7 @@
         <v>7</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>9</v>
@@ -5442,7 +5442,7 @@
         <v>7</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>9</v>
@@ -5459,7 +5459,7 @@
         <v>7</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>9</v>
@@ -5476,7 +5476,7 @@
         <v>7</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>9</v>
@@ -5493,7 +5493,7 @@
         <v>7</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>9</v>
@@ -5510,7 +5510,7 @@
         <v>7</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>9</v>
@@ -5527,7 +5527,7 @@
         <v>7</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>9</v>
@@ -5544,7 +5544,7 @@
         <v>7</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>9</v>
@@ -5561,7 +5561,7 @@
         <v>7</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>9</v>
@@ -5578,7 +5578,7 @@
         <v>7</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>9</v>
@@ -5595,7 +5595,7 @@
         <v>7</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>9</v>
@@ -5612,7 +5612,7 @@
         <v>7</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>9</v>
@@ -5629,7 +5629,7 @@
         <v>7</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>9</v>
@@ -5646,7 +5646,7 @@
         <v>7</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>9</v>
@@ -5663,7 +5663,7 @@
         <v>7</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>9</v>
@@ -5680,7 +5680,7 @@
         <v>7</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>9</v>
@@ -5697,7 +5697,7 @@
         <v>7</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>9</v>
@@ -5705,16 +5705,16 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>9</v>
@@ -5722,16 +5722,16 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>9</v>
@@ -5739,16 +5739,16 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>9</v>
@@ -5765,7 +5765,7 @@
         <v>7</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>9</v>
@@ -5782,7 +5782,7 @@
         <v>7</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>9</v>
@@ -5799,7 +5799,7 @@
         <v>7</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>9</v>
@@ -5816,7 +5816,7 @@
         <v>7</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>9</v>
@@ -5833,7 +5833,7 @@
         <v>7</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>9</v>
@@ -5850,7 +5850,7 @@
         <v>7</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>9</v>
@@ -5867,7 +5867,7 @@
         <v>7</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>9</v>
@@ -5884,7 +5884,7 @@
         <v>7</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>9</v>
@@ -5901,7 +5901,7 @@
         <v>7</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>9</v>
@@ -5918,7 +5918,7 @@
         <v>7</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>9</v>
@@ -5935,7 +5935,7 @@
         <v>7</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>9</v>
@@ -5952,7 +5952,7 @@
         <v>7</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>9</v>
@@ -5969,7 +5969,7 @@
         <v>7</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>9</v>
@@ -5986,7 +5986,7 @@
         <v>7</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>9</v>
@@ -6003,7 +6003,7 @@
         <v>7</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>9</v>
@@ -6020,7 +6020,7 @@
         <v>7</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>9</v>
@@ -6037,7 +6037,7 @@
         <v>7</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>9</v>
@@ -6054,7 +6054,7 @@
         <v>7</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>9</v>
@@ -6071,7 +6071,7 @@
         <v>7</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>9</v>
@@ -6088,7 +6088,7 @@
         <v>7</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>9</v>
@@ -6105,7 +6105,7 @@
         <v>7</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>9</v>
@@ -6122,7 +6122,7 @@
         <v>7</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>9</v>
@@ -6139,7 +6139,7 @@
         <v>7</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>9</v>
@@ -6156,7 +6156,7 @@
         <v>7</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>9</v>
@@ -6173,7 +6173,7 @@
         <v>7</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>9</v>
@@ -6190,7 +6190,7 @@
         <v>7</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>9</v>
@@ -6198,16 +6198,16 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>9</v>
@@ -6215,16 +6215,16 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>9</v>
@@ -6232,16 +6232,16 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>9</v>
@@ -6249,16 +6249,16 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>9</v>
@@ -6275,7 +6275,7 @@
         <v>7</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>9</v>
@@ -6292,7 +6292,7 @@
         <v>7</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>9</v>
@@ -6309,7 +6309,7 @@
         <v>7</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>9</v>
@@ -6326,7 +6326,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>9</v>
@@ -6343,7 +6343,7 @@
         <v>7</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>9</v>
@@ -6360,7 +6360,7 @@
         <v>7</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>9</v>
@@ -6377,7 +6377,7 @@
         <v>7</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>9</v>
@@ -6394,7 +6394,7 @@
         <v>7</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>9</v>
@@ -6411,7 +6411,7 @@
         <v>7</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>9</v>
@@ -6428,7 +6428,7 @@
         <v>7</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>9</v>
@@ -6445,7 +6445,7 @@
         <v>7</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>9</v>
@@ -6462,7 +6462,7 @@
         <v>7</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>9</v>
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>9</v>
@@ -6496,7 +6496,7 @@
         <v>7</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>9</v>
@@ -6513,7 +6513,7 @@
         <v>7</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>9</v>
@@ -6530,7 +6530,7 @@
         <v>7</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>9</v>
@@ -6547,7 +6547,7 @@
         <v>7</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>9</v>
@@ -6564,7 +6564,7 @@
         <v>7</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>9</v>
@@ -6581,7 +6581,7 @@
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>9</v>
@@ -6598,7 +6598,7 @@
         <v>7</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>9</v>
@@ -6615,7 +6615,7 @@
         <v>7</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>9</v>
@@ -6632,7 +6632,7 @@
         <v>7</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>9</v>
@@ -6649,7 +6649,7 @@
         <v>7</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>9</v>
@@ -6666,7 +6666,7 @@
         <v>7</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>9</v>
@@ -6683,7 +6683,7 @@
         <v>7</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>9</v>
@@ -6700,7 +6700,7 @@
         <v>7</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>9</v>
@@ -6717,7 +6717,7 @@
         <v>7</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>9</v>
@@ -6734,7 +6734,7 @@
         <v>7</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>438</v>
+        <v>495</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>9</v>
@@ -6742,16 +6742,16 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D242" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>9</v>
@@ -6759,16 +6759,16 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>9</v>
@@ -6785,7 +6785,7 @@
         <v>7</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>9</v>
@@ -6802,7 +6802,7 @@
         <v>7</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>9</v>
@@ -6819,7 +6819,7 @@
         <v>7</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>9</v>
@@ -6836,7 +6836,7 @@
         <v>7</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>9</v>
@@ -6853,7 +6853,7 @@
         <v>7</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>9</v>
@@ -6870,7 +6870,7 @@
         <v>7</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>9</v>
@@ -6887,7 +6887,7 @@
         <v>7</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>9</v>
@@ -6904,7 +6904,7 @@
         <v>7</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>9</v>
@@ -6921,7 +6921,7 @@
         <v>7</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>9</v>
@@ -6938,7 +6938,7 @@
         <v>7</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>9</v>
@@ -6955,7 +6955,7 @@
         <v>7</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>9</v>
@@ -6972,7 +6972,7 @@
         <v>7</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>9</v>
@@ -6989,7 +6989,7 @@
         <v>7</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>9</v>
@@ -7006,7 +7006,7 @@
         <v>7</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>9</v>
@@ -7023,7 +7023,7 @@
         <v>7</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>9</v>
@@ -7040,7 +7040,7 @@
         <v>7</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>9</v>
@@ -7057,7 +7057,7 @@
         <v>7</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>9</v>
@@ -7074,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>9</v>
@@ -7091,7 +7091,7 @@
         <v>7</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>9</v>
@@ -7108,7 +7108,7 @@
         <v>7</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>9</v>
@@ -7125,7 +7125,7 @@
         <v>7</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>9</v>
@@ -7142,7 +7142,7 @@
         <v>7</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>9</v>
@@ -7159,7 +7159,7 @@
         <v>7</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>9</v>
@@ -7176,7 +7176,7 @@
         <v>7</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>9</v>
@@ -7193,7 +7193,7 @@
         <v>7</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>9</v>
@@ -7210,7 +7210,7 @@
         <v>7</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>9</v>
@@ -7227,7 +7227,7 @@
         <v>7</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>499</v>
+        <v>554</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>9</v>
@@ -7235,16 +7235,16 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D271" s="3" t="s">
-        <v>499</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>9</v>
@@ -7252,16 +7252,16 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>499</v>
+        <v>554</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>9</v>
@@ -7269,16 +7269,16 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>9</v>
@@ -7295,7 +7295,7 @@
         <v>7</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>9</v>
@@ -7312,7 +7312,7 @@
         <v>7</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>9</v>
@@ -7329,7 +7329,7 @@
         <v>7</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>9</v>
@@ -7346,7 +7346,7 @@
         <v>7</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>9</v>
@@ -7363,7 +7363,7 @@
         <v>7</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>9</v>
@@ -7380,7 +7380,7 @@
         <v>7</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>9</v>
@@ -7397,7 +7397,7 @@
         <v>7</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>9</v>
@@ -7414,7 +7414,7 @@
         <v>7</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>9</v>
@@ -7431,7 +7431,7 @@
         <v>7</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>9</v>
@@ -7448,7 +7448,7 @@
         <v>7</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>9</v>
@@ -7465,7 +7465,7 @@
         <v>7</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>9</v>
@@ -7482,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>9</v>
@@ -7499,7 +7499,7 @@
         <v>7</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>9</v>
@@ -7516,7 +7516,7 @@
         <v>7</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>9</v>
@@ -7533,7 +7533,7 @@
         <v>7</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>9</v>
@@ -7550,7 +7550,7 @@
         <v>7</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>9</v>
@@ -7567,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>9</v>
@@ -7584,7 +7584,7 @@
         <v>7</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>9</v>
@@ -7601,7 +7601,7 @@
         <v>7</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>9</v>
@@ -7618,7 +7618,7 @@
         <v>7</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>9</v>
@@ -7635,7 +7635,7 @@
         <v>7</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>9</v>
@@ -7652,7 +7652,7 @@
         <v>7</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>9</v>
@@ -7669,7 +7669,7 @@
         <v>7</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>9</v>
@@ -7686,7 +7686,7 @@
         <v>7</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E297" s="3" t="s">
         <v>9</v>
@@ -7703,7 +7703,7 @@
         <v>7</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>9</v>
@@ -7720,7 +7720,7 @@
         <v>7</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>9</v>
@@ -7737,7 +7737,7 @@
         <v>7</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>9</v>
@@ -7754,7 +7754,7 @@
         <v>7</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>560</v>
+        <v>617</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>9</v>
@@ -7762,16 +7762,16 @@
     </row>
     <row r="302" spans="1:5">
       <c r="A302" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D302" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>9</v>
@@ -7779,16 +7779,16 @@
     </row>
     <row r="303" spans="1:5">
       <c r="A303" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>9</v>
@@ -7805,7 +7805,7 @@
         <v>7</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>9</v>
@@ -7822,7 +7822,7 @@
         <v>7</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>9</v>
@@ -7839,7 +7839,7 @@
         <v>7</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>9</v>
@@ -7856,7 +7856,7 @@
         <v>7</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>9</v>
@@ -7873,7 +7873,7 @@
         <v>7</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>9</v>
@@ -7890,7 +7890,7 @@
         <v>7</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>9</v>
@@ -7907,7 +7907,7 @@
         <v>7</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>9</v>
@@ -7924,7 +7924,7 @@
         <v>7</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>9</v>
@@ -7941,7 +7941,7 @@
         <v>7</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>9</v>
@@ -7958,7 +7958,7 @@
         <v>7</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>9</v>
@@ -7975,7 +7975,7 @@
         <v>7</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>9</v>
@@ -7992,7 +7992,7 @@
         <v>7</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>9</v>
@@ -8009,7 +8009,7 @@
         <v>7</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>9</v>
@@ -8026,7 +8026,7 @@
         <v>7</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>9</v>
@@ -8043,7 +8043,7 @@
         <v>7</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>9</v>
@@ -8060,7 +8060,7 @@
         <v>7</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>9</v>
@@ -8077,7 +8077,7 @@
         <v>7</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>9</v>
@@ -8094,7 +8094,7 @@
         <v>7</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>9</v>
@@ -8111,7 +8111,7 @@
         <v>7</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>9</v>
@@ -8128,7 +8128,7 @@
         <v>7</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>9</v>
@@ -8145,7 +8145,7 @@
         <v>7</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>9</v>
@@ -8162,7 +8162,7 @@
         <v>7</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>9</v>
@@ -8179,7 +8179,7 @@
         <v>7</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>9</v>
@@ -8196,7 +8196,7 @@
         <v>7</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>9</v>
@@ -8213,7 +8213,7 @@
         <v>7</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>9</v>
@@ -8230,7 +8230,7 @@
         <v>7</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>9</v>
@@ -8247,7 +8247,7 @@
         <v>7</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>9</v>
@@ -8264,7 +8264,7 @@
         <v>7</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E331" s="3" t="s">
         <v>9</v>
@@ -8281,7 +8281,7 @@
         <v>7</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>9</v>
